--- a/导入数据/量表导入_评定量表.xlsx
+++ b/导入数据/量表导入_评定量表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>说明</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>完整内容</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -445,6 +450,69 @@
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ADL评分（改良Barthel指数）
+姓名_________ 性别_________ 年龄_________ 床号_________ 住院号_________ 
+进食：10——独立，包括配戴辅助工具及进行相关预备活动
+ 8——能独立，但在以下情况需要协助，入切肉，打开盒装牛奶，瓶盖
+ 5——在监督下进食，要协助入糖、盐、抹黄油和其他预备活动
+ 2——能操作食具，如汤勺，但要他人在进食过程中主动协助
+ 0——依赖
+洗澡：5——在没有他人在旁能自行洗澡，包括浴池、盆池或淋浴
+ 4——在调节水温或转移时需要监督
+ 3——在转移到淋浴处或浴缸、清洗需要协助
+ 1——每一个步骤也需协助
+ 0——依赖
+修饰：5——患者能自行清洗脸、双手、梳头、刷牙，男性能使用任何
+剃须刀包括插入刀片，使用电插头，女性能涂上化妆品
+ 4——完成所有个人卫生项目，但在完成操作之前或之后需要协助
+ 3——在每一个或以上步骤需要协助
+ 1——每一个步骤都需协助
+ 0——不能进行整个过程，依赖
+穿衣：10——独立，包括穿、脱腰封或支具
+ 8——需要轻度协助，如系并纽扣、拉链、鞋带
+ 5——协助穿上或脱掉衣服
+ 2——患者有小量参与，但整体需要协助
+ 0——依赖
+入厕：10——独立，包括转移、整理衣服及用便纸。如在晚间借助便具，并能自行清理
+ 8——需监督。在夜间使用便椅或尿壶，需协助清理
+ 5——整理衣服、转移或洗手时需协助
+ 2——整个过程需协助
+ 0——依赖
+大便控制：10——完全控制排便，有需要时能自行使用栓剂或灌肠
+ 8——能在监督下使用栓剂、灌肠。偶尔失禁
+ 5——患者能配合合适位置，需协助进行通便或清洁。偶有失控现象
+ 2——需协助摆放合适位置排便及进行通便之方法
+ 0——失禁
+小便控制：10——能控制。如需要借助外置或内置便具，能自理
+ 8——大致能保持全日干爽。偶尔失禁或需轻度协助使用内置或外置便具
+ 5——保持干爽除夜间外，需协助使用便具
+ 2——失禁，但能协助运用外置或内置便具
+ 0——失禁，或依赖他人导尿
+床椅转移：15——独立，包括锁轮椅、移脚踏
+ 12——在监督下转移
+ 8——在任何方面需他人协助
+ 5——能参与，但需大量协助
+ 0——不能参与，需两人或机器协助转移
+平地步行：15——独立步行50米，可使用助行器
+ 12——在帮助或监督下步行50米
+ 8——需协助抓住并操作助行器
+ 5——能在一人不断协助下步行
+ 0——依赖
+使用轮椅（步行0-5分者）：5——能以轮椅行走50米，独立停在桌、床、马桶等地方
+ 4——能用轮椅在合理时间内行走在尝使用之地域，在转狭窄角落时需协助
+ 3——将轮椅停在桌前、床边时需他人不断协助
+ 1——能在短程推动轮椅
+ 0——依赖
+上下楼梯10——独立上下一段楼梯，可使用扶手或助行器
+ 8——整体不需协助，但因安全理由上需监督
+ 5——患者上下楼梯时需监督及协助，拿助行器
+ 2——整个过程需协助
+ 0——不能上下楼梯
+总分：_________</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -458,6 +526,25 @@
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>第九人民医院
+龙岗中心医院
+ 深圳市康复科
+ Ashworth量表评定
+姓名 性别 年龄 岁 科别 床号 床
+诊断： 住院号 
+0级 无肌张力的增加，被动活动患侧肢体在整个范围内都无阻力。
+1级 肌张力稍增加，表现为受累部分被动屈伸到ROM之末出现很小的阻力，或出现突然的卡住和释放。
+1+ 级 肌张力稍增加，表现为被动屈伸患肢在前50％ROM出现轻微的卡住感觉，后ROM的50％范围内，始终呈现极轻度的阻力。
+2级 肌张力轻度增加，被动活动患肢在ROM的大部分均有阻力，但受累部分仍可以活动。
+3级 肌张力中度增加，被动活动患肢在整个ROM内均有阻力，活动比较困难。
+4级 肌张力高度增加，患侧肢体僵硬，阻力很大，被动活动十分困难。
+时 间
+评 级
+评定者</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -471,6 +558,32 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+BDAE失语症严重程度分级
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断：
+分级
+语言表现
+ 年 月 日
+ 年 月 日
+ 年 月 日
+0级
+无有意义的言语，无听觉理解能力。
+1级
+言语交流中有不连续的言语表达，但大部分需要听者去推测、询问和猜测；可交流的信息范围有限、听者在言语交流中感到闲难。
+2级
+在听者的帮助下，可能进行熟悉话题的交谈。但对陌生话题常常不能表达出自己的思想，使患者与检查者都感到进行言语交流有困难。
+3级
+在仅需要少量帮助或无帮助下，患者可以讨论几乎所有的日常问题。但由于言语和(或)理解能力的减弱，使某些谈话出现困难或不大可能。
+4级
+言语流利，但可观察到有理解障碍，但思想和言语表达尚无明显限制。
+5级
+有极少的可分辨得出的言语障碍，患者主观上感到有点儿困难，但听者不一定能明显觉察到。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -480,6 +593,95 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>项 目
+分数
+內                 容
+初期评定
+ / /
+中期评定
+ / /
+末期评定
+ / /
+一、进食
+10
+5
+0
+自己在合理的时间內（约10秒钟吃一口）可用筷子取食眼前的食物。若需辅具时，应会自行穿脱。
+需部分帮助（切面包、抹黄油、夹菜、盛饭等）。
+依赖。
+二、转移
+15
+10
+5
+0
+自理。
+需要少量帮助(1人)或语言指导
+需两人或1个强壮、动作娴熟的人帮助。
+完全依赖别人。
+三、修饰
+5
+0
+可独立完成洗脸、洗手、刷牙及梳头。
+需要別人帮忙。
+四、上厕所
+10
+5
+0
+可自行进出厕所，不会弄脏衣物，并能穿好衣服。使用便盆者，可自行清理便盆。
+需帮忙保持姿勢的平衡，整理衣物或使用卫生紙。使用便盆者，可自行取放便盆，但须仰赖他人清理。
+需他人帮忙。
+五、洗澡
+5
+0
+可独立完成（不论是盆浴或淋浴）。
+需別人帮忙。
+六、行走（平地45m）
+15
+10
+5
+0
+使用或不使用辅具皆可独立行走50公尺以上。
+需要稍微的扶持或口头指导方可行走50公尺以上。
+虽无法行走，但可独立操纵轮椅（包括转弯、进门、及接近桌子、床沿）并可推行轮椅50公尺以上。
+需別人帮忙。
+七、上下楼梯
+10
+5
+0
+可自行上下楼梯（允许抓扶手、用拐杖）
+需要稍微帮忙或口头指导。
+无法上下楼梯。
+八、穿脫衣服
+10
+5
+0
+可自行穿脫衣服、鞋子及辅具。
+在別人帮忙下、可自行完成一半以上的动作。
+需別人帮忙。
+九、大便控制
+10
+5
+0
+能控制。
+偶尔失禁（每周＜1次）。
+失禁或昏迷。
+十、小便控制
+10
+5
+0
+能控制。
+偶尔失禁（每周＜1次）或尿急（无法等待便盆或无法即时赶到厕所）或需別人帮忙处理。
+失禁、昏迷或需要他人导尿。
+总  分
+评分标准：最高分100分。&gt;60分: 良，生活基本自理，41~60分：中度残疾，日常生活需要帮助；
+21~40分：重度残疾，日常生活明显依赖；≤20分：完全残疾，日常生活完全依赖。
+姓名 （第 PAGE 2 页） 病案号 
+ PAGE 2 
+评定者：</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,583 +695,5244 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>民
+热
+爹
+水
+名
+乐
+贴
+嘴
+若
+盆
+神
+都
+围
+女
+棚
+人
+偷
+肥
+吕
+法
+字
+骄
+学
+船
+瓦
+次
+悄
+绝
+床
+牛
+钟
+呼
+晕
+润
+刘
+冲
+脖
+南
+桑
+搬
+开
+模
+兰
+脏
+攀
+诺
+哭
+军
+伦
+该
+这是风车
+这是篷车
+这是大哥
+这是大车
+这是人民
+这是人名
+这是木盆
+这是木棚
+这是一半
+这是一磅
+这是木船
+这是木床
+ 这是工人
+这是功臣
+这是果子
+这是果汁
+这是诗词
+这是誓词
+这是公司
+这是工资
+这是阔绰
+这是过错</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Frenchay构音评定总结表</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+Frenchay构音评定总结表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 检查日期：
+主诉： 诊断： 
+正常
+轻度障碍
+中度障碍
+重度障碍
+极重度障碍
+27-28/28a
+18-26/28a
+14-17/28a
+7-13/28a
+0-6/28a
+ 构音障碍类型： 严重程度分级：</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>GMFCS</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>GMFCS分级</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GMFCS分级
+从障碍轻重、治疗等不同角度对 HYPERLINK "http://www.haodf.com/jibing/xiaoernaotan.htm" \t "_blank" 脑性瘫痪进行分度有助于综合判断及其预后，并指导制订康复目标。 +      1．障碍程度 +      按障碍程度的分度，是美国脑性 HYPERLINK "http://www.haodf.com/jibing/piantan.htm" \t "_blank" 瘫痪学会( AACP)的一种分类方法，他们根据患儿障碍的程度分以下四个等级： HYPERLINK "http://zhangjiankui.haodf.com/"  +      ①第一等级：几乎没有行动限制的脑性瘫痪患儿。 +      ②第二等级：具有中等程度限制的脑性瘫痪患儿。 +      ③第三等级：具有重等程度限制的脑性瘫痪患儿。 +      ④第四等级：有用性的运动及动作几乎完全不可能完成。 +      2．治疗角度 +      从治疗角度又分为以下几级： +      ①不需要特殊治疗的脑性瘫痪患儿。 +      ②只需要利用支具或少量的必要性治疗（如机能训练）的脑性瘫痪患儿。 +      ③需要利用必要的器具和支具，同时需要脑性瘫痪治疗专业小组进行必要的治疗。 +      ④存在着高度的运动障碍和机能障碍，需要长期的在具备综合医疗教育设施的儿童康复机构收容治疗。
+粗大运动功能分级脑性瘫痪粗大运动功能分级系统(gross motor function classification system, GMFCS)是Palisan。1997年在长期临床实践的基础上，根据脑性瘫痪患儿运动功能随年龄变化规律设计提出的分级系统，将脑性瘫痪患儿分为4个年龄组，每个年龄组又根据患儿运动功能的表现分为5个级别，I级最低，V级最高。5个级别最高能力描述见如下：  
+ HYPERLINK "http://www.haodf.com/jibing/xiaoernaotan.htm" \t "_blank" 脑瘫儿童GMFCS能力描述 +      脑性瘫痪各年龄组详细分级标准 +      小于2岁的脑性瘫痪患儿 +      I级：孩子可以坐位转换，还能坐在地板上用双手玩东西。孩子能用手和膝盖爬行，能拉着物体站起来并且扶着家具走几步。18个月到2岁的孩子可以不用任何辅助设施独立行走。 +      Ⅱ级：孩子可以坐在地板上但是需要用手支撑来维持身体的平衡。孩子能贴着地面匍匐爬行或者用双手和膝盖爬行。他们有可能拉着物体站起来并且扶着家具走几步。 +      Ⅲ级：孩子需要在下背部有支撑的情况下维持坐姿，还能够翻身及用腹部贴着地面爬行。 +      Ⅳ级：孩子可以控制头部，但坐在地板上的时候躯干需要支撑。他们可以从俯卧翻成仰卧，也可能从仰卧翻成俯卧。 +      V级：生理上的损伤限制了孩子对自主运动的控制能力。孩子在俯卧位和坐位时不能维持头部和躯干的抗重力姿势，只能在大人的帮助下翻身。 +      2~4岁的脑性瘫痪患儿 +      I级：孩子可以坐在地板上玩东西。他们可以在没有大人的帮助下完成地板上坐位和站立位的姿势转换，把行走作为首选移动方式，并不需要任何助步器械的帮助。 +      Ⅱ级：孩子可以坐在地板上，．但当双手拿物体的时候可能控制不了平衡。他们可以在没有大人帮助的情况下自如地坐位转换，可以拉着物体坐在稳定的对方，可以用手和膝盖交替爬行，可以扶着家具慢慢移动。他们首选的移动方式是使用助步器行走。 +      Ⅲ级：孩子可以用“W"状的姿势独自维持坐姿（坐在屈曲内旋的臀部和膝之间），并可能需要在大人的帮助下维持其他坐姿。腹爬或者手膝并用爬行是他们首选的自身移动的方式（但是常常不会双腿协调交替运动）。他们能拉着物体爬起来站在稳定的地方并做短距离的移动。如果有助步器或者大人帮助掌握方向和转弯，他们可以在房间里短距离行走。 +      Ⅳ级：这一级的孩子能坐在椅子上，但他们需要依靠特别的椅子来控制躯干，从而解放双手。他们可以在大人的帮助下，或者在有稳定的平面供他们用手推或拉的时候坐进椅子或离开椅子，顶多能在大人的监督下用助步器走一段很短的距离，但很难转身也很难在不平的平面上维持身体的平衡。这些孩子在公共场所不能独自行走，能在动力轮椅的帮助下自己活动。 +      V级：生理上的损伤限制了这些孩子对随意运动的控制以及维持身体和头部抗重力姿势的能力。他们各方面的运动功能都受到限制。特殊器械和辅助技术并不能完全补偿孩子在坐和站能力上的功能限制。这些第五级的孩子没有办法独立行动，需要转运，部分孩子能使用进一步改造后的电动轮椅进行活动。
+4~6岁的脑性瘫痪患儿 +      I级：的脑性瘫痪患儿可以在没有双手帮助的情况下离开或者坐在椅子上，可以在没有任何物体支撑的情况下从地板上或者从椅子上站起来，他们可以在室内室外走动，还能爬楼梯，正在发展跑和跳能力。 +      Ⅱ级：的脑性瘫痪患儿可以在双手玩东西的时候在椅子上坐稳，可以从地板上或者椅子上站起来，但是经常需要一个稳定的平面供他们的双手拉着或者推着。可以在室内没有任何助步器的帮助下行走，在室外的水平地面上也可以走上一小段距离。他们可以扶着扶手爬楼梯，但是不能跑和跳。 +      Ⅲ级：的脑性瘫痪患儿可以坐在一般的椅子上，但是需要骨盆或者躯干部位的支撑才能解放双手。孩子坐在椅子和离开椅子的时候需要一个稳定的平面供他们双手拉着或者推着。他们能够在助步器的帮助下在水平地面行走，在成人的帮助下可以上楼梯，但是当长距离旅行时或者在室外不平的地面无法独立行走。 +      Ⅳ级：的脑性瘫痪患儿可以坐在椅子上，但是需要特别的椅子来控制躯干平衡从而尽量地解放双手。他们坐在椅子或者离开椅子的时候，必须有大人的帮助，或在双手拉着或推着稳定平面的情况下才能完成。孩子顶多能够在助步器的帮助和成人的监视下走上一小段距离，但是他们很难转身，也很难在不平的地面上维持平衡。他们不能在公共场合自己行走，应用电动轮椅的话可以自己活动。 +      V级：生理上的损伤限制了孩子对自主运动的控制，也限制了他们维持头部和躯干抗重力姿势的能力。这些孩子各方面的运动功能都受到了限制，即使使用了特殊器械和辅助技术，也不能完全补偿他们在坐和站的功能上受到的限制。第五级的孩子完全不能独立活动，部
+分孩子通过使用进一步改造过的电动轮椅可能进行自主活动。 +      6~12岁的脑性瘫痪患儿 +      I级：孩子可以没有任何限制地在室内和室外行走并且可以爬楼梯。他们能表现出跑和跳等粗大运动能力，但是他们的速度、平衡和协调能力都有所下降。 +      Ⅱ级：的脑性瘫痪患儿可以在室内和户外行走，能够抓着扶手爬楼梯，但是在不平的地面或者斜坡上行走就会受到限制，在人群中或者狭窄的地方行走也受到限制。他们最多能勉强达到跑和跳的平衡。 +      Ⅲ级：孩子可以使用助步器在室内和室外的水平地面上行走，可能可以扶着扶手爬楼梯。根据上肢功能的不同，在较长距离的旅行或者户外不平的地形上时，有的孩子可以自己推着轮椅走，有的则需要被帮助。 +      Ⅳ级：这些的脑性瘫痪患儿可能继续维持他们在6岁以前获得的运动能力，也有的孩子在家、学校和公共场合可能更加依赖轮椅。这些孩子使用电动轮椅就可以自己活动
+V级：生理上的损伤限制了孩子对自主运动的控制，也限制了他们维持头部和躯干的抗重力姿势能力。这些孩子各方面的运动功能都受到了限制，即使使用了特殊器械和辅助技术，也不能完全补偿他们在坐和站功能上受到的限制。第五级的孩子完全不能独立活动，部分孩子通过使用进一步改造过的电动轮椅可以进行自主活动。 +      4．脑性瘫痪的临床分度（见表1） +      脑性瘫痪依据临床分度可分为轻度、中度及重度
+轻度：症状轻微，日后不需要依赖他人照顾，可独立完成一切日常生活活动。
+中度：症状较重，治疗后仍需借助于支架和助具才能进行日常生活。
+重度：有严重的运动功能障碍，常伴有语言、智力障碍、治疗困难，日后很难独立生活，必须终生照顾。
+按1989年Russian和Gage提出的功能状态分级，小儿脑瘫可分为轻、中、重三级，见表1如下：
+表1 脑性瘫痪的临床分度
+分级 粗大运动 精细运动 IQ 语言 ADL
+ 轻 独立行走 功能不受限 &gt;70 2字 独立
+ 中 爬行或有支撑行走 功能受限 50~70 单字 需求帮助
+ 重 不能在辅具器具下行走？ 无功能 &lt;50 严重受损 完全照顾
+IQ：智商 ADL：日常生活活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>GMFCS分级1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GLASGOW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Glasgow昏迷评定表</t>
-        </is>
-      </c>
       <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GMFCS分级
+从障碍轻重、治疗等不同角度对 HYPERLINK "http://www.haodf.com/jibing/xiaoernaotan.htm" \t "_blank" 脑性瘫痪进行分度有助于综合判断及其预后，并指导制订康复目标。 +      1．障碍程度 +      按障碍程度的分度，是美国脑性 HYPERLINK "http://www.haodf.com/jibing/piantan.htm" \t "_blank" 瘫痪学会( AACP)的一种分类方法，他们根据患儿障碍的程度分以下四个等级： HYPERLINK "http://zhangjiankui.haodf.com/"  +      ①第一等级：几乎没有行动限制的脑性瘫痪患儿。 +      ②第二等级：具有中等程度限制的脑性瘫痪患儿。 +      ③第三等级：具有重等程度限制的脑性瘫痪患儿。 +      ④第四等级：有用性的运动及动作几乎完全不可能完成。 +      2．治疗角度 +      从治疗角度又分为以下几级： +      ①不需要特殊治疗的脑性瘫痪患儿。 +      ②只需要利用支具或少量的必要性治疗（如机能训练）的脑性瘫痪患儿。 +      ③需要利用必要的器具和支具，同时需要脑性瘫痪治疗专业小组进行必要的治疗。 +      ④存在着高度的运动障碍和机能障碍，需要长期的在具备综合医疗教育设施的儿童康复机构收容治疗。
+粗大运动功能分级脑性瘫痪粗大运动功能分级系统(gross motor function classification system, GMFCS)是Palisan。1997年在长期临床实践的基础上，根据脑性瘫痪患儿运动功能随年龄变化规律设计提出的分级系统，将脑性瘫痪患儿分为4个年龄组，每个年龄组又根据患儿运动功能的表现分为5个级别，I级最低，V级最高。5个级别最高能力描述见如下：  
+ HYPERLINK "http://www.haodf.com/jibing/xiaoernaotan.htm" \t "_blank" 脑瘫儿童GMFCS能力描述 +      脑性瘫痪各年龄组详细分级标准 +      小于2岁的脑性瘫痪患儿 +      I级：孩子可以坐位转换，还能坐在地板上用双手玩东西。孩子能用手和膝盖爬行，能拉着物体站起来并且扶着家具走几步。18个月到2岁的孩子可以不用任何辅助设施独立行走。 +      Ⅱ级：孩子可以坐在地板上但是需要用手支撑来维持身体的平衡。孩子能贴着地面匍匐爬行或者用双手和膝盖爬行。他们有可能拉着物体站起来并且扶着家具走几步。 +      Ⅲ级：孩子需要在下背部有支撑的情况下维持坐姿，还能够翻身及用腹部贴着地面爬行。 +      Ⅳ级：孩子可以控制头部，但坐在地板上的时候躯干需要支撑。他们可以从俯卧翻成仰卧，也可能从仰卧翻成俯卧。 +      V级：生理上的损伤限制了孩子对自主运动的控制能力。孩子在俯卧位和坐位时不能维持头部和躯干的抗重力姿势，只能在大人的帮助下翻身。 +      2~4岁的脑性瘫痪患儿 +      I级：孩子可以坐在地板上玩东西。他们可以在没有大人的帮助下完成地板上坐位和站立位的姿势转换，把行走作为首选移动方式，并不需要任何助步器械的帮助。 +      Ⅱ级：孩子可以坐在地板上，．但当双手拿物体的时候可能控制不了平衡。他们可以在没有大人帮助的情况下自如地坐位转换，可以拉着物体坐在稳定的对方，可以用手和膝盖交替爬行，可以扶着家具慢慢移动。他们首选的移动方式是使用助步器行走。 +      Ⅲ级：孩子可以用“W"状的姿势独自维持坐姿（坐在屈曲内旋的臀部和膝之间），并可能需要在大人的帮助下维持其他坐姿。腹爬或者手膝并用爬行是他们首选的自身移动的方式（但是常常不会双腿协调交替运动）。他们能拉着物体爬起来站在稳定的地方并做短距离的移动。如果有助步器或者大人帮助掌握方向和转弯，他们可以在房间里短距离行走。 +      Ⅳ级：这一级的孩子能坐在椅子上，但他们需要依靠特别的椅子来控制躯干，从而解放双手。他们可以在大人的帮助下，或者在有稳定的平面供他们用手推或拉的时候坐进椅子或离开椅子，顶多能在大人的监督下用助步器走一段很短的距离，但很难转身也很难在不平的平面上维持身体的平衡。这些孩子在公共场所不能独自行走，能在动力轮椅的帮助下自己活动。 +      V级：生理上的损伤限制了这些孩子对随意运动的控制以及维持身体和头部抗重力姿势的能力。他们各方面的运动功能都受到限制。特殊器械和辅助技术并不能完全补偿孩子在坐和站能力上的功能限制。这些第五级的孩子没有办法独立行动，需要转运，部分孩子能使用进一步改造后的电动轮椅进行活动。
+4~6岁的脑性瘫痪患儿 +      I级：的脑性瘫痪患儿可以在没有双手帮助的情况下离开或者坐在椅子上，可以在没有任何物体支撑的情况下从地板上或者从椅子上站起来，他们可以在室内室外走动，还能爬楼梯，正在发展跑和跳能力。 +      Ⅱ级：的脑性瘫痪患儿可以在双手玩东西的时候在椅子上坐稳，可以从地板上或者椅子上站起来，但是经常需要一个稳定的平面供他们的双手拉着或者推着。可以在室内没有任何助步器的帮助下行走，在室外的水平地面上也可以走上一小段距离。他们可以扶着扶手爬楼梯，但是不能跑和跳。 +      Ⅲ级：的脑性瘫痪患儿可以坐在一般的椅子上，但是需要骨盆或者躯干部位的支撑才能解放双手。孩子坐在椅子和离开椅子的时候需要一个稳定的平面供他们双手拉着或者推着。他们能够在助步器的帮助下在水平地面行走，在成人的帮助下可以上楼梯，但是当长距离旅行时或者在室外不平的地面无法独立行走。 +      Ⅳ级：的脑性瘫痪患儿可以坐在椅子上，但是需要特别的椅子来控制躯干平衡从而尽量地解放双手。他们坐在椅子或者离开椅子的时候，必须有大人的帮助，或在双手拉着或推着稳定平面的情况下才能完成。孩子顶多能够在助步器的帮助和成人的监视下走上一小段距离，但是他们很难转身，也很难在不平的地面上维持平衡。他们不能在公共场合自己行走，应用电动轮椅的话可以自己活动。 +      V级：生理上的损伤限制了孩子对自主运动的控制，也限制了他们维持头部和躯干抗重力姿势的能力。这些孩子各方面的运动功能都受到了限制，即使使用了特殊器械和辅助技术，也不能完全补偿他们在坐和站的功能上受到的限制。第五级的孩子完全不能独立活动，部
+分孩子通过使用进一步改造过的电动轮椅可能进行自主活动。 +      6~12岁的脑性瘫痪患儿 +      I级：孩子可以没有任何限制地在室内和室外行走并且可以爬楼梯。他们能表现出跑和跳等粗大运动能力，但是他们的速度、平衡和协调能力都有所下降。 +      Ⅱ级：的脑性瘫痪患儿可以在室内和户外行走，能够抓着扶手爬楼梯，但是在不平的地面或者斜坡上行走就会受到限制，在人群中或者狭窄的地方行走也受到限制。他们最多能勉强达到跑和跳的平衡。 +      Ⅲ级：孩子可以使用助步器在室内和室外的水平地面上行走，可能可以扶着扶手爬楼梯。根据上肢功能的不同，在较长距离的旅行或者户外不平的地形上时，有的孩子可以自己推着轮椅走，有的则需要被帮助。 +      Ⅳ级：这些的脑性瘫痪患儿可能继续维持他们在6岁以前获得的运动能力，也有的孩子在家、学校和公共场合可能更加依赖轮椅。这些孩子使用电动轮椅就可以自己活动
+V级：生理上的损伤限制了孩子对自主运动的控制，也限制了他们维持头部和躯干的抗重力姿势能力。这些孩子各方面的运动功能都受到了限制，即使使用了特殊器械和辅助技术，也不能完全补偿他们在坐和站功能上受到的限制。第五级的孩子完全不能独立活动，部分孩子通过使用进一步改造过的电动轮椅可以进行自主活动。 +      4．脑性瘫痪的临床分度（见表1-2） +      脑性瘫痪依据临床分度可分为轻度、中度及重度</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HACHINSKI</t>
+          <t>GLASGOW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HACHINSKI缺血指数量表</t>
+          <t>Glasgow昏迷评定表</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Glasgow昏迷评定表
+项目 
+患者反应 
+评分
+睁眼（E）
+对疼痛无反应（捏患者时不睁眼）
+1
+对疼痛刺激可有反应（捏患者时能睁眼）
+2
+对语言剌激可有反应（大声向患者提问时患者睁眼） 
+3
+自然睁眼 
+4
+最佳言语反应（V）
+无反应（不发声）
+1
+不可理解的反应（发声）
+2
+不适当反应（能理解，无意义）
+3
+含混反应（言语错乱，定向障碍）
+4
+完全清醒，定向佳（正确会话，人时地定向）
+5
+最佳运动反应
+无反应（捏痛患者毫无反应）
+1
+痛刺激有伸展反应（捏痛时患者身体呈大脑强直：上肢伸直、内收内旋，腕指屈曲，下肢与去皮质强直同）
+2
+痛刺激出现屈曲反应（捏痛时患者身体呈去皮质强直：上肢屈曲、内收内旋；下肢伸直，内收内旋，踝跖屈）
+3
+痛刺激出现逃避反应（捏痛时患者撤出被捏的部分）
+4
+痛刺激出现局部反应（捏痛时患者拨开医生手）
+5
+正常反应（能执行简单命令）
+6
+≤8有昏迷； ≥9示无昏迷； ＜8──严重损伤； 9～11──中度损伤； ≥12──轻度损伤</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOFFER</t>
+          <t>HACHINSKI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hoffer步行能力及Holden步行功能评定表</t>
+          <t>HACHINSKI缺血指数量表</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+HACHINSKI缺血指数量表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+项目
+是
+否
+1.急性起病 
+2
+0
+2.阶梯性恶化 
+1
+0
+3.波动性病程 
+2
+0
+4.夜间谵妄 
+1
+0
+5.人格保持良好 
+1
+0
+6.抑郁 
+1
+0
+7.诉说躯体症状 
+1
+0
+8.情绪不稳定 
+1
+0
+9.高血压的既往史 
+1
+0
+10.脑血管障碍的既往史 
+2
+0
+11.合并动脉粥样硬化的证据 
+1
+0
+12.神经系统局灶性症状 
+2
+0
+13.神经系统局灶性体征 
+2
+0
+说明：
+仅用于老年性痴呆和血管性痴呆的鉴别诊断
+≥7分为血管性痴呆
+≤4分者为AD
+5~6之间为混合型痴呆</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JOA</t>
+          <t>HOFFER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JOA颈椎病判定标准</t>
+          <t>Hoffer步行能力及Holden步行功能评定表</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>第九人民医院
+龙岗中心医院
+ 深圳市康复科
+姓名 性别 年龄 岁 床号 床 住院号 
+诊断： 
+Hoffer步行能力分级
+分级
+评定标准
+Ⅰ 不能步行(nonambulator)
+完全不能步行
+Ⅱ 非功能性步行
+(nonfunctional ambulator)
+借助于膝-踝-足矫形器（KAFO）、手杖等能在室内行走，又称治疗性步行。
+Ⅲ 家庭性步行
+(household ambulator)
+借助于踝-足矫形器（AFO）、手杖等能在室内行走自如，但在室外不能长时间行走。
+Ⅳ 社区性步行
+(community ambulator)
+借助于AFO、手杖或独立可在室外和社区内行走、散步、去公园、去诊所、购物等活动，但时间不能持久，如需要离开社区长时间步行仍需坐轮椅。
+时 间
+分 级
+评定者
+Holden步行功能分类
+级别
+表现
+0级：无功能
+患者不能走，需要轮椅或2人协助才能走。
+Ⅰ级：需大量持续性的帮助
+需使用双拐或需要1个人连续不断地搀扶才能行走或保持平衡。
+Ⅱ级：需少量帮助
+能行走但平衡不佳，不安全，需1人在旁给予持续或间断的接触身体的帮助或需使用膝-踝-足矫形器（KAFO）、踝-足矫形器（AFO）、单拐、手杖等以保持平衡和保证安全。
+Ⅲ级：需监护或语言指导
+能行走，但不正常或不够安全，需1人监护或用语言指导，但不接触身体。
+Ⅳ级：平地上独立
+在平地上能独立行走，但在上下斜坡、在不平的地面上行走或上下楼梯时仍有困难，需他人帮助或监护。
+Ⅴ级：完全独立
+在任何地方都能独立行走。
+时 间
+级 别
+评定者</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>JOA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MMSE</t>
+          <t>JOA颈椎病判定标准</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>颈椎病功能评价量表（JOA百分法）
+姓名 性别 年龄 岁 科别 床号 床
+诊断： 住院号 
+指标
+评分
+运动功能（左右独立评价）
+肩、肘功能（三角肌、肱二头肌肌力测定）：
+ MMT≤2（排除肘部疾病所致）
+ MMT=3
+ MMT=4
+ MMT=5（耐久力不足，有脱力感）
+ MMT=5
+手指功能
+ 吃饭时不能用匙、叉，不能系扣子
+ 吃饭时能有匙、叉，能系大扣子
+ 吃饭时能有匙、叉，不能用刀，勉强可用筷子，能系扣子，但不能解
+ 吃饭时可勉强用力，能用筷子，能系大扣子，但系T恤衫的扣子困难
+ 吃饭时能自由运用刀叉，能有筷子，但不灵活，能解或系大扣子，能解或系T恤衫的扣子， 
+但稍有些不灵活
+下肢功能：（下肢功能没有明显的左右差别，左右同分）
+ 能站立，不能行走
+ 能扶着东西站立，能用步行器行走
+可用拐杖（单拐）行走，可上楼梯，不能单腿跳
+平地可不用拐杖行走，可上下楼梯（下楼时需有扶手），单腿可站立
+平地可快速行走，对跑没有信心，下楼梯不灵活，可单腿跳
+正常，可单腿跳，步行、上下楼梯很自由
+感觉功能（左右独立评价）
+上肢、躯干、下肢% 左 右 
+感觉消失 0 0：
+难以忍受的麻木，知道自己接触了东西、但不能识别其形状、质地，麻木的难以入睡 3 3：
+能识别所接触物品的形状、质地，但只能感觉出一半，有时要用药物才能止住的疼痛， 5 5：
+ 有麻木感
+触觉基本正常，有轻微的痛觉钝性麻木 8 8：
+正常，无麻木、疼痛 10 10：
+（%为根据患者自己的评价与正常对比所残存感觉的程度）
+膀胱功能
+ 不能自行排尿或尿失禁
+ 可勉强自行排尿，有时有尿不尽感，或需用尿布
+ 尿频，排尿时无尿线，有时有尿失禁，弄脏下装
+膨胀感正常，但排尿时需等一段时间，尿频
+膨胀感，排尿均正常
+治疗前（ 月 日）总分：
+治疗后（ 月 日）总分：
+0
+2
+3
+4
+5
+0
+2
+4
+6
+8
+0
+2
+4
+6
+8
+10
+（0-10%）
+（20%-40%）
+（50%-70%）
+（80%-90%）
+（100%）
+0
+3
+5
+8
+10
+注:改善率= 治疗后分数-治疗前分数 ×100%
+ 100-治疗前分数
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RIVERMEAD</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rivermead行为记忆功能评定</t>
+          <t>MMSE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+简易智能状态评定表（MMSE）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+诊断： 检查日期：
+题号
+检查内容
+记分
+1
+现在是那一年？
+1
+2
+现在是什么季节？
+1
+3
+现在是几月份？
+0
+4
+今天是几号？
+0
+5
+今天是星期几？
+0
+6
+我们现在是在哪个国家？
+1
+7
+我们现在是在哪个城市？
+1
+8
+我们现在是在哪个城区（或什么路、哪一个省）？
+1
+9
+（这里是什么地方？）这里是哪个医院？ 
+1
+10
+这里是第几层楼？（你是哪一床？）
+1
+11
+我告述你三样东西，在我说完之后请你重复一遍它们的名字，“树”、“钟”、“汽车”。
+请你记住，过一会儿我还要你回忆出它们的名字来。
+树
+钟
+汽车
+1
+1
+1
+12
+请你算算下面几组算术：
+100―7=？
+93―7=？
+86―7=？
+79―7=？
+72―7=？
+93
+86
+79
+72
+65
+1
+1
+1
+1
+1
+13
+现在请您说出刚才我让你记住的那三种东西的名字？
+树
+钟
+汽车
+1
+0
+0
+14
+（出示手表）这个东西叫什么？
+1
+15
+（出示铅笔）这个东西叫什么？
+1
+16
+请你跟我说“如果、并且、但是”
+1
+17
+我给你一张纸，请你按我说的去做，现在开始：“用左/右手（未受累侧）拿着这张纸”；“用（两只）手将它对折起来”“把纸放在你的左腿上”
+2
+18
+请你念念这句话，并按上面的意思去做。“闭上你的眼睛”
+1
+19
+请你给我写一个完整的句子
+1
+20
+（出示图案）请你按这个样子把它画下来。
+1
+总分
+闭上你的眼睛
+ 。
+文盲小于17分、小学小于20分、中学以上小于24分为痴呆。（20-26 轻度痴呆，10－19 中度痴呆，10以下严重痴呆）。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPENGLER</t>
+          <t>RIVERMEAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spengler腰椎间盘突出症评价</t>
+          <t>Rivermead行为记忆功能评定</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+Rivermead行为记忆功能评定表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+检查项目
+操作方法
+评分标准
+1、记住姓和名
+让患者看一张人像照片，并告知他照片上人的姓和名。延迟一段时间后让他回答照片上人的姓和名，延迟期间让他看一些其他东西。
+姓和名均答对，2分；仅答出姓或名1分；否则0分。
+2.记住藏起的物品
+向患者借一些属于他个人的梳子、铅笔、手帕、治疗时间表等不贵重的物品，当着他的面藏在抽屉或柜橱内，然后让他进行一些与此无关的活动，结束前问患者上述物品放于何处。
+正确指出所藏的地点，1分；否则0分。
+3. 记住预约的申请
+告诉患者，医生将闹钟定于20min后闹响，让他20min后听到闹钟响时提出一次预约的申请，如向医生问“您能告诉我什么时候再来就诊吗”？
+钟响当时能提出正确问题，1分；否则0分。
+4. 记住一段短的路线
+让患者看着医生手拿一信封在屋内走一条分5段的路线：椅子→门→窗前→书桌，并在书桌上放下信封→椅子→从书桌上拿信封放到患者前面。让患者照样做。
+5段全记住，1分；否则0分。
+5. 延迟后记住一段短路线 +
+方法同4 ，但不立刻让患者重复，而是延迟一段时间再让他重复，延迟期间和他谈一些其他事。
+评分：全记住，1分；否则0分。
+6. 记住一项任务
+即观察4 .中放信封的地点是否对。
+立即和延迟后都对，1分；否则0分。
+7.学一种新技能
+找一个可设定时间、月、日的计算器或大一些的电子表，让患者学习确定月、日、时和分（操作顺序可依所用工具的要求而定）。①按下设定扭（set）；②输人月份，如为3月，输人3；③输入日，如为 16，输人 16；④接仪器上的日期（date）扭，通知仪器这是日期⑤输人时间，如为1时54分，输人l－5－4；按下时刻（time）扭，告诉仪器这是时刻。然后按复位扭，消除一切输人，让患者尝试3次。
+3次内成功，1分；否则0分。
+8 定向
+问患者下列问题：①今年是哪一年？②本月是哪个月？③今日是星期几？④今日是本月的几号？⑤现在我们在哪里？⑥现在我们在哪个城市？⑦您多大年纪？⑧您何年出生？⑨现在总理的名字是什么？⑩谁是现届的国家主席？
+①②③④⑤⑥⑦全对，1分；否则0分。
+9.日期
+问8 .中的第④题时记下错、对。
+正确给1分，否则0分。
+10、辨认面孔
+让患者细看一些面部照片，每张看5 S，一共看5张。然后逐张问他这是男的还是女的？是不到40岁，还是大于40岁？然后给他10张面部照片，其中有5张是刚看过的，让他挑出来。
+全对1分；否则0分
+11 认识图画
+让患者看10张用线条图绘的物体画，每次一张，每张看5S，让他叫出每图中的物体的名字。在延迟后让患者从20张图画中找出刚看过的10张。
+全对1分；否则0分。
+总分
+以上11题除第一题最高2分外，余各最高为1分，故满分为12分。正常人总分9~12分，平均10.12分，标准差为1.16。脑损伤时至少3项不能完成，总分0~9分，平均3.76标准差为2.84。对脑损伤的患者最难的是①、②、③、⑩题，对第②题尤感困难。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>SPENGLER</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Spengler腰椎间盘突出症评价</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>腰椎间盘突出症综合功能评价
+姓名 性别 年龄 岁 科别 床号 床 住院号 
+神经生理检查
+评分
+月日
+月日
+月日
+1. 神经体征（25分）
+与突出节段相一致的肌肉无力
+伴有阳性EMG表现* 
+伴有阴性EMG表现 
+肌肉萎缩（大于2cm） 
+反射消失或两侧不对称** 
+患者50岁或50岁以下 
+患者50岁以上 
+无临床体征，EMG阳性*** 
+25
+10
+10
+20
+10
+15
+2. 坐骨神经紧张体征（25分）
+对侧直腿抬高试验阳性# 
+骨盆倾斜 
+背部运动时，腰椎椎旁肌无节律性收缩 
+同侧直腿抬高试验阳性## 
+20
+15
+15
+5
+总 分
+痛觉及活动能力评价
+背痛和下肢痛大部分（76%-100%）解除
+能从事惯常的工作
+身体活动不受限制或轻微受限
+不经常使用止痛药或不用止痛药
+良
+背痛和下肢痛大部分（26%-75%）解除
+能从事惯常的工作但受限制，或能从事轻工作
+身体活动受限制
+经常使用一般止痛药
+可
+背痛和下肢痛减轻很少一部分或没有缓解（0-25%），或疼痛加重
+不能工作
+身体活动极度受限
+经常使用强止痛药或麻醉药
+差
+评定人：
+其它记要：
+*EMG=肌电图（electromyography）
+**如果EMG阳性加5分
+***如果EMG阳性加15分
+#阳性表示：在无症状一侧做直腿抬高试验诱发无症状的臀、大腿、小腿的疼痛症状
+##标准的直腿抬高试验
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>ZUNG</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ZUNG抑郁自我评价表</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+Zung 抑郁自我评价量表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+提问内容：
+无
+有时
+经常
+持续
+得分
+1.我感到情绪沮丧，郁闷 
+1
+2
+3
+4
+2.我感到早晨心情最好 
+4
+3
+2
+1
+3.我要哭或想哭
+1
+2
+3
+4
+4.我夜间睡眠不好
+1
+2
+3
+4
+5.我吃饭像平时一样多 
+4
+3
+2
+1
+*6.我与异性密切接触时和以往一样感到愉快
+4
+3
+2
+1
+7.我感到体重减轻
+1
+2
+3
+4
+8.我为便秘烦恼
+1
+2
+3
+4
+9.我的心跳比平时快
+1
+2
+3
+4
+10.我无故感到疲劳
+1
+2
+3
+4
+*11.我的头脑像往常一样清楚
+4
+3
+2
+1
+*12.我做事情像平时一样不感到困难
+4
+3
+2
+1
+13.我坐卧不安，难以保持平静
+1
+2
+3
+4
+*14.我对未来感到有希望
+4
+3
+2
+1
+15.我比平时更容易激怒
+1
+2
+3
+4
+*16.我觉得决定什么事很容易
+4
+3
+2
+1
+*17.我感到自己是有用的和不可缺少的人
+4
+3
+2
+1
+*18.我的生活很有意义
+4
+3
+2
+1
+19.假如我死了别人会过的更好
+1
+2
+3
+4
+*20.我仍旧喜爱自己平时喜爱的东西
+4
+3
+2
+1
+总分
+结果分析：指标为总分。将20个项目的各个得分相加，即得粗分。标准分等于粗分乘以1.25后的整数部分。标准分：25-49正常，50-59轻度抑郁，60－69中度抑郁； 70及以上严重抑郁。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
         <is>
           <t>ZUNG焦虑自我评价表</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>APGAR</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>apgar评分</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+Zung 焦虑自我评定量表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期
+提问内容：
+没有或很少时间
+小部分时间
+相当多时间
+绝大部分或全部时间
+得分
+1.我感到比往常更加神经过敏和焦虑
+1
+2
+3
+4
+2.我无缘无故地感到担心
+1
+2
+3
+4
+3.我容易心烦意乱或感到恐慌
+1
+2
+3
+4
+4.我感到我的身体好象被分成几块,支离破碎
+1
+2
+3
+4
+5.我感到事事都很顺利,不会有倒霉的事发生
+4
+3
+2
+1
+6.我的四肢抖动和震颤
+1
+2
+3
+4
+7.我因头痛、颈痛和背痛而烦恼
+1
+2
+3
+4
+8.我感到无力且容易疲劳
+1
+2
+3
+4
+9.我感到很平静，能安静坐下来
+4
+3
+2
+1
+10.我感到我的心跳较快
+1
+2
+3
+4
+11.我因阵阵的眩晕而不舒服
+1
+2
+3
+4
+12.我有阵阵要昏倒的感觉
+1
+2
+3
+4
+13.我呼吸时进气和出气都不费力
+4
+3
+2
+1
+14.我的手指和脚趾感到麻木和刺痛
+1
+2
+3
+4
+15.我因胃痛和消化不良而苦恼
+1
+2
+3
+4
+16.我必须时常排尿
+1
+2
+3
+4
+17.我的手经常温暖而干燥
+4
+3
+2
+1
+18.我觉得脸红发烧发红
+1
+2
+3
+4
+19.我容易入睡,晚上睡得很好
+4
+3
+2
+1
+20.我做恶梦
+1
+2
+3
+4
+总分
+主要统计指标为总分。把 20 题得分相加为粗分，把粗分乘以 1.25 ，四舍五入取整数，即得到标准分。焦虑评定的分界值是&lt;46分,正常； 46-50分,轻度焦虑； &gt;50分,焦虑。 症状分值越高，症状越严重。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BERG</t>
+          <t>APGAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>berg平衡评定量表</t>
+          <t>apgar评分</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>apgar评分
+目录
+ HYPERLINK "http://baike.baidu.com/view/460973.htm" \l "1#1" 概念 
+ HYPERLINK "http://baike.baidu.com/view/460973.htm" \l "2#2" 评分标准 
+ HYPERLINK "http://baike.baidu.com/view/460973.htm" 编辑本段概念
+ Apgar评分，即阿氏评分、新生儿评分，是孩子出生后立即检查他身体状况的标准评估方法。在孩子出生后，根据皮肤颜色、心搏速率、呼吸、肌张力及运动、反射五项体征进行评分。满10分者为正常新生儿，评分7分以下的新生儿考虑患有轻度窒息，评分在4分以下考虑患有重度窒息。大部分新生儿的评分多在7 - 10分之间。 
+ HYPERLINK "http://baike.baidu.com/view/460973.htm" 编辑本段评分标准
+ 评分具体标准是： 
+ 1．皮肤颜色：评估新生儿肺部血氧交换的情况。全身皮肤呈粉红色为2分，手脚末梢呈青紫色为1分，全身呈青紫色为0分。 
+ 2．心搏速率：评估新生儿心脏跳动的强度和节律性。心搏有力大于100次/分钟为2分，心搏微弱小于100次/分钟为1分，听不到心音为0分。 
+ 3．呼吸：评估新生儿中枢和肺脏的成熟度。呼吸规律为2分，呼吸节律不齐（如浅而不规则或急促费力）为1分，没有呼吸为0分。 
+ 4．肌张力及运动：评估新生儿中枢反射及肌肉强健度。肌张力正常为2分，肌张力异常亢进或低下为1分，肌张力松弛为0分。 
+ 5．反射：评估新生儿对外界刺激的反应能力。对弹足底或其他刺激大声啼哭为2分，低声抽泣或皱眉为1分，毫无反应为0分。 
+ 以这五项体征为依据，满10分者为正常新生儿，评分7分以下的新生儿考虑患有轻度窒息，评分在4分以下考虑患有重度窒息。大部分新生儿的评分多在7- 10分之间，医生会根据孩子的评分予以相应的处理。轻度窒息的新生儿一般经清理呼吸道、吸氧等措施后会很快好转，预后良好。一般新生儿出生后，分别做1分钟、5分钟及10分钟的Apgar评分，以便观察新生儿窒息情况的有无及其变化，以此决定是否需要做处理，以及做相应处理后，评价新生儿的恢复情况。[1]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>BERG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>berg平衡评定量表</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>第九人民医院
+龙岗中心医院
+ 深圳市康复科
+Berg平衡评定量表
+姓名 性别 年龄 岁 科别 床号 床
+诊断： 住院号 
+项 目
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+1.由坐到站
+2.独立站立
+3.独立坐
+4.由站到坐
+5.床－椅转移
+6.闭眼站立
+7.双足并拢站立
+8.站立位上肢前伸
+9.站立位从地上拾物
+10.转身向后看
+11.转身一周
+12.双足交替踏
+13.双足前后站
+14.单腿站立
+总 分
+评 定 人
+注：低于40分表明有摔倒的危险
+1.由坐到站 受试者体位：患者坐于治疗床上 测试命令：请站起来
+4分：不用手帮助即能够站起且能够保持稳定； 3分：用手帮助能够自己站起来 2分：用手帮助经过几次努力后能够站起来； 1分：需要较小的帮助能够站起来或保持稳定 0分：需要中度或较大的帮助才能够站起来
+2.独立站立 受试者体位：站立位 测试命令：请尽量站稳
+4分：能够安全站立2分钟； 3分：能够在监护下站立2分钟 2分：能够独立站立30秒； 1分：经过几次努力能够独立站立30秒 ； 0分：没有帮助不能站立30秒（如果受试者能够独立站立2分钟则第3项满分继续进行第4项评定）
+3.独立坐 受试者体位：坐在椅子上，双足平放在地上、背部要离开椅背；测试命令：请将上肢交叉抱在胸前并尽量坐稳 
+4分：能够安全的坐2分钟； 3分：能够在监护下坐2分钟； 2分：能够坐30秒； 
+1分：能够坐10秒； 0分：没有支撑则不能坐10秒
+4.由站到坐 受试者体位：站立位 测试命令：请坐下
+4分：用手稍微帮助即能够安全的坐下； 3分：需要用手帮助来控制身体重心下移； 2分：需要双腿后侧抵住椅子来控制身体重心下移； 1分：能独立坐在椅子上但不能控制身体重心下移； 0分：需要帮助才能坐下 
+5.床－椅转移（先在治疗床旁边准备一张有扶手和一张无扶手的椅子） 受试者体位：患者坐于治疗床上，双足平放于地面 测试命令：请坐到有扶手的椅子上来，再坐回床上，然后再坐到无扶手的椅子上，再坐回床上。
+ 4分：用手稍微帮助即能够安全转移； 3分：必须用手帮助才能够安全转移； 2分：需要监护或语言提示才能完成转移
+1分：需要一个人帮助才能完成转移； 0分：需要两个人帮助或监护才能够完成转移
+6.闭眼站立 受试者体位：站立位 测试命令：请闭上眼睛，尽量站稳
+4分：能够安全站立10秒； 3分：能够在监护下站立10秒； 2分：能够站立3秒
+1分：闭眼不能站立3秒但睁眼站立能保持稳定； 0分：需要帮助以避免跌倒
+7.双足并拢站立 受试者体位：站立位 测试命令：请将双脚并拢并且尽量站稳
+4分：能够独立将双脚并拢并独立站立1分钟； 3分：能够独立将双脚并拢并在监护下站立1分钟； 2分：能够独立将双脚并拢但不能站立30秒；1分：需要帮助才能将双脚并拢且能够站立15秒； 0分：需要帮助才能将双脚并拢且双脚并拢后不能站立15秒
+8.站立位上肢前伸 受试者体位：站立位 测试命令：将手臂抬高90度，伸直手指并尽力向前伸，请注意双脚不要移动。（进行此项测试时，要先将一根皮尺横向固定在墙壁上，受试者上肢前伸时，测量手指起始位和终末位对应于皮尺上的刻度，两者之差为患者上肢前伸的距离，如果可能的话，为了避免躯干旋转，受试者要两臂同时前伸）
+4分：能够前伸大于25cm的距离； 3分：能够前伸大于12cm的距离； 2分：能够前伸大于5cm的距离；；
+1分：能够前伸但需要监护； 0分：当试图前伸时失去平衡或需要外界支撑
+9.站立位从地上拾物 受试者体位：站立位 测试命令：请把你双脚前面的拖鞋捡起来
+4分：能够安全而轻易的捡起拖鞋； 3分：能够在监护下捡起拖鞋； 2分：不能捡起但能够到达距离拖鞋2～5cm的位置并且独立保持平衡； 
+1分：不能捡起并且当试图努力时需要监护； 0分：不能尝试此项活动或需要帮助以避免失去平衡或跌倒
+10.转身向后看 受试者体位：站立位 测试命令：双脚不要动，先向左侧转身向后看，再向右侧转身向后看（评定者可以站在受试者身后手拿一个受试者可以看到的物体以鼓励其更好的转身）
+4分：能够从两侧向后看且重心转移良好； 3分：只能从一侧向后看，另一侧重心转移较差； 2分：只能向侧方转身但能够保持平衡； 
+1分：当转身时需要监护； 0分：需要帮助以避免失去平衡或跌倒
+11.转身一周 受试者体位：站立位 测试命令：请转一圈，暂停，然后在另一个方向转一圈。
+4分：能从两个方向用4秒或更短时间安全转一圈； 3分：能在一个方向用4秒或更短时间安全转一圈； 
+2分：能够安全的转一圈但用时超过4秒； 1分：转身时需要密切监护或语言提示； 0分：转身时需要帮助
+12.双足交替踏台阶 受试者体位：站立位 测试命令：请将左、右脚交替放到台阶上，直到每只脚都踏过4次台阶或凳子（先在受试者面前放一个台阶或一只高度与台阶相当的小凳子）。
+4分：能够独立安全站立且在20秒内完成8个动作； 3分：能够独立站立，但完成8个动作的时间超过20秒； 
+2分：在监护下不需要帮助能够完成4个动作；1分：需要较少帮助能够完成2个或以上的动作；0分：需要帮助以避免跌倒或不能尝试此项活动
+13.双足前后站立 受试者体位：站立位 测试命令：（示范给受试者）将一只脚放在另一只脚的正前方并尽量站稳，如果不行就将一只放在另一只脚前面尽量远的地方，这样前脚后跟就在后脚足趾之前（要得到3分，步长要超过另一只脚长度且双脚支撑的宽度应接近受试者正常支撑宽度）
+4分：能够独立的将一只脚放在另一只脚的正前方且保持30秒； 3分：能够独立的将一只脚放在另一只脚的前方且保持30秒；
+2分：能够独立的将一只脚向前迈一小步且能够保持30秒；； 1分：需要帮助才能向前迈步但能保持15秒； 0分：当迈步或站立时失去平衡。14.单腿站立 受试者体位：站立位 测试命令：请单腿站立尽可能长的时间。
+4分：能够独立抬起一条腿且保持10秒以上； 3分：能够独立抬起一条腿且保持5～10秒； 2分：能够独立抬起一条腿且保持3～5秒； 
+1分：经过努力能够抬起一条腿，保持时间不足3秒站立平衡；； 0分：不能尝试此项活动或需要帮助以避免跌倒
+PAGE 
+PAGE 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>CAROLL</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>caroll上肢功能评定</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Carroll手功能试验
+姓名：          性别：        年龄：       病历号：
+临床诊断：                                      
+结论：                  
+分类
+方法
+实验用品规格（cm）
+重量（g）
+得分
+一、抓握
+1.抓起正方体木块
+10×10×10
+576
+2.抓起正方体木块
+7.5×7.5×7.5
+243
+3.抓起正方体木块
+5×5×5
+72
+4.抓起正方体木块
+2.5*2.5*2.5
+9
+二、握
+5.握圆柱体
+直径4，长15
+500
+6.握圆柱体
+直径2.2，长10
+125
+三、侧捏
+7.用拇指与食指侧捏起石板条
+11×2.5×1
+61
+四、捏
+8.捏起木球
+直径7.5
+100
+9-24.分别用拇指与食指、中指、环指和小指捏起4个不同大小的玻璃球或钢球
+直径± 1.6
+直径±1.1
+直径± 0.6
+直径±0.4
+6.3
+6.6
+1.0
+0.34
+五、放置
+25.把一个钢垫圈套在钉子上
+外径3.5，内径1.5，厚0.25±
+14.5
+26.把熨斗放在架子上
+2730
+六、旋前和旋后
+27.把壶里的水倒进一个杯
+子里
+2.84L
+28.把杯里的水倒进另一个杯子里（旋后）
+273ml
+29.把杯里的水倒进前一个杯子里（旋后）
+273ml
+30.把手依次放在头后
+31.把手放在头顶
+32.把手放在嘴上
+33.写上自己的名字
+  总分：             
+ 评定人：                   评定日期：       年   月    日
+评分标准：
+0分 全部不能完成
+1分 只能完成一部分
+2分 能完成但动作慢或笨拙
+3分 能正确地完成
+功能级的确定：
+1级 微弱 0-25分
+2级 很差 26-50分
+3级 差 51-75分
+4级 部分 76-89分
+5级 完全 90-98分
+6级 最大 99分（利手）96分（非利手）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
         <is>
           <t>三级平衡、10米步行、3米坐站时间</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>坐位、站位三级平衡：
+1级平衡：静态平衡
+2级平衡：自动态平衡
+3级平衡：他动态平衡
+10米步行时间：
+10米
+记录患者走10米的时间（前后2米不计）
+3米坐-站时间：
+3米
+记录患者从坐位站起，向前走3米，再返回座位上坐下的时间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>上田敏偏瘫上下肢12级评定总结表</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>评定系列表
+上田敏偏瘫上下肢12级评定表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp38.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp39.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp40.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp41.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp42.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp43.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp44.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp46.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp47.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp49.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp50.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp51.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp52.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp53.gif" \* MERGEFORMATINET</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>VAPS</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>下腰痛评估表（JOA、VAPS）</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>评定系列表
+下腰痛评定表（JOA score）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+（日期：前 / / / ，后 / / / ）
+主观症状(9分)
+评分
+评分
+LBP(3分) 
+前
+后
+感觉障碍(2分)
+前
+后
+无
+3
+3
+无
+2
+2
+偶有轻痛 
+2
+2
+轻度
+1
+1
+频发静止痛或偶发严重疼痛 
+1
+1
+明显
+0
+0
+频发或持续性严重疼痛
+0
+0
+运动障碍(MMT)(2分)
+腿痛或麻(3分) 
+正常(5级)
+2
+2
+无 
+3
+3
+稍弱(4级)
+1
+1
+偶有轻度腿痛 
+2
+2
+明显弱(0-3级)
+0
+0
+频发轻度腿痛或偶有重度腿痛 
+1
+1
+ADL受限(14分)
+重
+轻
+无
+频发或持续重度腿痛00前后前后前后步行能力(3分) 卧位翻身001122正常33站立001122能步行500m以上，可有痛、麻、肌弱22洗漱001122步行＜500 m，有痛、麻、肌弱 11身体前倾001122步行＜100 m，有痛、麻、肌弱00坐(1h)001122体征(6分)举物、持物001122直腿抬高(包括月国 绳肌紧张)(2分)膀胱功能(-6分)正常 
+2
+2
+正常
+0
+0
+30~70 
+1
+1
+轻度失控
+-3
+-3
+＜30
+0
+0
+严重失控
+-6
+-6
+总分
+前： 分
+后： 分
+2.视觉类比评分法（VAPS）（0无痛，10剧痛难忍，5中度疼痛）
+前：
+ 0 1 2 3 4 5 6 7 8 9 10
+后：
+ 0 1 2 3 4 5 6 7 8 9 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>BDC</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>伯恩斯忧郁症清单（BDC)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>低体重儿</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>偏瘫上下肢功能评定</t>
-        </is>
-      </c>
       <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+伯恩斯忧郁症清单（BDC）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+内 容
+没有０
+轻度１
+中度２
+严重３
+１．悲伤：你是否一直感到伤心或悲哀？ 
+２．泄气：你是否感到前景渺茫？
+３．缺乏自尊：你是否觉得自己没有价值或自以为是一个失败者？
+４．自卑：你是否觉得力不从心或自叹比不上别人？
+５．内疚：你是否对任何事都自责？
+６．犹豫：你是否在作决定时犹豫不决？
+７．焦躁不安：这段时间你是否一直处于愤怒和不满状态？
+８．对生活丧失兴趣：你对事业、家庭、爱好、或朋友是否丧失了兴趣？
+９．丧失动机：你是否感到一蹶不振，做事情毫无动力？
+１０．自我印象可怜：你是否以为自己已衰老或失去魅力？
+１１．食欲变化：你是否感到食欲不振？或情不自禁的暴饮暴食？
+１２．睡眠变化：你是否患有失眠症？或整天感到体力不支，昏昏欲睡？
+１３．丧失性欲：你是否丧失了对性的兴趣？
+１４．臆想症：你是否经常担心自己的健康？
+１５．自杀冲动：你是否认为生存没有价值，或生不如死？
+总分
+0-4分 没有忧郁症；5-10分 偶尔有忧郁情绪；11-20分 有轻度忧郁症；21-30分 有中度忧郁症；31-45分 有严重忧郁症并需要立即治疗。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>偏瘫患者平衡反应评价表</t>
+          <t>低体重儿</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>低体重儿
+ HYPERLINK "http://baike.baidu.com/view/1707800.htm" 求助编辑百科名片
+出生体重低于2500克的新生儿称为低体重儿。 在胎儿阶段，也就是孕后的8~38周里，母亲营养不良或疾病因素都可能导致胎儿发育迟缓，在出生时体重过低。 这样的新生儿皮下脂肪少，保温能力差，呼吸机能和代谢机能都比较弱，特别容易感染疾病，死亡率比体重正常的新生儿要高得多。其智力发展也会受到一定的影响。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ROM</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>关节活动度评定（ROM）</t>
+          <t>偏侧忽视症评定小结</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+偏侧空间忽视症评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+左半空间
+右半空间
+左右空间
+左半/右半（%）
+短线划销
+/18
+/18
+ /36
+字母划销
+ /20
+ /20
+ /40
+小五角星划销
+ /27
+ /27
+ /54
+双分线
+左：
+中：
+右：
+&lt;1.5cm, 3分，&lt;2cm, 2分，&lt;2.5cm，1 分
+图形临摹
+四角形：
+菱形：
+菊花：
+完整：1；细节：1，正确：1
+读时间
+7：40
+2：25
+11：55
+正确：1</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>利手评定</t>
+          <t>偏瘫上下肢功能评定</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>评定系列表
+偏瘫上下肢功能评定
+姓名： 性别： 年龄： 科室： 床号： 住院号：
+主诉：
+诊断： 检查日期：
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp54.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp55.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp56.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp57.gif" \* MERGEFORMATINET 
+ INCLUDEPICTURE "D:\\SSREADERBETA\\temp\\sstemp58.gif" \* MERGEFORMATINET</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>FIM</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>功能独立性评定（FIM）</t>
+          <t>偏瘫患者平衡反应评价表</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>评定系列表
+偏瘫患者平衡反应评价表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+评价动作
+判定标准
+分级
+1
+长坐位
+不能独立完成，需辅助
+0
+2
+长坐位
+能独立完成
+ = 1 \* ROMAN I
+3
+端坐位
+能独立完成，但不稳定．外力一推即倒
+ = 2 \* ROMAN II
+4
+坐位平衡反应出现
+端坐位，外力破坏坐位姿势时出现调整反应
+ = 3 \* ROMAN III
+5
+膝手卧位
+能够完成并且可以抬起一侧上肢，一侧下肢
+ = 4 \* ROMAN IV
+6
+跪位
+可以维持，但不稳定，一推即倒
+ = 5 \* ROMAN V
+7
+跪位步行
+跪位稳定，并且可以利用跪位步行
+ = 6 \* ROMAN VI
+8
+站立位
+可以维持站立，但不稳定，重心移动时常不能维持站立
+ = 7 \* ROMAN VII
+9
+单腿站立
+重心转移可以维持站立位
+ = 8 \* ROMAN VIII
+10
+平衡板上站立
+站在平衡板上，PT摇动平衡板患者，出现平衡反应
+ = 9 \* ROMAN IX
+11
+站立平衡反应
+外力破坏患者的立位平衡，可出现立位平衡反应
+ = 10 \* ROMAN X
+诊断：</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FCA</t>
+          <t>ROM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>功能综合评定量表 （FCA)</t>
+          <t>关节活动度评定（ROM）</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>评定系列表
+关节活动度（ROM）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+关节 
+运动 
+测量姿位 
+量角器放置标志 
+0点 
+正常值 
+检测值 
+中心 近端 远端 肩屈、伸 解剖位，背贴立柱站立 肩峰 腋中（铅垂线） 肱骨外上髁 两尺相重 屈180° 伸50° 外展 同上 同上 同上 同上 同上 外展180° 内、外旋 仰卧，肩外展肘屈90° 鹰嘴 铅垂线 尺骨茎突 同上 内旋90° 外旋90°肘 屈、伸 解剖位 肱骨外上髁 骨峰 尺骨茎突 两尺成一直线 屈150° 伸0° 腕屈、伸 解剖位 桡骨茎突 前臂纵轴 第二掌骨头 两尺成一直线 屈90° 伸90° 尺、桡屈 解剖位 腕关节中点 同上 第三掌骨头 同上 桡屈25° 尺屈65° 髋屈 仰卧，对侧髋过伸 股骨大粗隆 水平线 股骨外髁 两尺成一直线 屈125° 伸 仰卧，对侧髋屈曲 同上 同上 同上 同上 伸15° 内收、外展 仰卧，避免大腿旋转 髂前上棘 对侧髂前上棘 髌骨中心 两尺成直角 内收45° 外展45° 内外旋 仰卧、两小腿桌缘外下垂髌骨下端 铅垂线 胫骨前缘 两尺相重 内旋45° 
+外旋45°
+膝 屈、伸 仰卧 股骨外踝 股骨大粗隆 外踝 两尺成一直线 屈150°伸0°踝屈、伸 仰卧 内踝 股骨内踝 第一跖骨头 两尺成直角 屈150° 伸0° 内、外翻 俯卧 踝后方两踝 中点 小腿后纵轴 足跟中点 两尺成一直线 内翻35° 外翻25°</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>压疮分级</t>
+          <t>利手评定</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+利手评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+1.（右）写字（左） 2.（右）拿筷（左） 3.（右）剪纸（左） 
+4.（右）切菜（左） 5.（右）刷牙（左） 6.（右）提物（左） 
+7.（右）穿针（左） 8.（右）洗脸（左） 9.（右）划火柴（左）10.（右）扫地（左） 11.（右）炒菜（左） 12.（右）持钉锤（左）
+如果12项目全部或前7项都习用右手（或左手），而后5项中任何1至5项用另一只手，为右（或左）手利；前7项中有1至6项为一只手，其余6至1项用另一手，为混合利。
+结果： 1、左利手 2、右利手 3、混合利手</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FIM</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>吞咽功能评定量表汇总</t>
+          <t>功能独立性评定（FIM）</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>功能独立性评定（FIM）量表
+功能水平和评分标准：
+独立：活动中不需他人帮助
+ 1. 完全独立（7分）-- 构成活动的所有作业均能规范、完全地完成，不需修改和辅助设备或用品，并在合理的时间内完成
+ 2. 有条件的独立（6分）-- 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；或需要安全方面的考虑
+依赖：为了进行活动，患者需要另一个人予以监护或身体的接触性帮助，或者不进行活动
+ 1. 有条件的依赖--患者付出50%或更多的努力，其所需的辅助水平如下：
+ （1） 监护和准备（5分）-- 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需要帮助准备必需用品；或帮助带上矫形器。
+ （2）少量身体接触的帮助（4分）-- 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力。 
+ （3）中度身体接触的帮助（3分）-- 患者需要中度的帮助，自己能付出50%~75%的努力。
+2. 完全依赖 -- 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行。 
+（1）大量身体接触的帮助（2分）-- 患者付出的努力小于50%，但大于25%。 
+（2）完全依赖（1分）-- 患者付出的努力小于25%。
+ +FIM的最高分为126分（运动功能评分91分，认知功能评分35分），最低分18分。 +126分=完全独立；108分~125分=基本独立；90~107分=有条件的独立或极轻度依赖；72~89分轻度依赖；54~71分中度依赖；36~53分=重度依赖；19~35分=极重度依赖；18分=完全依赖。 + +表2 功能独立性量表（Function Independent Measure,FIM） +项 目 +自理活动 
+ • 进食 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+B．梳洗修饰 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+C．沐浴 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+D．穿上身衣服 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3 分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+E．穿下身衣服 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑
+5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% +1分 完全依赖 患者付出的努力小于25%
+ F．上厕所 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25%
+1分 完全依赖 患者付出的努力小于25% 括约肌控制 
+G．膀胱管理 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+H．大肠管理 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25%
+ 转移 +I．床、椅、轮椅 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25%
+1分 完全依赖 患者付出的努力小于25% 
+J．坐厕 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+ K.浴盆、淋浴室 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+进行步行* L．步行/轮椅 轮椅 两者 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+M．上下楼梯 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+运动总积分： 
+交流听* +N．理解 视 两者 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+言语* O．表达 非言语 两者 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力 +3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力 +2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+社会认知 +P．社会交往 +7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成 +6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑 +5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器 +4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力
+3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力
+2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+Q．解决问题
+7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成
+6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑
+5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器
+4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力
+3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力
+2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+R．记忆
+7分 完全独立 构成活动的所有作业均能规范的、安全的完成，不需要修改和辅助设备和用品，并在合理的时间内完成
+6分 有条件的独立 具有下列一项或几项：活动中需要辅助设备；活动需要比正常长的时间；需要安全方面的考虑
+5分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：监护或准备 患者所需的帮助只限于备用、提示或劝告，帮助者和患者之间没有身体的接触或帮助者仅需帮助准备必须用品；或帮助带上矫形器
+4分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：少量身体接触的帮助 患者所需的帮助只限于轻轻接触，自己能付出75%或以上的努力
+3分 有条件的依赖 患者自己付出50%或更多的努力，其所需的辅助水平如下：中度身体接触的帮助 患者需要中度的帮助，自己能付出50%-75%的努力
+2分 完全依赖 患者需要一半以上的帮助或完全依赖他人，否则活动就不能进行，大量身体接触的帮助，患者付出的努力小于50%，但大于25% 
+1分 完全依赖 患者付出的努力小于25% 
+认识总积分 
+总积分</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FCA</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>失用症检查</t>
+          <t>功能综合评定量表 （FCA)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>评定表系列
+功能综合评定量表 （FCA）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 
+评测内容
+月 日
+月 日
+月 日
+A. 自我照料
+进食
+修饰
+洗澡
+穿上衣
+穿下衣
+用厕
+B. 括约肌控制
+排便管理
+排尿管理
+C. 转移
+床椅转移
+11．卫生间
+12．浴池/浴室
+D. 行走
+12．步行/轮椅
+13．上下楼梯
+运动功能评分合计
+E. 交流
+14．视听理解
+15．语言表达
+F. 社会认知
+16．社会往来
+17．解决问题
+18．记忆能力
+认知功能评定合计
+总分
+ 评价者签名: __________时间: __________</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>平衡功能评定（Berg）</t>
+          <t>压疮分级</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>压疮分级
+ 1、褥疮依其病理过程分为4级，1级-皮肤完整出现指压不会变白的红印；2级-表皮或 HYPERLINK "http://baike.baidu.com/view/87952.htm" \t "_blank" 真皮受损，但尚未穿透真皮层;；3级-表皮或真皮全部受损，穿入皮下组织，但尚未穿透筋膜及肌肉层;；4级-全皮层损害；涉及肌肉，骨头。 2、根据伤口的颜色将褥疮愈合发展的过程分为:：①红色伤口：伤口基底部为健康的红色肉芽组织，清洁或正在愈合的伤口属于此类； ②黄色伤口：伤口基底部为脱落 HYPERLINK "http://baike.baidu.com/view/3687.htm" \t "_blank" 细胞和死亡细菌，一般黄色伤口又指感染伤口;；③黑色伤口:伤口有黑色的坏死组织和黑痂，如糖尿病足干性坏疽、深度褥疮表面的坏死痂皮； ④粉色伤口：有新生的上皮组织覆盖。 
+ 3、临床分度 
+ Ⅰ度：表皮无损伤，只是皮肤发红，但解除压迫30分钟以上发红尚无改善者，此期为急性炎症反应期。 
+ Ⅱ度：表皮发红、糜烂，有水泡，组织缺损未及真皮，创面湿润呈粉红色，伴有疼痛，无坏死组织。 
+ Ⅲ度：由真皮达皮下，为 喷火口状的组织缺损，伴有渗出液和感染，但几乎无疼痛，有坏死组织。 
+Ⅳ度：深达肌腱及骨，有渗出液和感染，有坏死组织，如有神经损伤则伴有剧烈疼痛。
+治疗
+ 治疗褥疮应该及早开始原则是解除患处压迫促进局部 HYPERLINK "http://baike.baidu.com/view/21711.htm" \t "_blank" 血液循环，加强创面处理。一度褥疮应定时按摩、变换体位，局部 HYPERLINK "http://baike.baidu.com/view/1722.htm" \t "_blank" 酒精涂擦或 HYPERLINK "http://baike.baidu.com/view/1813.htm" \t "_blank" 红外线照射，若炎症显著，可用0.5%的 HYPERLINK "http://baike.baidu.com/view/97031.htm" \t "_blank" 新霉素溶液湿敷。二度褥疮可外涂抗生素软膏后覆以无菌纱布。三度褥疮应进行清创处理， HYPERLINK "http://baike.baidu.com/view/465915.htm" \t "_blank" 溃疡小者可外用0.5% HYPERLINK "http://baike.baidu.com/view/168969.htm" \t "_blank" 硝酸银湿敷，以去除感染。同时可外用促进肉芽组织形成的药物。溃疡大而清洁者可采用分层皮片移植或覆以全层皮瓣。对坏疽性溃疡应去除坏死组织，充分引流后再做上述处理。对于创面脓液宜经常培养并做药敏试验，从而指导选择敏感抗生素外用若无全身感染迹象，一般健康搜索不需系统使用抗生素。此外对于重症患者应加强支持疗法。 1.中医疗法： 
+ 治法：益气通络，养血润肤。 
+ 方药1：黄芪15g， HYPERLINK "http://baike.baidu.com/view/41140.htm" \t "_blank" 党参15g， HYPERLINK "http://baike.baidu.com/view/41879.htm" \t "_blank" 白芍10g， HYPERLINK "http://baike.baidu.com/view/20956.htm" \t "_blank" 鸡血藤15g， HYPERLINK "http://baike.baidu.com/view/41407.htm" \t "_blank" 当归10g， HYPERLINK "http://baike.baidu.com/view/39526.htm" \t "_blank" 川芎5g， HYPERLINK "http://baike.baidu.com/view/20990.htm" \t "_blank" 红花10g， HYPERLINK "http://baike.baidu.com/view/41067.htm" \t "_blank" 丹参15g伸筋草15g，银花15g，连翘15g，陈皮10g。若肉腐溃脓，可加 HYPERLINK "http://baike.baidu.com/view/24824.htm" \t "_blank" 白芷、桔梗拔毒排脓；若肉腐不脱，可加炒山甲、炒皂刺。 
+ 方药2：田七 血竭 琥珀 生大黄 桃仁 红花 泽兰 归尾 乳香 川断 骨碎补 土鳖 杜仲 制马 钱子 苏木 秦艽 自然铜 没药 七叶一枝花 无名异 
+ 用法用量：外用：药酒纱布填塞伤口，每日滴药酒一次。也可内服。当发现皮肤潮红时，将十一方酒l0ml倒人手中用手掌按摩患处，每日二三次，局部有水疱形成者，用无菌注射器抽吸水疱内液后再涂擦十一方酒，每日二三次。如皮肤有溃疡、渗液，应立即用十一方酒纱布湿敷，每日三四次。 
+ 制备方法：上药各适量放人米三花酒7500ml，浸泡三至六个月后备用。 
+ 单方成药：可服八珍丸、人参养荣丸。 
+ 治疗药物 
+ 2.局部治疗 (1)局部红肿者 HYPERLINK "http://baike.baidu.com/view/1640887.htm" \t "_blank" 紫草茸油涂擦，或紫色消肿膏薄敷。 
+ (2)溃烂初期，创面表浅者，外用化毒散软膏或紫色消肿膏。 
+ (3)形成创面者，应用中医化腐生肌法： 
+ ①疮面有坏死者(腐肉)炎症仍有扩散，坏死组织与健皮分界不清时宜用紫色疽疮膏、化毒散软膏各等量，混匀外敷。 
+ ②坏死组织(腐肉)已深达肌肉，或更深而形成窦道时，宜用红血药捻，蘸紫色疽疮膏插入疮口内，外用化毒散软膏加盖。 
+ ③坏死组织与正常皮肤分界清楚而且开始脱落时，宜用 HYPERLINK "http://baike.baidu.com/view/3315432.htm" \t "_blank" 紫色疽疮膏、化毒散软膏、甘乳膏各等量，混匀外敷。 
+ ④坏死组织已脱落，疮面新生肉芽开始生长时，宜用甘乳膏80g、紫色疽疮膏20g，混匀外敷。 
+ ⑤新生肉芽生长良好，疮面边缘已有上皮生长时，宜用珍珠散薄撒疮面，再用甘乳膏制成油纱条覆盖。 
+ ⑥用药期间，疮面周围出现湿疹样变化时可用祛湿散，甘草油调敷。 
+ 3、老药新用治疗 
+ （1） HYPERLINK "http://baike.baidu.com/view/7281.htm" \t "_blank" 云南白药治疗褥疮：Ⅰ度褥疮，可将云南白药粉溶于75％酒精中调成稀糊状，用棉签蘸取糊状药液，涂抹患处，每天3～4次。Ⅱ或Ⅲ度褥疮，按无菌操作法，抽出皮肤水疱中的渗出液，或清理创面后敷云南白药，无菌纱布覆盖，隔日换药1次。此法治疗Ⅰ、Ⅱ、Ⅲ度褥疮的总有效率为100％。 
+ （2） HYPERLINK "http://baike.baidu.com/view/337716.htm" \t "_blank" 碘酊预防褥疮易发生褥疮的部位，用2％碘酊外涂，一日3次，连续3天，使表皮形成一层较厚的保护层，以增加皮肤的抵抗力，对预防褥疮的发生有良好的效果。 
+ （3）皮康霜治疗多发性褥疮：Ⅰ度褥疮的红斑处用皮康霜外搽，一日3次。Ⅱ度褥疮的水疱处，在无菌条件下，抽去疱液，用1∶1000的雷夫奴尔溶液湿敷，一日3次，待结痂后再搽皮康霜，一日3次。Ⅲ度糜烂溃疡的褥疮，先用1∶1000的雷夫奴尔溶液湿敷，一日3次，结痂后再搽皮康霜，一日3次。Ⅰ度褥疮1～2天可治愈，水疱和溃疡处5～7天可痊愈。 
+ （4）消炎止血散治褥疮：取消炎止血散2～5克，去腐生肌散2克，云南白药1.5克，3药混匀装瓶备用。先用生理盐水冲洗清创，然后将混合的消炎止血散撒布患处包扎，每日1次。 
+ （5）胰岛素与庆大霉素治疗深部褥疮先常规消毒创面皮肤，并用生理盐水清洗创面，再用红外线灯照烤创面20分钟（距离10cm左右以使病人能耐受）。胰岛素8单位加庆大霉素8万单位，放在无菌纱布上敷于创面，外敷生理盐水湿纱布，最后用干纱布覆盖，一日1次。用药后4～12天炎症反应逐渐减轻，表面渗出减少，肉芽组织明显增生，12～14天褥疮可愈合。 
+ (6)成纤维生长因子：将褥疮局部消毒，清洗后用 2 %的成纤维生长因子软膏均匀覆盖创面，用消毒敷料包扎，每日换药 1次。能促进创伤愈合过程中所有细胞增生，加快创口的愈合速度 
+ （7）多抗甲素 它能刺激机体的免疫细胞增强免疫功能，促进创面组织修复。对创面较大者，先用生理盐水清创，然后用红外线灯照射20分钟，创面干燥后用多抗甲素液湿敷，再用红外线灯照射10分钟，最后用灭菌紫草油纱布覆盖，对渗出液多者，每日换药3次。 
+ （8）灭滴灵 对杀灭厌氧菌有特效，并能扩张血管，增强血液循环。用此药冲洗后，湿敷创面，加红外线灯照射20分钟，每日3－4次。 
+ （9)传统中药药膏 对于III和IV期褥疮，传统中药药膏的应用十分重要。中药膏一般可起到活血化瘀，去腐生肌的作用。例如：近远堂褥疮散、一枝堂褥疮护理膏、普济褥疮膏等，可以先用生理盐水清洁创面，去除坏死组织，再采用中药膏外贴进行治疗，临床上获得了较好的效果。 
+ HYPERLINK "http://baike.baidu.com/view/323311.htm" 编辑本段验方治疗
+ 一、十一方酒 
+ 1、药物组成： 田七 血竭 琥珀 生大黄 桃仁 红花 泽兰 归尾 乳香 川断 骨碎补 土鳖 杜仲 制马 钱子 苏木 秦艽 自然铜 没药 七叶一枝花 无名异 
+ 2、功能主治：活血化瘀、消肿止痛、收敛防腐生肌。 
+ 3、用法用量：外用：药酒纱布填塞伤口，每日滴药酒一次。也可内服。当发现皮肤潮红时，将十一方酒l0ml倒人手中用手掌按摩患处，每日二三次，局部有水疱形成者，用无菌注射器抽吸水疱内液后再涂擦十一方酒，每日二三次。如皮肤有溃疡、渗液，应立即用十一方酒纱布湿敷，每日三四次。 
+ 4、制备方法：上药各适量放人米三花酒7500ml，浸泡三至六个月后备用。 
+ 二、复方红花酒 
+ 1、药物组成：红花50g 黄芪30g 白蔹20g 75%乙醇(酒精)500ml 
+ 2、功能主治：褥疮，扭伤血肿，皮肤灼伤等。 
+ 3、药物组成：干红花30g 70%的乙醇(酒精)100ml 
+ 4、功能主治：活血化瘀，消结止痛。主治：①因注射而致局部硬结肿块。②外伤肿痛。③褥疮形成。 
+ 5、用法用量：用纱布或脱脂棉蘸30%的红花消结酒，局部涂擦患部，日二三次，每次5分钟。 
+ 6、制备方法：每lOOml70%的 HYPERLINK "http://baike.baidu.com/view/3010.htm" \t "_blank" 乙醇(酒精)中，放人干红花驸s，浸泡密封一星期，滤去药渣，即可使用。 
+ 按：药酒密封浸泡时间越长效果越佳。 
+ 三、芎参花酒 
+ 1、药物组成：川芎10g 丹参10g 红花10g 
+ 2、功能主治：祛瘀活血、行气通络。主治褥疮。 
+ 3、用法用量：预防褥疮组：在骨骼隆起受压处，每2-4小时翻身涂擦药液一次，3-5分钟后用滑石粉外敷。治疗褥疮组：早期(即淤血红润期)每日涂擦药液四至六次。对水疱或者局部皮肤已溃烂(即褥疮期)，在其周围每日涂擦药液六至八次，保持疮面清洁，同时用棉圈保护疮面，防止局部再次受压。 
+ 4、制备方法：上药共研末置50%乙醇(酒精)500ml中密羽浸泡一个月以上，滤出药液备用。 
+ 四、 红当酒 
+ 1、药物组成：红花30g 当归尾30g 
+ 2、功能主治： 活血祛瘀，通络止痛，消散瘀肿。主治褥疮。 
+ 3、用法用量：用红花酒少许涂于受压部位，用大小鱼际肌在受压部位由轻至重环形按摩3-5分钟，再用滑石粉或爽身粉，每日4-6次。 
+ 4、制备方法：上两药浸人50%乙醇(酒精)1000ml中，浸泡一个月滤取清液备用。
+预防
+ 1、充分认识褥疮的好发部位和外在因素、内在因素褥疮一般多在受压和缺乏脂肪组织保护，无肌肉包裹或肌层较薄的骨骼隆突处出现，好发于肩胛部、肋骨、脊椎体隆突处，肘关节、髂嵴、股骨大转子，骶尾部、膝关节，内外踝部，足跟等部位，俯卧时还可发生于髂前上棘、膝关节、肋沿突出处。皮肤潮湿、摩擦、烫伤、冻伤、擦伤为易引发褥疮的外在因素；截瘫丧失知觉、年老体弱、身体消瘦、 HYPERLINK "http://baike.baidu.com/view/88997.htm" \t "_blank" 贫血、 HYPERLINK "http://baike.baidu.com/view/249560.htm" \t "_blank" 营养不良、蛋白质缺乏、大小便失禁、发热、 HYPERLINK "http://baike.baidu.com/view/923.htm" \t "_blank" 糖尿病、感染为易引发褥疮的内在因素。 2、掌握皮肤颜色、质地（软硬），观察温度，皮肤变红：即皮肤变红的部位压之褪色；皮肤发绀：即皮肤发绀（紫）的部位，压之不褪色；皮肤水泡：即皮肤呈水泡的部位，说明表浅层组织下的坏死。轻轻触摸皮肤可感受到皮肤的温度和质地。体温每升高1℃，组织代谢的氧需要量增加13%，持续压力引起组织缺血时，温度升高将增加褥疮的易发性。 
+ 3、勤翻身：实施有效到位的翻身来间歇性地解除局部压迫，是预防褥疮最为有效、关键的措施。一般卧床病人每1—2小时翻身一次，发现皮肤变红，则应每小时翻身一次，左、右侧卧、平卧、俯卧位交替进行，并用软枕、气枕、 HYPERLINK "http://baike.baidu.com/view/1160922.htm" \t "_blank" 水枕、气垫圈、海绵圈等垫在骨突出部位，可起到局部悬空、减轻压力作用。坐轮椅的病人可在足底放一个海绵垫，臀下软枕（垫）或海绵垫，每15—20分钟变换重心1次，应阻止病人长时间坐轮椅（2小时以上），在可能的情况下，让病人站立，行走10分钟。 
+ 4、正确实施按摩：平卧时，将手放入臀下，掌心向下向上均可。充分感受皮肤温度和受压力情况，并上按摩皮肤5分钟，每20分钟重复一次。左、右侧卧时，侧身要侧到位，半平半侧（斜侧）应用软枕支撑腰背部，对皮肤颜色、温度、质地正常的受压部位可用50%红花酒精倒入掌心，两侧由轻→重→轻按摩5—10分钟；发现皮肤变红，则不宜进行皮肤按摩，可悬空压红部位，一般解除压力30—40分钟后皮肤颜色可恢复正常。皮肤持续发红、发绀、更不宜 HYPERLINK "http://baike.baidu.com/view/19116.htm" \t "_blank" 按摩、以免加重损伤。 
+ 5、床褥、床单的要求：卧床病人的床褥要透气，软硬适中、吸水性好，可用气垫床（卵窝形为佳）、高密度海绵床垫，床单应为纯棉，另外在床单上可铺一条纯棉浴巾，便于更换。床单保持平整、干燥、清洁、无皱折、无渣屑、无杂物；气垫床充气软硬要适度，过度充气反而可使皮肤受压增加。为病人更换床单时应防止拖、拉、拽，以防损坏皮肤。 
+ 6、保持皮肤清洁干燥完整：预防褥疮的方法多种多样，我们通常使用的方法是温水擦浴每天1—2次，擦洗时不可用刺激性强的清洁剂，不可用力擦拭，以防损伤皮肤。对易出汗的腋窝、腹肌沟部位，可用小毛巾随时擦拭。为防止皮肤损伤可在局部扑“强生” HYPERLINK "http://baike.baidu.com/view/153199.htm" \t "_blank" 婴儿护臀粉或痱子粉。大便失禁者，及时洗净肛周皮肤，涂上强生婴儿护臀粉或护臀霜，即可有效防治肛周和会阴縻烂、 HYPERLINK "http://baike.baidu.com/view/1001.htm" \t "_blank" 湿疹； HYPERLINK "http://baike.baidu.com/view/690230.htm" \t "_blank" 小便失禁者可使用bt型高颈透气接尿器；应用热水袋热敷，水温应在50℃，并用毛巾包好，热敷时间30分钟，应经常观察热敷部位皮肤情况，不能长时间在一个部位热敷，以防烫伤。用冰袋降温时，冰袋应放在颈部两侧、 HYPERLINK "http://baike.baidu.com/view/1273753.htm" \t "_blank" 腋窝、腹股沟处。冰敷时间以10—30分钟为宜，放置时间不可过长，以防冻伤。 
+ 7、加强营养： ①给予 HYPERLINK "http://baike.baidu.com/view/117029.htm" \t "_blank" 高蛋白、 HYPERLINK "http://baike.baidu.com/view/1062540.htm" \t "_blank" 豆类。②多食用植物油，如 HYPERLINK "http://baike.baidu.com/view/47086.htm" \t "_blank" 花生油、 HYPERLINK "http://baike.baidu.com/view/47093.htm" \t "_blank" 芝麻油、 HYPERLINK "http://baike.baidu.com/view/168061.htm" \t "_blank" 豆油、 HYPERLINK "http://baike.baidu.com/view/47090.htm" \t "_blank" 菜籽油等，有润肠功效，利于缓解便秘。 ③选用富含植物纤维的食物，如粗粮、蔬菜、水果、豆类等。④食用富含维生素b1的食物，如粗粮、豆类、瘦肉、动物内脏、新鲜 HYPERLINK "http://baike.baidu.com/view/13544.htm" \t "_blank" 蔬菜等。 ⑤多食果汁、新鲜水果、果酱、蜂蜜等刺激肠蠕动。 ⑥多喝水、饮料，以免大便干燥。 ⑦必要时少食多餐，以利消化吸收。 ⑧凡伴有消化不良、肠炎、腹泻、便秘的病人，宜多食用酸奶。 
+ 8、早发现，早治疗：褥疮早期皮肤发红，采取翻身、减压等措施后可好转。当皮肤出现浅表溃烂、溃疡、渗出液多时就应及时到医院接受治疗。 
+ 9、在治疗方面议建大家可以用由陕西强生药业生产的“冰石愈伤软膏”具有独特的杀菌、祛腐生肌、解毒收敛、消炎止痛等作用。治疗褥疮疗程短、见效快，涂抹后立即止痛，有消炎祛腐生肌的功能，是目前国内治疗创伤及烧烫伤等病症感染的首选药物。 
+ HYPERLINK "http://baike.baidu.com/view/323311.htm" 编辑本段护理要点
+ 1、初期局部皮肤红肿时，用45%酒精倒于手心做局部按摩10分钟、再擦 HYPERLINK "http://baike.baidu.com/view/49064.htm" \t "_blank" 滑石粉，每天数次；若皮色变紫，有水泡形成或表皮破损时，用1%龙胆紫涂擦表面，保持局部干燥，避免患处再受压。 
+ 2、水疱破损，局部感染有浅层坏死时，可用浓度为1：5000的高猛酸钾溶液冲洗，擦干创面及周围皮肤后，用60瓦电灯在距创面30厘米处烘烤，使其干燥愈合，处理后创面可用凡士林油纱布复盖。 
+ 3、患者床垫要柔软，床单平整，洁净并勤更换；每2小时给患者翻身一次，避免拖拉；对经常受压部位勤按摩，也可在受压部垫海绵垫，气圈或软枕等以减轻压力。 
+ 4、保持皮肤清洁干燥，防止尿液，粪便污染皮肤或疮面。 
+ 5、居室应空气新鲜、阳光充足，注意保暖，防止上呼吸道感染而致发热，因高热可使褥疮迅速扩大或愈后复发。 
+ HYPERLINK "http://baike.baidu.com/view/323311.htm" 编辑本段预防
+ 一、床铺要松软平整，尽可能地经常改换卧床患者的体位，帮助患者翻身，一般每２～３小时翻身一次，必要时每１小时翻身一次，最长不超过４小时。翻身动作要轻柔，避免推、拖、拉等，以防止擦伤皮肤。 
+ 二、经常检查患者骨骼突出处以及受压部位，定期按摩全背或受压处，按摩时自上而下，压力由轻到重，再由重到轻，切勿擦伤皮肤。受压局部要垫气圈、棉圈、海绵垫等。 
+ 三、大小便失禁的患者要及时更换其尿垫，注意保持皮肤和被褥的干燥、清洁。 
+ 四、对使用夹板或者其他矫形器械的患者，应加上松软的衬垫，观察患者的反应，随时调节夹板或器械松紧。 
+ 五、卧床患者不可使用掉瓷的便盆。使用便盆时应协助病人抬高臀部，防止局部皮肤擦伤，同时臀部与便器间应垫软纸、海绵或海绵垫。 
+ 六、鼓励病人进食，保证充足的营养。饮食要有足够的蛋白质、维生素和热量，并选择容易消化的食物。注意每日摄入适量的水果和蔬菜。 
+ 七、平时注意多活动身体。有活动能力的老人，不要睡卧过多；不能单独行动者，应在他人帮助下适度活动；因病卧床者，一旦病情许可，应尽早离床。 
+ 八、要经常用温水洗浴、擦背，保持患者皮肤清洁，促进血液循环。 
+ HYPERLINK "http://baike.baidu.com/view/323311.htm" 编辑本段健康饮食
+ ①给予高蛋白食品 
+ ②多食用植物油，如花生油、芝麻油、豆油、菜籽油等，有润肠功效，利于缓解便秘。 
+ ③选用富含植物纤维的食物，如粗粮、蔬菜、水果、豆类等。 
+ ④食用富含维生素b1的食物，如粗粮、豆类、瘦肉、动物内脏、新鲜蔬菜等。 
+ ⑤多食果汁、新鲜水果、果酱、蜂蜜等刺激肠蠕动。 
+ ⑥多喝水、饮料，以免大便干燥。 
+ ⑦必要时少食多餐，以利消化吸收。 
+ ⑧凡伴有消化不良、肠炎、腹泻、便秘的病人，宜多食用酸奶。
+PAGE 
+PAGE 6</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>FUGL-MEYER</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>平衡功能评定（Fugl-Meyer)</t>
+          <t>吞咽功能评定量表汇总</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>对于吞咽困难的评估，有9个评价量表，具体介绍如下： + +量表1：吞咽困难评价标准。来自日本康复学界，分为0～10分，分数越高表示吞咽困难的程度越低，10分表示正常吞咽。该量表包含康复训练方法的选择，以营养摄取为线索反应经口进食的能力，分级较细。 +分数 评价内容 +1 不适合任何吞咽训练，仍不能经口进食 +2 仅适合基础吞咽训练，仍不能经口进食 +3 可进行摄食训练，但仍不能经口进食 +4 在安慰中可能少量进食，但需静脉营养 +5 1～2种食物经口进食，需部分静脉营养 +6 3种食物可经口进食，需部分静脉营养 +7 3种食物可经口进食，不需静脉营养 +8 除特别难咽的食物外，均可经口进食 +9 可经口进食，但需临床观察指导 +10 正常摄食吞咽能力 +疗效判定标准： +大于等于9分：基本痊愈； +提高 6～8分：明显好转； +提高 3～5分：好转； +1～2分：无效。 + +量表2：洼田饮水试验。日本学者洼田俊夫提出的，分级明确清楚，操作简单，利于选择有治疗适应症的患者。但是该检查根据患者主观感觉，与临床和实验室检查结果不一致的很多，并要求患者意识清楚并能够按照指令完成试验。 +患者端坐，喝下30毫升温开水，观察所需时间喝呛咳情况。 +1级（优）能顺利地1次将水咽下 +2级（良）分2次以上，能不呛咳地咽下 +3级（中）能1次咽下，但有呛咳 +4级（可）分2次以上咽下，但有呛咳 +5级（差）频繁呛咳，不能全部咽下 +正常：1级，5秒之内；可疑：1级，5秒以上或2级；异常：3～5级 +疗效判断标准： +治愈：吞咽障碍消失，饮水试验评定1级 +有效：吞咽障碍明显改善，饮水试验评定2级 +无效：吞咽障碍改善不显著，饮水试验评定3级以上 + +量表3：洼田吞咽能力评定法。该表提出3种能减少误吸的条件，根据患者需要条件的多少及种类逐步分级，分为1～6及，级别越高吞咽障碍越轻，6级为正常。 +评定条件：帮助的人，食物种类，进食方法和时间。 +1级：任何条件下均有吞咽困难和不能吞咽； +2级：3个条件均具备则误吸减少； +3级：具备2个条件则误吸减少； +4级：如选择适当食物，则基本上无误吸； +5级：如注意进食方法和时间基本上无误吸； +6级：吞咽正常。 +疗效判定标准： +无效：治疗前后无变化； +有效：吞咽障碍明显改善，吞咽分级提高1级； +显效：吞咽障碍缓解2级，或接近正常。 + +量表4：吞咽障碍程度分级。分为正常，轻，中，重4个层面，从严重吞咽困难到正常吞咽功能共10级。该量表以所能吞咽食物的种类及营养摄取途径为线索，分级与量表1非常接近，因此从表面看二者的相关性应该最好。 +重度（不能经口进食） +1级 吞咽困难或不能吞咽，不适合做吞咽训练 +2级 大量误吸，吞咽困难或不能吞咽，适合做吞咽基础训练 +3级 如做好准备可减少误吸，可进行进食训练 +中度（经口及辅助营养） +4级 作为兴趣进食可以，但营养摄取仍需非口途径 +5级 仅1～2顿的营养摄取可经口 +6级 3顿的营养摄取均可经口，但需补充辅助营养 +轻度（可经口营养） +7级 如为能吞咽的食物，3顿均可经口摄取 +8级 除少数难吞咽的食物，3顿均可经口摄取 +9级 可吞咽普通食物但需给予指导 +正常： +10级 进食，吞咽能力正常 +疗效判定标准： +无效：治疗前后无变化； +有效：吞咽障碍明显改善，吞咽分级提高1级； +显效：吞咽障碍缓解2级，或接近正常。 + +量表5：吞咽功能障碍评价标准。仍然是日本的洼田提出的，注重于吞咽肌的临床评定，以肌力减弱的程度分为4肌，1肌为正常肌力。 +舌肌： +1级：可紧抵上腭及左右牙龈 +2级：可紧抵上腭但不能抵左右牙龈 +3级：可上抬但不能达上腭 +4级：不能上抬 +咀嚼肌及颊肌： +1级：可左右充分偏口角，鼓气叩颊不漏气，上下牙齿咬合有力 +2级：鼓气叩颊漏气，上下牙齿咬合一侧有力一侧力弱 +3级：鼓气扣不紧，有咬合动作，但力弱 +4级：鼓气完全不能，咬合动作不能 +咽喉肌： +1级：双软腭上举有力 +2级：一侧软腭上举有力 +3级：软腭上举无力 +4级：软腭不能上举 +疗效评价标准： +完全恢复：吞咽功能达到1级； +基本恢复：由3级或4级提高到2级； +有效：由4级提高到3级 + +量表6：为吞咽功能的分级，评定难度最小。 +1级：完全胃管进食 +2级：口腔与胃管混合进食 +3级：完全口腔进食，但需辅以代偿合适应等方法 +4级：完全口腔进食，无需代偿适应等方法 +疗效标准： +无效：治疗前后无变化， +有效：吞咽障碍明显改善，吞咽分级提高1级； +显效：吞咽障碍缓解2级，或接近正常。 + +量表7：吞咽功能分级标准。是日本学者才藤结合康复锻炼方法制定的，该量表将症状和康复治疗的手段相结合，对临床指导价值较大。不需要复杂的检查手段，一定程度上简化了评价方法。 +7级：正常范围：摄食咽下没有困难，没有康复医学治疗的必要； +6级：轻度问题：摄食咽下有轻度问题，摄食时有必要改变食物的形态，如因咀嚼不充分需要吃软食，但是口腔残留的很少，不误咽； +5级：口腔问题：主要是吞咽口腔期的中度或重度障碍，需要改善咀嚼的形态，吃饭的时间延长，口腔内残留食物增多，摄食吞咽时需要他人的提示或者监视，没有误咽。这种程度是吞咽训练的适应症； +4级：机会误咽：用一般的方法摄食吞咽有误咽，但经过调整姿势或一口量的调整和咽下代偿后可充分防止误咽。包括咽下造影没有误咽，仅有多量的咽部残留，水和营养的主要经口摄取，有时吃饭需要选择调整食物，有时需要间歇性的补给静脉营养，如果用这种方法可以保持患者的营养供给就需要积极地进行咽下训练。 +3级：水的误咽：有水的误咽，使用误咽防止法也不能控制，改变食物形态有一定的效果，吃饭只能吃咽下食物，但摄取的能量不充分。多数情况下需要静脉营养，全身长期的营养管理需要考虑胃造瘘，如果能采取适当的摄食咽下方法，同样可以保证水分和营养的供应，还有可能进行直接咽下训练。 +2级：食物误咽：有误咽，改变食物的形态没有效果，水和营养基本上由静脉供给，长期管理应积极进行胃造瘘，因单纯的静脉营养就可以保证患者的生命稳定性，这种情况尽管间接训练不管什么时间都可以进行，直接训练要在专门设施进行。 +1级：唾液误咽：连唾液都产生误咽，有必要进行持续的静脉营养，由于误咽难以保证患者的生命稳定性，并发症的发生率很高，不能试行直接训练。 +疗效判定标准： +无效：治疗后无得分增加； +有效：治疗后得分增加1级。
+量表8：脑卒中患者神经功能缺损程度评分标准中的吞咽困难亚量表。分为5个评分级别，0分为正常。 +0分：没有异常； +2分：有一定困难，吃饭或喝水缓慢，喝水时停顿比通常次数多； +4分：进食明显缓慢，避免一些食物或流食； +5分：仅能吞咽一种特殊的饮食，如单一的或绞碎的食物； +6分：不能吞咽，必须用鼻饲管。 +疗效判定标准： +无效：治疗后无得分增加； +有效：治疗后得分增加1级。 + +量表9：医疗床旁评估量表。是南曼彻斯特大学医学院语言治疗科的Smithard DG及Wyatt R编写的。 +意识水平 +清醒＝1，嗜睡但能唤醒＝2，有反应但无睁眼和言语＝3，对疼痛有反应＝4 +头与躯干的控制 +正常坐稳＝1，不能坐稳＝2，只能控制头部＝3，头部也不能控制＝4 +呼吸模式 +正常＝1，异常＝2 +唇的闭合 +正常＝1，异常＝2 +软腭运动 +对称＝1，不对称＝2，减弱或缺乏＝3 +喉功能 +正常＝1，减弱＝2，缺乏＝3 +咽反射 +存在＝1，缺乏＝2 +自主咳嗽 +正常＝1，减弱＝2，缺乏＝3 +第1阶段:给予1汤匙水（5毫升）3次 +水流出 +无或一次＝1，大于一次＝2 +有无效喉运动 +有＝1，无＝2重复吞咽 +无或一次＝1，一次以上＝2 +吞咽时咳嗽 +无或一次＝1，一次以上＝2 +吞咽时喘鸣 +无＝1，有＝2 +吞咽后喉的功能 +正常＝1，减弱或声音嘶哑＝2，发音不能＝3 +第2阶段：如果第1阶段正常（重复3次，2次以上正常），那么给予吞咽60毫升烧杯中的水 +能否完成？ +能＝1，不能＝2 +饮完需要的时间 秒 +吞咽中或完毕喉咳嗽 +无＝1，有＝2 +吞咽时或完毕喉喘鸣 +无＝1，有＝2 +吞咽后喉的功能 +正常＝1，减弱或声音嘶哑＝2，发音不能＝3 +误吸是否存在 +无＝1，可能＝2，有＝3 +如果患者不能正常吞咽5毫升的水，即尝试3次中多于1次出现咳嗽或者气哽，或者出现吞咽后声音嘶哑（即喉功能减弱），则不再继续第2阶段。不能进入第2阶段，在第2 阶段中出现咳嗽或气哽，或出现吞咽后声音嘶哑，就认为是不安全吞咽。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>康复科吞咽障碍评价表</t>
+          <t>失用症检查</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+失用症检查
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+动作完成3近似或模仿2仿似或实物1失败0
+备注
+动作完成3近似或模仿2仿似或实物1失败0备注握拳敬礼挥手再见抓头捻手指伸舌闭眼吹哨闻花吹熄火柴用梳子梳头用牙刷刷牙用汤匙喝汤用锤子钉钉子用钥匙开锁假装驾驶汽车假装敲门和开门假装折纸假装点烟假装弹钢琴
+意念运动性失用
+结构性失用
+穿衣失用
+评定时让患者给玩具娃娃穿衣，如不能则为阳性。让患者给自已穿衣、系扣、系鞋带，如对衣服的正、反、左、右不分；手穿不进袖子，系扣、系带困难者为阳性，不能在合理时间内完成上述指令者亦为阳性。
+口颜面失用检查
+1、鼓腮
+4、缩拢嘴唇
+ 正常 
+ 正常 
+ 摸索 
+ 摸索 
+2、吹气
+5、摆舌
+ 正常 
+ 正常 
+ 摸索 
+ 摸索 
+3、咂唇
+6、吹口哨
+ 正常 
+ 正常 
+ 摸索 
+ 摸索 
+言语失用检查
+元音顺序（1、2、3、要说五遍）
+1、 （a—u—i）
+3、词序（复述爸爸、妈妈、弟弟）
+ 正常顺序 
+ 正常顺序 
+ 元音错误 
+ 词音错误 
+ 摸 索 
+ 摸 索 
+2、 （i—u—a）
+4、词复述（啪嗒、洗手、你们打球、不吐葡萄皮）
+ 正常顺序 
+ 正常顺序 
+ 元音错误 
+ 词音错误 
+ 摸 索 
+ 摸 索 
+PAGE 
+PAGE 1
+4.5分
+3分
+1.5分
+示范</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>康复科肢体周径、肌力量表</t>
+          <t>平衡功能评定（Berg）</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>评定系列表
+Berg平衡量表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 
+检查内容
+年 月 日
+年 月 日
+1.由坐位到站位
+指导：起立。尝试不用手支撑
+评分：选出分类的最低分数
+（4）能够站立，无需用手可维持平衡
+（3）能够站立，用手可以维持平衡
+（2）能够站立，用手可以维持平衡，但要尝试数次
+（1）站立或维持稳定需要少量的辅助
+（0）站立需要中等到很多的辅助
+2.无扶持站立
+指导：无扶持站立2min
+评分：选出分类的最低分数
+（4）能够站立2min
+（3）能够站立2min,需要监护
+（2）能够站立30s,不需扶持
+（1）能够站立30s,不需扶持，需要几次尝试
+（0）无辅助，不能站立30s
+如果受试者可安全站立2min，本项满分，直接进入站位到坐位
+3.无扶持坐位，双脚落地
+指导：双臂抱于胸前坐位2min
+评分：选出分类的最低分数
+（4）能够坐2min
+（3）能够坐2min,监护下
+（2）能够坐30s
+（1）能够坐10s
+（0）能够坐10s,需扶持
+4.由站位到坐位
+指导：坐下
+评分：选出分类的最低分数
+（4）维持平稳坐位，基本不用手扶持
+（3）需用手控制下滑
+（2）用腿的背侧抵住椅子以控制下滑
+（1）可独立坐位但不能控制下滑
+（0）坐位需要辅助
+5.位置移动
+指导：从椅子移动到床上，再从床上移动到椅子上，可用手或不用手
+评分：选出分类的最低分数
+（4）位置移动较少用手
+（3）位置移动必须用手
+（2）位置移动需言语提示或监护
+（1）需要1人辅助
+（0）需要2人监护或辅助
+6.无扶持站立，闭眼
+指导：闭眼，无扶持静立10s
+评分：选出分类的最低分数
+（4）能够站立10s
+（3）能够站立10s,监护下
+（2）能够站立3s
+（1）闭眼不能坚持3s,但可站稳
+（0）需帮助防止跌倒
+7.双足并拢站立不需扶持
+指导：双足并拢站立不需扶持
+评分：选出分类的最低分数
+（4）可双足并拢站立1min
+（3）双足并拢站立1min,需监护
+（2）双足并拢站立不能坚持30s
+（1）到站位需要帮助，但双足并拢可站立15s
+（0）到站位需要帮助，但双足并拢站立不足15s
+在无扶持站立时完成以下项目
+8.手臂前伸
+指导：手臂上举90度，尽可能伸手取远处的物品。（检查者将直尺置于指尖处，臂前伸时勿触及直尺。测量身体尽量前伸时的距离）
+评分：选出分类的最低分数
+（4）可前伸10cm
+（3）可前伸5cm
+（2）可前伸超过2cm
+（1）前伸，需要监护
+（0）需帮助避免跌倒
+9.自地面拾物
+指导：拾起足前的鞋子
+评分：选出分类的最低分数
+（4）可轻松拾起
+（3）可拾起，需要监护
+（2）不能拾起，差2.54-5.08cm(1-2英寸).可保持平衡
+（1）不能拾起，尝试时需监护
+（0）不能尝试/需要辅助避免跌倒
+10.躯干不动，转头左右后顾
+指导：交替转头，左右后顾
+评分：选出分类的最低分数
+（4）左右后顾时重心移动平稳
+（3）只能一侧后顾，另一侧有少量重心移动
+（2）只能转到侧面，但可维持平衡
+（1）转头时需要监护
+（0）需要辅助避免跌倒
+11.转身360度
+指导：转身360度，停顿，反向旋转360度
+评分：选出分类的最低分数
+（4）双侧都可在4s内完成
+（3）一侧可在4s内完成
+（2）能完成转身，但速度慢
+（1）转身时需密切监护或言语提示
+（0）转身时需要辅助
+无扶持站立时动态移动重心
+12.计数脚底接触板凳的次数
+指导：每只脚交替放于板凳上，直到每只脚能踏上板凳上4次
+评分：选出分类的最低分数
+（4）可独自站立，20s内踏8次
+（3）可独自站立，踏8次超过20s
+（2）监护下，无辅助可踏4次
+（1）最简单的辅助可踏2次
+（0）需要辅助才能避免跌倒，不能尝试踏凳
+13.无扶持站立，一只脚在前
+指导：双脚前后位站立，如果困难，增加双足前后距离
+评分：选出分类的最低分数
+（4）双足可前后接触位站立30s
+（3）双足前后站立不能接触站立30s
+（2）可迈小步后独立坚持30s
+（1）迈步需要帮助，坚持15s
+（0）站立或迈步失衡
+14.单腿站立
+指导：不需扶物，单腿站立
+评分：选出分类的最低分数
+（4）可抬腿，坚持超过10s
+（3）可抬腿5-10s
+（2）可抬腿超过3s
+（1）尝试抬腿，不能坚持3s,但可独自站立
+（0）不能尝试/需要辅助避免跌倒
+总分 
+36分及36分以下提示有100%的跌倒危险。
+PAGE 
+PAGE 1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>FUGL-MEYER</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>改良波士顿失语症评定</t>
+          <t>平衡功能评定（Fugl-Meyer)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>评定系列表
+Fugl-Meyer平衡功能评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+测试项目
+评 分 标 准
+得 分
+Ⅰ无支撑坐位
+0分：不能保持坐位
+1分：能坐，但少于5min
+2分：能坚持坐5min
+Ⅱ健侧“展翅”反应
+0分：肩部无外展或肘关节无伸展
+1分：反应减弱
+2分：反应正常
+Ⅲ患侧“展翅”反应
+0分：肩部无外展或肘关节无伸展
+1分：反应减弱
+2分：反应正常
+Ⅳ支撑站位
+0分：不能站立
+1分：在他人的最大支撑下可站立
+2分：由他人稍给支撑即能站立1min
+Ⅴ无支撑站立
+0分：不能站立
+1分：不能站立1min或身体摇晃
+2分：能平衡站立1min以上
+Ⅵ健侧站立
+0分:不能维持1~2s
+1分:平衡站稳达4~9s
+2分:平衡站立超过10s
+Ⅶ患侧站立
+0分:不能维持1~2s
+1分:平衡站稳达4~9s
+2分:平衡站立超过10s
+总分</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>ADL</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>日常生活活动能力评定（ADL）</t>
+          <t>康复科吞咽障碍评价表</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>吞咽障碍评价表
+姓名： 性别： 年龄： 岁 科别： 科 床号： 床 住院号： 
+诊断： 评定人： 
+检查日期
+月 日
+ 月 日 
+月 日
+月 日
+ 月 日
+30秒内吞咽次数
+进餐所需时间
+30Ml
+水
+试
+验
+1级
+2级
+3级
+4级
+5级
+备注：评价及训练时有误吸的危险存在，甚至引起窒息。
+如同意评价/治疗请患者/家属签名＿＿＿＿＿＿＿
+洼田饮水试验法：直坐位，30mI温水
+简况：1、可一次喝完，无呛咳 2、分两次喝完，无呛咳
+3、能一次喝完，但有呛咳 4、分两次以上喝，且有呛咳
+5、常常呛住，难以全部喝完
+诊断：简况1，5秒内，正常范围
+简况1，5秒以上；简况2，可疑
+简况3、4、5异常
+吞咽困难的临床评价
+病史
+药物
+症状
+呛咳频度
+何时发生： 吞咽前 吞咽中 吞咽后
+症状加重的原因： 流质 半流质 固体食物
+伴随症状：
+梗阻： 喉部 胸部食物堵塞感 疼痛
+鼻腔返流： 饮水 进食 肺炎
+口臭： 牙周病 口腔食物滞留 言语/嗓音
+误咽： 体质量下降 胃灼热（返流）
+饮食改变：
+意识状态 体质量 呕吐反射 病理反射
+面部肌肉 咳嗽 咀嚼肌 喉头运动
+口腔黏膜 舌 口腔保持 牙齿 流涎
+言语 间接喉镜 进食种类 何种帮助 语音
+喉功能 进食量 进食所用时间 
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>格拉斯哥昏迷量表</t>
+          <t>康复科肢体周径、肌力量表</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>肢 体 周 径、肌 力评 定 表
+肢 体 周 径 检 查 表
+姓名 男、女 年龄 床号 住院号 评价人签字：
+左
+右
+日期
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+上臂鹰嘴突上10cm
+前臂鹰嘴突下5cm
+大腿髌上15cm
+小腿髌下10cm
+徒 手 肌 力 检 查 表
+左
+右
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+年 月 日
+三角肌
+肱二头肌
+肱三头肌
+腹肌
+臀中肌
+臀大肌
+股二头肌
+髂腰肌
+股四头肌
+胫前肌
+腓肠肌
+注：0级：不能触及肌肉收缩。Ⅰ级：可触及肌肉收缩，但不能引起关节活动。Ⅱ级：解除重力的影响下，可完成关节活动范围的运动。Ⅲ级：不施加阻力，能 抗重力完成关节活动范围。Ⅳ级：抗重力和中等阻力完成关节活动范围，Ⅴ级：能抗重力和最大阻力完成关节活动范围。
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>植物状态评分标准</t>
+          <t>改良波士顿失语症评定</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>河北省医院康复中心
+改良波士顿诊断性失语症检查记录
+姓名: 性别: 年龄: 科: 床号: 
+单位: 职业: 磁带号: 病历号: 
+文化程度(年): 出生地及成长地(18岁) 省 市(县),民族:
+利手:(右)写字(左),(右)拿筷(左),(右)掷东西(左),(右)刷牙(左),(右)剪刀(左)
+(右)划火柴(左),(右)穿针(左),(右)持钉锤(左),(右)握球拍(左),(右)洗脸(左)
+结论：右、左、混合
+语言背景：普通话、方言、英语、日语、法语、德语、俄语、西班牙语
+过去语言能力：流畅、迟缓、沙哑、口吃
+发病日期： 入院日期： 出院日期： 检查日期：
+现病史：
+既往史：脑A硬化 脑外伤 脑手术史 高血压 糖尿病 冠心病 高血脂症 其它
+神经系统检查：神志 合作：好、欠、不
+感觉系统：浅感觉 深感觉
+运动系统：肌力 不自主运动
+ 肌张力
+反射：肱二头肌反射 膝腱反射
+ 肱三头肌反射
+病理征：霍夫曼氏征 巴氏征 夏道克氏征
+ 戈登氏征 颈强直
+颅神经：视觉 眼球运动 面部感觉
+ 面瘫 舌运动 吞咽
+其它
+CT报告：
+其它检查：
+临床断诊：
+语言功能诊断：
+ 检查者：
+Ⅰ.对话
+A.与病人进行对话，提问题，尽可能激发病人作出多的反应，录音。询问病人有关情况如姓名、地址、工作单位、患病情况等。
+1.对问候作出回答（问：“你今天感觉如何？”或类似的问候）。
+2.用“是”或“不是”，“有”或“没有”作出回答（问：“你以前在这儿主过院吗？”或“我以前给你做过检查吗？”）。
+3.用“能”或“不能”作出回答（问：“你认为我能帮助你吗？”）
+4.用“知道”或“不知道”作出回答（问：“你知道你要在医院住多久吗？”）
+5.“你叫什么名字？”
+6.“你在什么单位工作？”
+7.“你住在哪儿？”
+8.对话
+ 检查者提出一些熟悉的话题，进行对话。如，“发病前你做什么工作？”，“你是怎么发病的？”鼓励病人进行至少10分钟的对话。
+B.图片叙述，时间1分钟（卡片）
+Ⅱ.听理解
+A.词辨别
+ 出示卡片2、3，由病人按听到的词或符号指出相应的卡片，如要求可重复一遍。
+卡2
+辨别
+＜5＂＞5＂
+词义 暗示 失败 范畴
+卡3
+辨别
+＜5＂＞5＂
+词义 暗示 失败 范畴
+物品
+2 1
+1/2 1/2 0
+动作
+2 1
+1/2 1/2 0
+椅子
+抽烟
+钥匙
+喝水
+手套
+跑步
+羽毛
+睡觉
+汽车
+摔到
+仙人掌
+滴水
+拼音
+颜色
+l
+兰色
+h
+黄色
+r
+红色
+t
+绿色
+s
+白色
+g
+黑色
+形状
+数字
+圆形
+7
+螺旋形
+42
+正方形
+700
+三角形
+1936
+圆锥形
+15
+五角星
+7000
+ 总分：
+B躯体部分辨认
+病人指出下列躯体部分，记录错误回答。
+躯体辨认 左右辨认
+正确
+＜5＂＞5＂失败
+正确
+＜5＂＞5＂失败
+正确 失败
+1 1/2 0
+1 1/2 0
+耳朵
+手腕
+右耳
+鼻子
+拇指
+左肩膀
+肩膀
+大腿
+左膝盖
+膝盖
+下巴
+右脚腕
+眼睫毛
+胳膊肘
+右手腕
+脚腕
+嘴唇
+左拇指
+胸
+眉毛
+右胳膊肘
+脖子
+脸
+左脸
+中指
+食指
+8项正确
+6、7项正确
+2分
+1分
+ 总分：
+C.执行指示
+病人执行下列指示，对下列划横线部分记分。要求时可重复一遍，但要求完整地重复。
+1.握拳
+2.指房顶，然后指地板。
+（按顺序将铅笔、手表、图片摆在桌上。）
+3.把铅笔放在图片的上面，然后再放回原来的地方。
+4.把手表放在铅笔的另一边，然后把图片翻过来。
+5.眼睛闭好，用两个手指拍打每个肩膀各两次。
+ 总分：
+D.复杂概念
+每对问题1分，共12分，要求时可重复一遍。
+1a.软木塞在水里能沉下去吗？
+2a.能用锤子砍柴吗？
+3a.2斤面粉比1斤面粉重吗？
+4a.水能透过新雨鞋吗？
+1b.石头在水里能沉下去吗？
+2b.能用锤子钉钉子吗？
+3b.1斤面粉比2斤面粉重吗？
+4b.新雨鞋防水吗？
+小王要到北京去，他打算坐火车去，他坐汽车到火车站，但在路上汽车轮胎破了，他还是及时到了火车站，赶上了火车。
+5a.小王误了火车吗？
+6a.小王是到北京去吗？
+5b.他赶上火车了吗？
+6b.他是在从北京回家的路上吗？
+一个战士到营房附近的邮局里去取邮包，但邮递员很严格又很客气地说：“对不起，请回去在包裹单上盖好公章后再来领取。”战士很丧气地说：“今天是星期天，我盖不上章。”
+7a.战士马上取了包裹了吗？
+8a.星期天他能盖上章吗？
+7b.邮递员不给他取包裹吗？
+8b.盖上公章能取包裹吗？
+一个旅客走进一家旅馆，一手拿着一卷绳子，一手拿着一个皮箱。旅馆服务员问到：“同志你拿绳子是干什么用的？”旅客回答说：“这是我的安全绳，以防发生火灾用。”服务员认真地说：“对不起，所有携带安全绳的旅客必须先付款。”
+9a.旅客每只手都各提一只箱子吗？
+10a.服务员对旅客有怀疑吗？
+9b.旅客一只手提着一卷绳子是吗？
+10b.服务员信任这个旅客吗？
+检查者先介绍说：“下面我念一段关于小狮子的文章。”
+幼狮生来就有根深蒂固的猎物天性。幼狮往往以急迫的心情互相追踪、攻击，小动物表现得极为惊恐。幼狮出生一年半后，这种嬉斗发展成为猎物和捕杀技巧。这种技巧来自长期的实践、模仿老狮子获得的。
+11a.这段文章告诉我们狮子是如何学习猎物了吗？
+12a.这段文章是说狮子一生下来就是熟练的捕杀能手是吗？
+11b.这段文章告诉我们如何抓捕狮子了吗？
+12b.这段文章是说狮子需要学习、实践，然后才会捕杀小动物是吗？
+ 总分：
+Ⅲ.言语表达
+言语器官的灵活性
+非言语的灵活性
+检查者示范，要求病人快速重复下列动作。记录在5秒内全部交替动作的次数。
+动 作
+5＂内动作的次数
+2分
+1分
+a.撅嘴—放松
+8
+4—7
+b.张—闭嘴
+10
+6—9
+c.缩回双唇—放松
+8
+4—7
+d.舌交替向嘴角移动
+8
+4—7
+e.舌前伸—后缩
+8
+4—7
+f.舔上下齿
+7
+3—6
+ 总分：
+言语的灵活性
+快速重复下列发音，记录5秒内重复的次数。可在开始时帮助病人发出语音。因重复言语或错语，病人在一、二项不能发音，删除该项，如二项以上不能记分，不记总分。用卡片4。
+5秒内词数2分
+1分
+a.妈妈
+9
+3—8
+b.梯田
+7
+3—6
+c.飞机
+7
+3—6
+d.山水
+5
+2—4
+e.汉口大道
+5
+2—4
+f.篮球运动员
+4
+2—3
+g.卡车拉货
+5
+2—4
+ 总分：
+ 正常：发音正确。
+ 发音笨拙：无改动的音素错误，但可察觉到发音笨拙。
+错音：至少一个音素可确定为音素错误，但仍可辨认出该词。
+失败：因发音困难，不能辨认出该字，但是在向正确发音努力。
+错语
+四声错语：每个音素均正确，但出现汉语的四声错误。
+新词症：字典上没有的词、该术语仅用来反映那些作为一个单位的词，发音较流畅。
+音素错语：音素漏掉，替代或是外来音。
+词语错语：词替代
+其它：
+Cl—累赘语。
+Irrl—无关言语，句法正常。
+P—持续言语。
+注：音节，实词的重复不记作错语，类似的、连续的咕噜或发出音节（不能分割成“字”）不记作错语。
+B.自动语序
+ 病人背诵下列语序，必要时检查者可念出第一个字，在提示的词上划圈，在遗漏的词划上×。
+发音 错语
+正常笨拙错音失败
+1分 2分四声新词音素语词其它周日 连续四个 全部 
+星期一，星期二，星期三，
+星期四，星期五，星期六，星期日四个季节
+春，夏，秋，冬 连续3个 全部数21
+1 2 3 4 5 6 7 8 9
+10 11 12 13 14 15 16 17 18 19
+20 21 连续8个 全部月份 
+一月，二月，三月，四月，五月，六月，七月，八月，九月，十月，十一月，十二月，连续5个全部 总分：
+C.背诵、歌唱、节律。
+ 如果病人失败了，或不熟悉这些韵律，可背诵其它记住的自动材料。
+背诵：《东方红》歌词，或熟悉的歌谣。
+唱歌（唱戏）
+节律：检查者在桌子上连续拍打下列节律（六次），直到病人表现出能够或不能够重复这些速度。
+V’V’ （as in：“along，along”）
+’VV’VV （as in：“long fellow”）
+V’’V’’ （as in：“a long time”）
+’V V’’， （as in：“shave and a haircut”）
+’：长
+V：短
+记分： 背诵 唱歌 节律
+良好=2
+差=1
+失败=0
+D.词复述
+发音 错词
+正常笨拙错音失败词四声新词音素词语其他钓鱼土色椅子汽车工作大篮球学游泳1776科学文化北京火车站 总分：
+E.短语复述：要求时，可复述全句一次。
+发音 错语
+正常笨拙错音失败1.高频语 2.低频语
+四声新词音素词语其他a.花开了a.大盆漏了。b.不许抽烟。b.桔子是酸的。c.下班我回家。c.罪犯逃到澳门。d.请给我一杯水。d.把罐头盖撬开。e.天热要开电扇。e.扇子上有罕见的绿宝石。f.凳子在餐厅的桌子旁边。f.燕子捕捉到一个圆滚滚的虫子。g.昨晚他们收听到老李在电台的讲话。g.律师的申辩能为被告减刑。h.我在门前停下来，按了一下门铃。h.飞碟飞过了晴朗的夜空。 高频语总分：
+ 低频语总分：
+F.读词（卡5）
+发音 反应延迟时间 错语
+正常笨拙错音失败0~3″
+3分3~10″
+2分10~30″
+1分失败
+0分四声新词音素词语其他椅子圆形汽车三角十五紫色七百二十一滴水白色吸烟 总分：
+G.回答名称
+发音 反应延迟时间 错语
+正常笨拙错音失败0~3″
+3分3~10″
+2分10~30″
+1分失败
+0分四声新词音素词语其他什么东西能告诉我们时间？拿钥匙能干什么用？拿肥皂能干什么用？拿铅笔能干什么用？我们用什么裁衣服？青草是什么颜色的？我们用什么点香烟？一打有多少个？煤是什么颜色？吸烟你到哪里可买到药？ 总分：
+H.识图呼名：
+发音 反应延迟时间 言语错乱
+正常笨拙错音失败0~3″
+3分3~10″
+2分10~30″
+1分失败
+0分四声新词音素词语其他物品椅子钥匙手套羽毛汽车仙人掌拼音htrlsg几何图形正方形三角形动作跑睡觉喝水吸烟摔到滴水数字7157001936427000颜色红色黄色绿色兰色白色黑色身体部分耳朵鼻子胳膊肘肩膀脚腕手腕 总分：
+J.列名
+告诉病人：“我想知道你在一分中的时间里能想出多少动物的名字，你把这些动物的名字告诉我，什么动物都可以，可以是农村的，森林里的，海里的，家里饲养的都可以。例如：“狗”，记录1′30″内说出的动物名称数，以60″连续说出的名称为基础记分，录音。
+15″ 15-30″ 30-45″ 45-60″ 60-75″ 75-90″
+ 总分：
+K.读句子：病人朗读卡6、7中的句子。记下给予的帮助、遗漏、替代等。完全正确的给1分。
+ 总分：
+正确
+失败
+花开了。
+不许抽烟。
+下班我回家。
+凳子在餐厅的桌子旁边。
+昨晚他收听到老李在电台的讲话。
+桔子是酸的。
+罪犯逃到澳门。
+燕子捕捉到一个圆滚滚的虫子。
+律师的申辩能为被告减刑。
+飞碟飞过了晴朗的夜空。
+ 总分：
+Ⅳ.书面语言的理解
+A.字辨别（卡8、9）
+田
+令
+日
+仗
+自
+甸
+天
+沮
+末
+迈
+ 总分：
+语音联系
+1.听词辨认：检查者读下列词，病人从图片10、11上指出相应的词。应告诉病人图片上正确的一行。
+轮船
+小狗
+池塘
+细雨
+书
+洞
+运用
+爆炸
+ 总分：
+C.词图匹配
+ 卡2、3、5，检查者给病人出示一个词，病人指出相应的图画。不应读出声。
+椅子
+红色
+圆形
+七百二十一
+汽车
+滴水
+三角形
+白色
+十五
+吸烟
+ 总分：
+D.阅读句子和段落
+图12、13、14、15。
+ 例题
+水是 小孩玩
+浓的、液体、干的、红色 门、鞋、铜币、皮鞋
+1.狗会
+ 说话、叫、唱歌、猫
+2.每个母亲都有自己的
+ 树、厨师、孩子、卡车
+3.老张给顾客理发、洗头。他是
+ 剃胡子、男同志、屠夫、理发师
+4.夏天，许多鸟飞过来，它们在树上
+ 搭鸟窝、下鸡蛋、抓麻雀、捕猫
+5.公路要保养和修建，就需要经费，因此骑自行车的人要
+ 交房子、国家、交税、找警察
+6.画出美丽图画的或雕塑出优美塑像的人是艺术家，另一种艺术家是
+ 图画、音乐家、图书管理员、战士
+7.铝的提炼曾经是非常昂贵的，现在电学技术解决了提纯问题，铝已变得
+ 很结实、很便宜、矿工、电子的
+8.随着城市的扩建，人们需要寻找新的水源，来满足 的需要。
+ 人口增长、河流、儿童、花园
+9.工业中的退休制度，是对年轻人的工作保证，这种机会
+ 是对老年人的帮助、将公平分配、必须在新的工作中寻找、是为年轻人敞开的就业机会
+10.国际上有两大问题非常突出，一个是和平问题，一个是战争问题。人民需要和平，不要战争。现在有核武器，一旦发生战争，核武器就会给人类带来
+ 战争、巨大的损失、原子弹、和平
+Ⅴ.书写
+A.书写机制
+ 书写动作的回忆和执行。
+姓名、住址、工作单位。
+如果病人不能完成1项，写出病人的姓名和住址，让病人抄写。
+抄写：我们要恢复和发扬自力更生，舍己为公，为实现四个现代化贡献一切的社会风尚。
+根据病人的书写输出，评价书写机制。
+1分字迹不清楚。 4分个别字不清楚。
+2分偶尔单个字清楚。 5分与患病前相同（可使用非惯用手）
+3分一些变形字体。
+ 总分：
+B文字符号的回忆
+系列书写
+1~21（序数） 正确数 总分：
+初级水平听写
+a.听写部首 正确数
+立人、月、木、提手、言 0 1 2 3 4 5
+b.数字
+7、15、42、193、1895 0 1 2 3 4 5
+c.常见字
+去、来、天、男、火 0 1 2 3 4 5
+ 总分：
+C.看图书写
+ 图2、3，病人写出各图画的名称
+汽车
+圆
+喝水
+椅子
+方
+抽烟
+ 总分：
+D.描述书写
+ 图1“尽量写出你在图中看到的发生的事情。”5分钟时间
+分 级
+ 0—无关词：书写不清楚，书写错语，无法辨认有关的名词和动词。
+ 1—有限的与情节有关的词字（1~4个）
+ 2—一个或一个以上的短语。例如：名词+动词，主语名词+宾语名词，但无思想的连续性。
+ 或
+ 较多的（五个或五个以上）列出孤立的，有关名词或动词。
+ 3—思想的连续：在书写顺序中，至少有两个动作或描述性叙述。不记语法错误或书写错语。
+ 4—组织较好的叙述：有关的叙述，仅有较少的书写错语，语法或拼写错误。
+ 或
+ 过多的简单句。
+ 5—正常：与患病前的水平相同
+听写句子。
+a.我看不见他们。
+b.那个男孩正在拿饼干。
+c.如果他不小心点儿，凳子就会翻倒。
+A.按下列标准评分
+0—两个或俩个以下的字正确
+1—三个或三个以上的字正确
+2—一半以上正确
+3—正确但完成的很吃力
+4—正常
+ 总分：
+B.书写错误分级：
+ 0—明显
+ 1—不明显
+2—无
+姓名 评价日期
+ 评价人
+失语症严重程度分级标准
+0—无有意义语言或听理解能力
+1—所有语言交流，通过不连续的言语表达；大部分需要听者猜测，可交流的信息范围有限，听者在言语交流中感到困难。
+2—在听者的帮助下，可能进行熟悉的话题的交谈。病人常常不能表达出自己的思想，病人与检查者都感到进行言语交流的困难。
+3—在极少的帮助下或无帮助下，病人可以讨论几乎所有的日常问题。但由于言语和/或理解能力的减弱，使某些谈话出现困难或不可能。
+4—言语流利和可观察到的理解障碍。在思想表达和言语形成无明显限制。
+5—极小的，可分辨得出的言语障碍；病人主观上可能感到有点儿困难，但听者不能明显觉察到。
+失写症的书写特点
+完全性书写障碍
+构字障碍
+书写惰性现象
+象形书写
+写字过多
+镜像书写
+言语特征分级表
+语调 1 2 3 4 5 6 7
+（语调轮廓线） 无 短语和日常熟练语 完整句子
+短语长度 1个字 4个字 7个字 
+（偶尔最长不中断的句子）
+构音能力（发音灵活性。完全不正常 只在熟悉的词 正常
+音素和音节的灵活性） 或不可能 和短语中正常
+语法形式 无 单个名词或 超不出 仅限于简单 超不出 正常
+（各种语法结构） 动词为主 谓和宾 陈述和日常 主谓宾结构
+ 熟练语
+连续语言中的错语
+（不用于短语长度 存在与每6句话中 5 对话中每 3 2 （正常）
+低于3级或3级） 分钟4次
+复述
+（按高频度语记分） 0 0 1 2 4 6 8
+觅词
+（信息内容与 流利无信息 信息与流利成正比 言语与内容
+流利言语的比较） （正常） 完全相关
+听理解
+（四个听理解分测验 1 15 30 45 60 75 90
+分数的平均百分数）
+音量： 小 正常 大
+嗓音： 低语 沙哑 正常
+速度： 慢 正常 快
+其他评语：
+失语症分测验总结图
+姓名： 检测日期：
+%0102030405060708090100严重度分级012345流 利发音分级124567短语长度134567语 调12467言语灵活025689111314听觉理解词辨别01525374653664677072身体部分辨认01510131516171820执行指示034681011131415复杂概念023456891112呼 名回答呼名015101520242730识图呼名09284360728494105114列 名012346923朗 读读词013715212630读句01247910复述词复述02578910高频度语0124578低频度语012468错语新词症401694210四声4717139653210音素4717139653210词语4023181512974310其他75125310自动言语自动语序01234678背诵012阅读理解字的辨认02578910听词辨认01345678词—图匹配01468910读句子和段落01234567810书写书写机制12345系列书写03910131517192021初级水平听写0146911131415看图书写012367910听写句子0136812描述书写012345音乐唱歌012节律012空间与计算绘画0678910111213小棒图案记忆034678910111314三维积木0245678910全部手指054708193100108120130141152左—右鉴别0134689111416算 术0248111417212732钟表时间调整0346891012</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ADL</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>步行能力（hoffer和holden）</t>
+          <t>日常生活活动能力评定（ADL）</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>评定系列表
+巴氏指数（Barthel Index）评定表
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+项目
+评分标准
+ 月 日
+1. 大便
+0=失禁或昏迷
+5=偶尔失禁（每周&lt;1次）
+10=能控制
+2. 小便
+0=失禁或昏迷或需由他人导尿
+5=偶尔失禁（每24小时&lt;1次，每周&gt;1次）
+10=能控制
+3. 修饰
+0=需帮助
+5=独立洗脸、梳头、刷牙、剃须
+4. 用厕
+0=依赖别人
+5=需部分帮助
+10=自理
+5. 吃饭
+0=依赖别人
+5=需部分帮助（夹饭、盛饭、切面包）
+10=全面自理
+6. 转移
+（床←→椅）
+0=完全依赖别人，不能坐
+5=需大量帮助（2人），能坐
+10=需少量帮助（1人）或指导
+15=自理
+7. 活动（步行）
+（在病房及其周围，不包括走远路）
+0=不能动
+5=在轮椅上独立行动
+10=需1人帮助步行（体力或语言指导）
+15=独立步行（可用辅助器）
+8. 穿衣
+0=依赖
+5=需一半帮助
+10=自理（系开钮扣、关、开拉锁和穿鞋）
+9. 上楼梯（上下一段楼梯，用手杖也算独立）
+0=不能
+5=需帮助（体力或语言指导）
+10=自理
+10. 洗澡
+0=依赖
+5=自理
+总分
+评定者</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
+      <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>汉语失语症评定量表ABC</t>
+          <t>格拉斯哥昏迷量表</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>第九人民医院
+龙岗中心医院
+ 深圳市康复科
+格拉斯哥昏迷量表评定（GCS）
+姓名 性别 年龄 岁 科别 床号 床
+诊断： 住院号 
+内容
+标准
+评分
+得分
+睁眼反应
+自动睁眼
+听到言语、命令时睁眼
+刺痛时睁眼
+对任何刺激无睁眼
+4
+3
+2
+1
+运动反应
+能执行简单命令
+刺痛时能指出部位
+刺痛时肢体能正常回缩
+刺痛时躯体出现异常屈曲（去皮层状态）
+刺痛时躯体异常伸展（去大脑强直）
+对刺痛无任何运动反应
+6
+5
+4
+3
+2
+1
+言语反应
+回答正确
+回答错误
+用词不适当但尚能理解含义
+言语难以理解
+无任何言语反应
+5
+4
+3
+2
+1
+总得分：
+时 间：
+评定者：
+最高计分15分为正常；最低计分3分；小于7分属昏迷；大于或等于9分不属昏迷。昏迷愈深，伤情愈重，得分愈少。下述2种情况不计入评分：①脑外伤入院6小时死亡；②颅脑火器伤。
+根据昏迷时间长短，可将颅脑损伤分为4型：轻型：总分13～15分，伤后昏迷20分钟以内者。中型：总分9～12分，伤后昏迷20分钟～6小时。重型：总分6～8分，伤后昏迷或再次昏迷持续6小时以上。特重型：总分3～5分。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>注意功能评定</t>
+          <t>植物状态评分标准</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>植物状态评分标准
+姓名： 性别： 年龄： 岁 科别： 科 床号： 床 住院号： 
+诊断： 
+评分项目
+评分级别
+分值
+年 月 日
+年 月 日
+年 月 日
+执行指令
+无
+微弱动作
+能执行简单指令
+能执行各种指令
+0
+1
+2
+3
+语言
+无
+能哼哼出声
+能说单词
+能说整句
+0
+1
+2
+3
+肢体运动
+无
+刺激后运动
+无目的随意运动
+有目的随意运动
+0
+1
+2
+3
+眼球运动
+无
+偶有眼球追踪
+经常眼球追踪
+有意注视
+0
+1
+2
+3
+吞咽
+无
+能吞咽液体
+能吞咽稠食
+能咀嚼
+0
+1
+2
+3
+情感反应
+无
+偶流泪
+能哭笑
+正常情感反应
+0
+1
+2
+3
+得分
+时间
+评定人
+疗效判断：18分为正常；≥12分为基本痊愈；提高6～11分，但＜12分为显效；提高1～5分，但＜12分为有效；其余为无变化、恶化、死亡。
+12～18分:基本恢复 10～11分：脱离植物状态
+8～9分：过渡性植物状态 3～7分：不完全性植物状态 
+＜3分：完全性植物状态
+最小意识状态（MCS）：是一种意识的严重改变情况，有极小但很明确的自我和环境觉醒的行为证据。要点：以下的一种或后几种条件必须显而易见，并且可重复或持续出现。1〕执行简单指令；2〕无论对错，能用手势或语言活动表示“是/否”；3〕语言表达可以被理解；4〕在情景下可能发生的动作或情感反应并非由反射性活动引起。
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>焦虑抑郁自评量表</t>
+          <t>步行能力（hoffer和holden）</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Hoffer步行能力分级
+Ⅰ 不能步行(nonambulator) 完全不能步行 
+Ⅱ 非功能性步行 (nonfunctional ambulator) 借助于膝-踝-足矫形器（KAFO）、手杖等能在室内行走，又称治疗性步行。
+ Ⅲ 家庭性步行 (household ambulator) 借助于踝-足矫形器（AFO）、手杖等能在室内行走自如，但在室外不能长时间行走。 
+Ⅳ 社区性步行 (community ambulator) 借助于AFO、手杖或独立可在室外和社区内行走、散步、去公园、去诊所、购物等活动，但时间不能持久，如需要离开社区长时间步行仍需坐轮椅。
+ Holden步行功能分类
+0级：无功能 患者不能走，需要轮椅或2人协助才能走。 
+Ⅰ级：需大量持续性的帮助 需使用双拐或需要1个人连续不断地搀扶才能行走或保持平衡。 
+Ⅱ级：需少量帮助 能行走但平衡不佳，不安全，需1人在旁给予持续或间断的接触身体的帮助或需使用膝-踝-足矫形器（KAFO）、踝-足矫形器（AFO）、单拐、手杖等以保持平衡和保证安全。 
+Ⅲ级：需监护或语言指导 能行走，但不正常或不够安全，需1人监护或用语言指导，但不接触身体。 
+Ⅳ级：平地上独立 在平地上能独立行走，但在上下斜坡、在不平的地面上行
+走或上下楼梯时仍有困难，需他人帮助或监护。 
+Ⅴ级：完全独立 ，在任何地方都能独立行走。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>瑞文彩色推理</t>
+          <t>汉语失语症评定量表ABC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+汉语失语症检查表（ABC法）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+谈话（流畅度9－27分、信息量0－6分）
+1．问答（录音）
+回答
+特征
+备注
+（1）您好些吗？
+（2）您以前来过这吗？
+（3）您叫什么名字？
+（4）您多大岁数了？
+（5）您家住在什么地方？
+（6）您做什么工作（或退休前做什么工作）？
+（7）您简单说说您的病是怎么得起来的？或您怎么不好？
+（8）让病人看图片，叙述。
+流畅度___ /27分 
+信息量___ /6分
+2．系列语言
+实数数
+备注
+从1数到21
+总分 /21分 
+理解
+（一）是/否问题（共60分）
+Ⅰ 问题、答案、表达方式与评分
+问题
+正确答案
+表达方式
+评分
+言语特征
+言语
+手
+头
+闭眼
+（1）你的名字是张小红吗？否2（2）你的名字是李华明吗？否2（3）你的名字是（真名）吗？是2（4）你家住在前门/鼓楼吗？否2（5）你家住在（正确地名）吗？是2（6）你住在通县/延庆吗？否2（7）你是大夫吗？否2（8）我是大夫吗？是2（9）我是男的/女的吗？否2（10）这个房间的灯亮着吗？是2（11）这个房间的门是关着的吗？否2（12）这儿是旅馆吗？否2（13）这儿是医院吗？是2（14）你穿的衣服是红/蓝色的吗？否2（15）纸在火中燃烧吗？是4（16）每年中秋节在端午节前先过吗？否4（17）您吃香蕉时先剥皮吗？是4（18）在本地七月下雪吗？否4（19）马比狗大吗？是4（20）农民用斧头割草吗？否4（21）一斤面比二斤面重吗？否4（22）冰在水里会沉吗？否4总分
+ /60
+（二）听辨认（共90分，45项，每项2分）
+实物&lt;5’’
+2分&gt;5’’
+1分0分图形&lt;5’’
+2分&gt;5’’
+1分0分图画&lt;5’’
+2分&gt;5’’
+1分0分梳子圆钥匙铅笔方火柴钥匙三角梳子火柴螺旋铅笔花五星花
+动作&lt;5’’
+2分&gt;5’’
+1分0分颜色&lt;5’’
+2分&gt;5’’
+1分0分家具&lt;5’’
+2分&gt;5’’
+1分0分吸烟红窗户喝水黄椅子跑步蓝电灯睡觉绿桌子摔倒黑床
+身体&lt;5’’
+2分&gt;5’’
+1分0分身体&lt;5’’
+2分&gt;5’’
+1分0分身体&lt;5’’
+2分&gt;5’’
+1分0分耳朵中指右耳鼻子胳膊肘左眼肩膀眉毛左拇指眼睛小指右手腕手腕拇指右中指听辨认总分：___ /90分。
+（三）口头指令（共80分）
+Ⅱ指令和评分
+总分
+评分
+备注
+（1）把手举起来
+2
+（2）闭上眼睛
+2
+（3）指一下房顶
+2
+ 2 2 2
+（4）指一下门，然后再指窗户
+6
+ 2 2 2
+（5）摸一下铅笔，然后再摸一下钥匙。
+6
+ 4 2 4
+（6）把纸翻过来，再把梳子 放在纸上边。
+10
+ 5 5
+（7）用钥匙指梳子，然后放回原处。
+10
+ 5 7
+（8）用梳子指铅笔，然后交叉放在一起。
+12
+ 2 4 2 4
+（9）用铅笔 指纸一角，然后 放在另一角处。
+12
+ 2 10 6 
+（10）把钥匙 放在铅笔和梳子中间，再用纸盖上。
+18
+总分
+ /80分
+复述（共100分）
+1.词复述（共24分）
+题号
+问题
+满分
+评分
+言语特征
+备注
+（1）
+门
+1
+（2）
+床
+1
+（3）
+尺
+1
+（4）
+哥
+1
+（5）
+窗户
+2
+（6）
+汽车
+2
+（7）
+八十
+2
+（8）
+新鲜
+2
+（9）
+天安门
+3
+（10）
+四十七
+3
+（11）
+拖拉机
+3
+（12）
+活蛤蟆
+3
+总分
+2.句复述（共76分）
+题号
+问题
+满分
+评分
+言语特征
+（1）
+听说过
+3
+（2）
+别告诉他
+4
+（3）
+掉到水里啦
+5
+（4）
+吃完饭就去遛弯
+7
+（5）
+办公室电话铃响着吧
+9
+（6）
+他出去以后还没有回来
+10
+（7）
+吃葡萄不吐葡萄皮
+8
+（8）
+所机全微他合（每秒2字）
+12
+（9）
+当他回到家的时候，发现屋子里坐满了朋友
+18
+总分
+复述总分_______/100分
+四．命名
+（一）词命名（共40分，20项）
+实物反应2触摸1提示0.5实物反应2触摸1提示0.5身体反应2触摸1提示0.5图片反应2触摸1提示0.5铅笔皮尺头发跑步纽扣别针耳朵睡觉牙刷橡皮手腕吸烟火柴表带拇指摔跤钥匙发卡中指喝水词命名总分 /40分
+（二）列名
+记录前半分钟和后半分钟说出的蔬菜名___ ， ____。
+（三）颜色命名（共12分）
+请告诉我，这是什么颜色？红__ 黄__ 黑__ 蓝__ 白__ 绿__ 评分____
+问题
+答案
+评分2
+言语特征
+1.晴天的天空是____的？
+蓝
+2.春天的草是____的？
+绿
+3.煤是____的？
+黑
+4.稻谷熟了是____的？
+黄
+5.牛奶是____的？
+白
+6.少先队员的领巾是____的？
+红
+总分
+颜色命名总分____/12分
+（四）反应命名（共10分）
+问题
+答案
+评分2
+言语特征
+1.您切菜用什么？
+刀
+2.看什么可以知道几点了？
+钟、表
+3.用什么点烟？
+火柴、打火机
+4.天黑了什么可以使房间亮？
+电灯、蜡烛
+5.到哪儿能买到药？
+医院、药店
+总分 /10分
+五.阅读
+（一）视—读（共10分，每项1分）
+内容
+评分1
+言语特征
+内容
+评分1
+言语特征
+明
+妹
+肚
+鸭
+动
+村
+和
+砂 
+睛
+转
+总分
+ /10分
+（二）听字—辨认（共10分，每字1分）
+目标词
+备选词
+得分
+备注
+（第）47
+17
+74
+14
+47
+407
+（水）田
+由
+甲
+申
+电
+田
+（喝）水
+永
+水
+本
+木
+术
+成（功）
+戊
+成
+戌
+咸
+威
+唱（歌）
+倡
+昌
+唱
+畅
+常
+（棉）被
+背
+被
+披
+杯
+倍
+（铅）笔
+币
+必
+笔
+比
+毕
+（电）灯
+登
+灯
+邓
+瞪
+等
+（您）好
+佳
+良
+棒
+冠
+好
+坏（人）
+次
+差
+坏
+下
+未
+总分
+/10分
+（三）字—画匹配（共40分，共20项，朗读、配画各1分）
+图画朗读配画图形朗读配画动作朗读配画颜色朗读配画钥匙圆形喝水黑铅笔方块跑步红火柴三角睡觉黄梳子螺旋吸烟绿菊花五星摔倒蓝总分
+ 朗读 /20分 配画 /20分
+读指令，并执行（共30分）
+内容
+朗读
+执行
+言语特征
+（1）闭眼
+1
+1
+（2）摸右耳
+1
+1
+ 1 2
+（3）指门，再指窗户
+3
+3
+ 2 2
+（4）先摸铅笔，后摸钥匙
+4
+4
+ 3 3
+（5）用梳子指铅笔，然后交叉放在一起
+6
+6
+总分
+ /15分
+ /15分
+读句选答案填空（共30分）
+句子
+答案
+评分
+备注
+（1）苹果是……的
+原的、圆的、圆圈、方的
+2
+（2）解放军带……
+呛、枪、强、仓
+2
+（3）老王修理汽车和卡车，他是……
+清洁工、司机、机器、修理工
+6
+（4）孙悟空本领高强，会七十二变，若不是……，唐僧怎管得住他
+想取经、紧箍咒、如来佛、猪八戒
+10
+（5）中国地大物博，人口众多，但是人均可耕地少，因此，应该珍惜……
+经济、水源、承包、土地
+10
+总分
+ /30分
+六．书写
+写姓名、地址（共10分）
+评分
+特征
+姓名3
+地址7
+总分
+ /10分
+抄写（共10分，每字1分）
+北京是世界文明的都市 ___/10分
+系列书写1-24（最高20分）
+ ____/20分
+听写（共34分）
+偏旁(共5分)
+立人1
+言1
+提手1
+走之1
+土1
+总分
+数字（共7分）
+各1分
+各2分
+总分
+7
+15
+42
+193
+1860
+字（共5分，每字1分）
+火柴
+铅笔
+嘴的口
+方块
+黄颜色
+总分
+词（共10分，每字1分）
+梳子
+钥匙
+睡觉
+跑步
+五星
+总分
+短句（共7分，每字1分）
+春风吹绿了树叶
+评分： 分
+听写总分： ______ /34分
+看图写字（共20分，每图2分） ____/20分
+写病情（最高5分） ____/5分
+结构与空间（共19分）
+照图画（共10分）
+图一1
+图二2
+图三3
+图四4
+总分
+ /10分
+摆方块（共9分）
+方块一1.5
+方块二3
+方块三4.5
+总分
+ /9分
+结构与空间总分：____/19分
+运用（最高30分）
+面部（共8分）
+执行2
+模仿1
+用实物0.5
+未完成0
+备注
+咳嗽
+吹灭火柴
+鼓腮
+用吸管吸水
+总分
+上肢（共8分）
+执行2
+模仿1
+用实物0.5
+未完成0
+备注
+挥手再见
+致礼
+刷牙
+梳头
+总分
+（三）复杂（共14分）
+得分
+备注
+假装划火柴（3），点烟（3）
+假装把信纸叠起来（3），放进信封（3），封好（2）
+总分
+运用总分：____/30分
+计算（共每题2分，共24分）
+加法
+减法
+备注
+5+4=9，20，1，8
+6+7=12，13，52，14
+9+3=6，17，12，21
+6-2=8，4，12，3
+8-3=5，11，24，16
+11-7=18，4，8，17
+乘法
+除法
+4×2=6，2，8，1
+6×7=13，21，2，42
+8×3=5，11，24，40
+9÷3=12，3，6，27
+64÷8=40，56，8，32
+35÷7=5，28，12，21
+总分 /24分
+ABC法评定结果总结表
+口语表达
+听理解
+阅读
+书写
+信息量流利性系列语言复述命名是/否题听辨认口头指令视读听字辨认字画
+匹配读指令执行填空姓名地址抄写听写系列书写看图书写自发书写词命名反应命名颜色命名朗读理解朗读理解%
+100
+90
+80
+70
+60
+50
+40
+30
+20
+10
+失语症诊断： 失语症, BDAE严重程度: 级
+PAGE 
+PAGE 1</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>简化Fugl-Meyer</t>
+          <t>注意功能评定</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+注意力评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+1. 视跟踪和辨别
+(Ａ)视跟踪 让患者看着一光源，医生将光源向患者左、右、上、下移动，观察患者随之移动的能力，每个方向评1分，正常4分。
+(Ｂ)形状辨别 让患者复制一根垂线、一个圆、一个正方形和大写字母Ａ，每项评1分，正常4分。
+(Ｃ)删字母 给患者一支铅笔，让他以最快速度准确地删去下面字母列中的Ｃ和Ｅ。
+供删除试验用的字母列
+ ───────────────────────────────────────────────
+ BEIFHEHFEGICHEICBDACBFBEDACDAFCIHCFEBAFEACFCHBDCFGHE
+ CAHEFACDCFEHBFCADEHAEIEGDEGHBCAGCIEHCIEFHICDBCGFDEBA
+ EBCAFCBEHFAEFEGCHGDEHBAEGDACHEBAEDGCDAFCBIFEADCBEACG
+ CDGACHEFBCAFEABFCHDEFCGACBEDCFAHEHEFDICHBIEBCAHCHEFB
+ ACBCGBIEHACAFCICABEGFBEFAEABGCGFACDBEBCHFEADHCAIEFEG
+ EDHBCADGEADFEBEIGACGEDACHGEDCABAEFBCHDACGBEHCDFEHAIE
+ ──────────────────────────────────────────────
+要注意实际试验时上表中的字母应为正常大小的规格。删除中每列约需删去18个字母，100s 内删错多于一个为注意有缺陷。
+ 2. 数或词的辨别
+(Ａ)听认字母 医生在60s 内以每秒一个的速度念无规则排列字母，其中有10个为指定的同一字母，让患者每听到此字母时举一下手，应举10次。 
+(Ｂ)重复数字 医生以每秒一个的速度给患者念随机排列的数目字，从两个开始，每念完一系列让患者重复一次，一直进行到患者不能重复为止。复述不到5个数字为异常。
+(Ｃ)词辨认 向患者播放一录音带，内有一段短文，其中有一定的数量的指定词(此例为“红”字)，让患者每听到红字举一次手，短文如下：“昨晚我骑着我的红自行车回家时，晚霞将天染得红通通的，我向红色的天空望了一眼，看见了一些云彩。回家时，我妹妹小红在屋里穿着一件红毛衣和红运动裤，她告诉我她要和同学去红都餐厅吃晚饭，她骑上我的红车子走了。我打开窗看见对面三层的红房子的阳台上挂着三件红色上衣。”举手次数少于9为有注意缺陷。
+3. 听跟踪 让患者闭目听铃，将铃在患者左、右、前、后和头上方摇动，让他指出铃之所在。每种位置评1分，少于5分为异常。
+ 4. 声辨认 可作下述检查：
+ (Ａ)声认识 向患者放一录有嗡嗡声、电话铃声、钟表卡嗒声和号角声的录音带，让他每听到号角声时举一下手，号角声出现5次，举手不到5次为有缺陷。
+ (Ｂ)在杂音背景中辨认词 向患者放一段有喧闹集市背景声的短文，内容和安排类似Ｂ中之(Ｃ)，其中亦有10个指定的词，让患者每听到此词时举一下手，举手不到8次为有缺陷。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MCGILL</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>简化McGill疼痛问卷（SF-MPQ）</t>
+          <t>焦虑抑郁自评量表</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>焦虑自评量表（SAS）
+姓名 年龄 男、女 床号 住院号 评价人
+ ABCD月 日月 日月 日1、我觉得比平常容易紧张或着急12342、我无缘无故地感到害怕12343、我容易心里烦乱或觉得惊恐12344、我觉得我可能将要发疯12345、我觉得一切都很好，也不会发生什么不幸*43216、我手脚发抖打颤12347、我因为头痛、颈痛和背痛而苦恼12348、我感觉容易衰弱和疲乏12349、我得心平气和，并且容易安静坐着*432110、我觉得心跳得很快123411、我因为一阵阵头晕而苦恼123412、我有晕倒发作，或觉得要头晕似的123413、我吸气呼气都感到很容易*123414、我的手脚麻木和刺痛123415、我因为胃痛和消化不良而苦恼123416、我常常要小便123417、我的手脚常常是干燥温暖的*432118、我脸红发热123419、我容易入睡并且一夜睡得很好*432120、我做恶梦1234总分注意：每一条文字后有四个字母分别表示：A没有或很少时间B少部分时间C相当多时间D绝大部分
+大部分或全部时间 *号为反序计分 粗分47分 标准分59分
+抑郁自评量表（SDS)
+项目偶无有时经常持续月 日月 日月 日1、我感到情绪沮丧、郁闷12342、我感到早晨心情最好*43213、我要哭或想哭12344、我夜间睡眠不好12345、我吃饭向平时一样多*43216、我的性功能正常*43217、我感到体重减轻12348、我为便秘烦恼12349、我的心跳比平时快123410、我无故感到疲劳123411、我的头脑像往常一样清楚*432112、我做事情向平时一样不感到困难*432113、我坐卧不安，难以保持平静123414、我对未来感到有希望*432115、我比平时更容易激怒123416、我觉得决定什么事很容易*432117、我觉得自己是有用的和不可缺少的人*432118、我的生活很有意义*432119、假若我死了别人会过得更好123420、我仍旧喜爱自己平时喜爱的东西*4321总分注意：根据近一周感觉，选适当位置划钩 *号为反序计分 粗分：46分 标准分：57.5分</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>TOKEN</t>
-        </is>
-      </c>
+      <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>简式Token测试量表</t>
+          <t>瑞文彩色推理</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+瑞文彩色推理评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+正确为1，错误为0，修改后正确为1.
+图1 图7 图13 图19 图25 图2 图8 图14 图20 图26 图3 图9 图15 图21 图27 图4 图10 图16 图22 图28 图5 图11 图17 图23 图29 图6 图12 图18 图24 图30 
+得分： /30</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>简易吞咽功能评定</t>
+          <t>简化Fugl-Meyer</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>评定系列表
+简化Fugl-Meyer运动功能评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 
+0分
+1分
+2分
+月 日
+月 日
+月 日
+Ⅰ上肢
+坐位或仰卧位
+1有无反射活动
+（1）肱二头肌
+不引起反射活动
+能引起反射活动
+（2）肱三头肌
+同上
+同上
+2屈肌协同运动
+（3）肩上提
+完全不能进行
+部分完成
+无停顿地充分完成
+（4）肩后缩
+同上
+同上
+同上
+（5）肩外展≥90度
+同上
+同上
+同上
+（6）肩外旋
+同上
+同上
+同上
+（7）肘屈曲
+同上
+同上
+同上
+（8）前臂旋后
+同上
+同上
+同上
+3伸肌协同运动
+（9）肩内收、内旋
+同上
+同上
+同上
+（10）肘伸展
+同上
+同上
+同上
+（11）前臂旋前
+同上
+同上
+同上
+4伴有协同运动的活动
+（12）手触腰椎
+没有明显活动
+手仅可向后越过髂前上棘
+能顺利进行
+（13）肩关节屈曲90度，肘关节伸直
+开始时手臂立即外展或肘关节屈曲
+在接近规定位置时肩关节外展或肘关节屈曲
+能顺利充分完成
+（14）肩0度，肘屈90度，前臂旋前、旋后
+不能屈肘或前臂不能旋前
+肩、肘位正确，基本上能旋前、旋后
+顺利完成
+5脱离协同运动的活动
+（15）肩关节外展90度，肘伸直，前臂旋前
+开始时肘就屈曲，前臂偏离方向，不能旋前
+可部分完成此动作或在活动时肘关节屈曲或前臂不能旋前
+顺利完成
+（16）肩关节前屈举臂过头，肘伸直，前臂中立位
+开始时肘关节屈曲或肩关节发生外展
+肩屈曲中途、肘关节屈曲、肩关节外展
+顺利完成
+（17）肩屈曲30度~90度，肘伸直，前臂旋前旋后
+前臂旋前旋后完全不能进行或肩肘位不正确
+肩、肘位置正确，基本上能完成旋前旋后
+顺利完成
+6反射亢进
+0分
+1分
+2分
+月 日
+月 日
+月 日
+（18）检查肱二头肌、肱三头肌和指屈肌三种反射
+至少2~3个反射明显亢进
+一个反射明显亢进或至少二个反射活跃
+活跃反射≤1个，且无反射亢进
+7腕稳定性
+（19）肩0度，肘屈90度时，腕背屈
+不能背屈腕关节达15度
+可完成腕背屈，但不能抗拒阻力
+施加轻微阻力仍可保持腕背屈
+（20）肩0度，肘屈90度，腕屈伸
+不能随意屈伸
+不能在全关节范围内主动活动腕关节
+能平滑地不停顿地进行
+8肘伸直，肩前屈30度时
+（21）腕背屈
+不能背屈腕关节达15度
+可完成腕背屈，但不能抗拒阻力
+施加轻微阻力仍可保持腕背屈
+（22）腕屈伸
+不能随意屈伸
+不能在全关节范围内主动活动腕关节
+能平滑地不停顿地进行
+（23）腕环形运动
+不能进行
+活动费力或不完全
+正常完成
+9手指
+（24）集团屈曲
+不能屈曲
+能屈曲但不充分
+能完全主动屈曲
+（25）集团伸展
+不能伸展
+能放松主动屈曲的手指
+能完全主动伸展
+（26）钩状抓握
+不能保持要求位置
+握力微弱
+能够抵抗相当大的阻力
+（27）侧捏
+不能进行
+能用拇指捏住一张纸，但不能抵抗拉力
+可牢牢捏住纸
+（28）对捏（拇食指可挟住一根铅笔）
+完全不能
+捏力微弱
+能抵抗相当的阻力
+（29）圆柱状抓握
+同（26）
+同（26）
+同（26）
+（30）球形抓握
+同上
+同上
+同上
+10协调能力与速度（手指指鼻试验连续5次）
+（31）震颤
+明显震颤
+轻度震颤
+无震颤
+（32）辨距障碍
+明显的或不规则的辨距障碍
+轻度的或规则的辨距障碍
+无辨距障碍
+（33）速度
+较健侧长6秒
+较健侧长2~5秒
+两侧差别&lt;2秒
+Ⅱ下肢
+仰卧位
+0分
+1分
+2分
+月 日
+月 日
+月 日
+1有无反射活动
+（1）跟腱反射
+无反射活动
+有反射活动
+（2）膝腱反射
+同上
+同上
+2屈肌协同运动
+（3）髋关节屈曲
+不能进行
+部分进行
+充分进行
+（4）膝关节屈曲
+同上
+同上
+同上
+（5）踝关节背屈
+同上
+同上
+同上
+3伸肌协同运动 
+（6）髋关节伸展
+没有运动
+微弱运动
+几乎与对侧相同
+（7）髋关节内收
+同上
+同上
+同上
+（8）膝关节伸展
+同上
+同上
+同上
+（9）踝关节跖屈
+同上
+同上
+同上
+坐位
+4伴有协同运动的活动
+（10）膝关节屈曲
+无主动运动
+膝关节能从微伸位屈曲，但屈曲&lt;90度
+屈曲&gt;90度
+（11）踝关节背屈
+不能主动背屈
+主动背屈不完全
+正常背屈
+站位
+5脱离协同运动的活动
+（12）膝关节屈曲
+在髋关节伸展位时不能屈膝
+髋关节0度时膝关节能屈曲，但&lt;90度，或进行时髋关节屈曲
+能自如运动
+（13）踝关节背屈
+不能主动活动
+能部分背屈
+能充分背屈
+仰卧
+6反射亢进
+（14）查跟腱、膝和膝屈肌三种反射
+2~3个明显亢进
+1个反射亢进或至少2个反射活跃
+活跃的反射≤1个且无反射亢进
+7协调能力和速度（跟-膝-胫试验，快速连续作5次）
+（15）震颤
+明显震颤
+轻度震颤
+无震颤
+（16）辨距障碍
+明显不规则的辨距障碍
+轻度规则的辨距障碍
+无辨距障碍
+（17）速度
+比健侧长6秒
+比健侧长2~5秒
+比健侧长2秒</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MCGILL</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>简易精神状态评价量表(MMSE量表)</t>
+          <t>简化McGill疼痛问卷（SF-MPQ）</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>简化McGill疼痛问卷（SF-MPQ）
+姓名 性别 年龄 岁 科别 床号 床
+诊断： 住院号 
+Ⅰ.疼痛分级指数(PRI)月 日月 日 疼痛性质疼痛程度A感觉项无轻中重1跳痛01232刺痛01233刀割痛01234锐痛01235痉挛牵扯痛01236绞痛01237热灼痛01238持续固定痛01239胀痛012310触痛012311撕裂痛0123感觉项总分B情感类软弱无力0123厌烦0123害怕0123罪、惩罚感0123情感项总分Ⅱ.视觉模拟评分法(VAS)无痛（0）+ ——+——+——+——+——+——+————————+——+——+（100）极痛
+VAS评分Ⅲ.现时疼痛强度(PPI)0无痛1轻度不适2不适3难受4可怕的5极为痛苦PPI评分
+深圳市
+第九人民医院
+康复医学科
+龙岗中心医院</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GMFM-88</t>
+          <t>TOKEN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>粗大运动功能评估表(GMFM-88)</t>
+          <t>简式Token测试量表</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+简式Token测验（代币测验，36项）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+一、放20个代币（7分）：
+指令
+得分
+1、摸一下圆形，
+2、摸一下方形，
+3、摸一下黄的，
+4、摸一下红的，
+5、摸一下黑的，
+6、摸一下绿的，
+7、摸一下白的，
+合计
+二、把小代币拿走：（4分）
+指令
+得分
+8、摸黄色的方形， 
+9、摸黑色的圆形，
+10、摸绿色的圆形，
+11、摸白色的方形，
+合计
+三、把小代币放回：（4分）
+指令
+得分
+12、摸小的白色圆形，
+13、摸大的黄色方形，
+14、摸大的绿色方形，
+15、摸小的黑色圆形，
+合计
+四、把小代币拿走：（4分）
+指令
+得分
+16、摸红色圆形和绿色方形，
+17、摸黄色方形和绿色方形，
+18、摸白色方形和绿色圆形，
+19、摸白色圆形和红色圆形
+合计
+五、把小代币放回：（4分）
+指令
+得分
+20、摸大的白色圆形和小的绿色方形，
+21、摸小的黑色圆形和大的黄色方形，
+22、摸大的绿色方形和大的红色方形，
+23、摸大的白色方形和小的绿色圆形，
+合计
+六、把小代币拿走：（13分）
+指令
+得分
+24、把红色圆形放在绿色方形上，
+25、用红色方形碰黑色圆形，
+26、摸黑色圆形与红色方形，
+27、摸黑色圆形或者红色方形，
+28、把绿色方形从黄色方形旁边拿开，
+29、如果有蓝色圆形，摸红色方形，
+30、把绿色方形放在红色圆形旁边，
+31、慢慢地摸那些方形，很快地摸那些圆形，
+32、把红色圆形放在黄色方形和绿色方形之间，
+33、摸除了绿色之外的所有圆形，
+34、摸红色圆形――，不，白色方形，
+35、摸黄色圆形，不是白色方形，
+36、除了摸黄色圆形还要摸黑色圆形。
+合计
+最后总分： ＋ ＋ ＋ ＋ ＋ ＝ 分
+受教育年数：3－6年：加1分；10－12年：减1分；13－16年：减2分；≥17年，减3分。
+听理解障碍严重分级：29－36：正常； 25－28：轻度； 17－24：中度； 9－16：重度；8分以下：极重度。
+摆放顺序：
+大圆：红、黑、黄、白、绿
+大方：黑、红、白、绿、黄
+小圆：白、黑、黄、红、绿
+小方：黄、绿、红、黑、白</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>粗大运动功能评估量表(翻译)</t>
+          <t>简易吞咽功能评定</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+简易吞咽功能评定
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+“饮水试验”（洼田氏）：让患者喝1－2勺水，如无问题，瞩患者取坐位，将30ml温水递给患者，让其“像平常一样喝下”，记录饮水情况：
+可一口喝完，无噎呛；
+分两次以上喝完，无噎呛；
+能一次喝完，但有噎呛；
+分两次以上喝完，且有噎呛；
+常常呛住，难以全部喝完。
+情况I，若5秒内喝完，为正常；
+超过5秒，则可疑有吞咽障碍；情况II也为可疑；
+情况III、IV、V则确定有吞咽障碍。
+如饮用一勺水就呛住时，可休息后再进行，两次均呛住属异常。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MMT</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>肌力评定（MMT）</t>
+          <t>简易精神状态评价量表(MMSE量表)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>简易精神状态评价量表（MMSE）
+项目
+积分
+定向力
+（10分）
+1.今年是哪一年
+ 现在是什么季节？
+ 现在是几月份？
+ 今天是几号？
+ 今天是星期几？
+1
+1
+1
+1
+1
+0
+0
+0
+0
+0
+2.你住在那个省？
+ 你住在那个县（区）？
+ 你住在那个乡（街道）？
+ 咱们现在在那个医院？
+ 咱们现在在第几层楼？
+1
+1
+1
+1
+1
+0
+0
+0
+0
+0
+记忆力
+（3分）
+3.告诉你三种东西，我说完后，请你重复一遍并记住，待会还会问你（各1分，共3分）
+3
+2
+1
+0
+注意力和计算力
+（5分）
+4.100-7=？连续减5次（93、86、79、72、65。各1分，共5分。若错了，但下一个答案正确，只记一次错误）
+5
+4
+3
+2
+1
+0
+回忆能力
+（3分）
+5.现在请你说出我刚才告诉你让你记住的那些东西？
+3
+2
+1
+0
+语言能力
+(9分)
+6．命名能力
+出示手表，问这个是什么东西？
+出示钢笔，问这个是什么东西
+1
+1
+0
+0
+7．复述能力
+我现在说一句话，请跟我清楚的重复一遍（四十四只石狮子）！
+1
+0
+8.阅读能力
+（闭上你的眼睛）请你念念这句话，并按上面意思去做！
+1
+0
+9.三步命令
+我给您一张纸请您按我说的去做，现在开始：“用右手拿着这张纸，用两只手将它对折起来，放在您的左腿上。”（每个动作1分，共3分）
+3
+2
+1
+0
+10.书写能力要求受试者自己写一句完整的句子
+1
+0
+11.结构能力
+（出示图案）请你照上面图案画下来！
+1
+0
+一、操作说明 +I. 定向力(最高分:10分) + 首先询问日期,之后再针对性的询问其他部分,如"您能告诉我现在是什么季节 ",每答对一题得一分. + 请依次提问,"您能告诉我你住在什么省市吗 "(区县 街道 什么地方 第几层楼 )每答对一题得一分. +II.记忆力(最高分:3分) + 告诉被测试者您将问几个问题来检查他/她的记忆力,然后清楚,缓慢地说出3个相互无关地东西的名称(如:皮球,国旗,树木,大约1秒钟说一个).说完所有的3个名称之后,要求被测试者重复它们.被测试者的得分取决于他们首次重复的答案.(答对1个得1分,最多得3分).如果他们没能完全记住,你可以重复,但重复的次数不能超过5次.如果5次后他们仍未记住所有的3个名称,那么对于回忆能力的检查就没有意义了.(请跳过IV部分"回忆能力"检查). +III.注意力和计算力(最高分:5分) + 要求病人从100开始减7,之后再减7,一直减5次(即93,86,79,72,65).每答对1个得1分,如果前次错了,但下一个答案是对的,也得1分. +IV.回忆能力(最高分:3分) + 如果前次被测试者完全记住了3个名称,现在就让他们再重复一遍.每正确重复1个得1分.最高3分. +V.语言能力(最高分:9分) +1. 命名能力(0-2分):拿出手表卡片给测试者看,要求他们说出这是什么 之后拿出铅笔问他们同样的问题. +2. 复述能力(0-1分):要求被测试者注意你说的话并重复一次,注意只允许重复一次.这句话话是"四十四只石狮子",只有正确,咬字清楚的才记1分. +3. 三步命令(0-3分):给被测试者一张空白的平纸,要求对方按你的命令去做,注意不要重复或示范.只有他们按正确顺序做的动作才算正确,每个正确动作计1分. +4.阅读能力(0-1分):拿出一张"闭上您的眼睛"卡片给被测试者看,要求被测试者读它并按要求去做.只有他们确实闭上眼睛才能得分. +5. 书写能力(0-1分):给被测试者一张白纸,让他们自发的写出一句完整的句子.句子必须有主语,动词,并有意义.注意你不能给予任何提示.语法和标点的错误可以忽略. +6.结构能力(0-1分):在一张白纸上画有交叉的两个五边形,要求被测试者照样准确地画出来.评分标准:五边形需画出5个清楚地角和5个边.同时,两个五边形交叉处形成菱形.线条的抖动和图形的旋转可以忽略. +判定标准：最高得分为30分,分数在27-30分为正常,分数&lt;27为认知功能障碍. +痴呆严重程度分级方法：轻度MMSE≥21分;中度,MMSE 10-20分;重度,MMSE≤9分 
+二、使用指南
+1 定向力：每说对一个记1分，总共5分。日期和星期差一天可计正常。月、日可以记阴历。如受访者少说了其中一个或几个（如忘记说月份、星期几等），调查员应该补充再问一遍受访者遗漏的内容。
+2 记忆：要求患者记忆3个性质不同的样物件，要告诉受访者你可能要考察他/她的记忆力。调查员说的时候需连续、清晰、一秒钟一个。第一次记忆的结果确定即刻记忆的分数，每说对一给1分，总共3分。如果受访者没有全部正确说出，调查员应该再重复说一遍让受访者复述。重复学习最多6次，若仍不能记忆，则后面的回忆检查则无意义。
+3 注意和计算： 
+①记分方式为0或2分，没有1分。调查员不能帮助受访者记答案，如受访者说20-3等于17，调查员不能说17-3等于多少？而只能说再减3等于多少。
+②要求患者从100连续减7。记分方式为0或2分，没有1分。调查员不能帮助受访者记答案。
+③记分方式为0或2分，没有1分。
+④记分方式为0或2分，没有1分。
+4 判别能力：该部分考查受访者的形成抽象概念的能力。
+①按照3个部分分别给分。说出苹果和桔子的大小、颜色、长在树上都是属于表面特征，给1分。如受访者说出“能吃的”则再给1分。而说出都是水果或果实再给1分。总共3分。这个项目的记分不是受访者说出任意一个相同点就给1分，如果说出的几点都是表面特征只能给1分。
+②按照3个部分分别给分。说出形状上的不同（如高/矮，外形）给1分。如果说出用途的不同单独给1分。如果说出两者设计依据上的不同（椅子以人腿的长度为设计依据，而桌子以人上半身高度为依据）再给1分。
+5 复述：考查受访者的短期记忆。说对一个给1分，总共3分。不论受访者第18项的完成情况如何，这里都要求受访者复述一遍。
+6 语言：从命名、语言的流畅性、听懂命令和阅读书写等方面考查受访者的语言能力。 
+①命名：给患者出示表和圆珠笔，能正确命名各记一分。 
+②语言复述：是检查语言复述能力，要求患者复述中等难度的短句子。调查员只能说一次，正确无误复述给1分。
+③三级命令：准备一张白纸，要求病人把纸用右手拿起来，把它对摺起来，放在左腿
+上。三个动作各得一分。调查员把三个命令连续说完后受访者再做动作。
+④-1阅读理解：让受访者看右边纸上“闭上您的眼睛三次”，请患者先朗读一遍，然后要求患者按纸写命令去做。患者能闭上双眼给一分。 
+④-2书写：让受访者看右边纸上第二个命令，受访者在纸上主动随意写一个句子。检查者不能用口述句子让受访者书写。句子应有主语和谓语，必须有意义，能被人理解。语法和标点符号不作要求。如果受访者在2分钟之内仍不能写出合格的句子给0分。 
+④-3临摹：让受访者自己看右边纸上的命令完成。要求患者临摹重叠的两个五角形，五角形的各边长应在2.5cm左右，但并不强求每条边要多长。必须是两个交叉的五边形，交叉的图形必须是四边形，但角不整齐和边不直可忽略不计。
+三、判定标准
+1、认知功能障碍：最高得分为30分,分数在27-30分为正常,分数&lt;27为认知功能障碍.
+2、痴呆划分标准：文盲≤17分，小学程度≤20分，中学程度（包括中专）≤22分，大学程度（包括大专）≤23分
+3、痴呆严重程度分级：轻度MMSE≥21分;中度,MMSE 10-20分;重度,MMSE≤9分</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GMFM-88</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>脊髓损伤步行指数</t>
+          <t>粗大运动功能评估表(GMFM-88)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>粗大运动功能评估表（GMFM-88）
+项 目
+得 分
+第一次评估
+第二次评估
+第三次评估
+A区仰 卧 位与俯 卧 位（17项）51分
+0 1 2 3
+0 1 2 3
+0 1 2 3 
+1.仰卧位：头正中位,最大限度左右对称转动头部
+2.仰卧位：双手于正中位,双手合拢
+3.仰卧位：抬头45度
+4.仰卧位：右侧髋、膝关节在生理活动范围内屈曲
+5.仰卧位：左侧髋、膝关节在生理活动范围内屈曲 
+6.仰卧位：伸出右上肢、手，越中线抓玩具
+7.仰卧位：伸出左上肢、手，越中线抓玩具
+8.仰卧位：向右侧翻身到俯卧位
+9.仰卧位：向左侧翻身到俯卧位
+10.俯卧位：竖直抬头
+11.肘支撑俯卧位：竖直抬头，肘部伸展，胸部离开床面
+12.肘支撑俯卧位：右前臂水平支撑躯体，左上肢充分向前伸直
+13.肘支撑俯卧位：左前臂水平支撑躯体，右上肢充分向前伸直
+14.俯卧位：向右侧翻身到仰卧位
+15.俯卧位：向左侧翻身到仰卧位
+16.俯卧位：使用四肢向右侧旋转90度
+17.俯卧位：使用四肢向左侧旋转90度
+得分
+得分
+得分
+B区坐 位（20项）60分
+0 1 2 3
+0 1 2 3
+0 1 2 3 
+18.仰卧位：检查者握婴儿双手，自行牵拉成坐位，头部能控制 
+19.仰卧位：向右侧翻身到坐位
+20.仰卧位：向左侧翻身到坐位
+21.坐于垫子上：检查者支撑胸部，头部保持正中位3秒钟
+22.坐于垫子上：检查者支撑胸部，头部保持正中位10秒钟
+23.用上肢支撑坐于垫子上，保持5秒钟
+24.坐于垫子上：没有上肢支撑，保持3秒钟
+25.坐于垫子上：身体前倾触摸玩具后，不用上肢支撑恢复坐位
+26.坐于垫子上：触摸右后方45度玩具后恢复坐位
+27.坐于垫子上：触摸左后方45度玩具后恢复坐位
+28.右侧坐：没有上肢支撑，保持5秒钟
+29.左侧坐：没有上肢支撑，保持5秒钟
+30.坐于垫子上：有控制的从坐位趴成俯卧位
+31.足向前坐于垫子上：向右侧转成四点支撑位
+32.足向前坐于垫子上：向左侧转成四点支撑位
+33.坐于垫子上：不使用上肢帮助，躯体旋转90度
+34.坐于椅凳上：不使用上肢和足支撑，保持10秒钟
+35.站立位：从站位坐到凳子上
+36.坐在地板上：从地板上坐到凳子上
+37.坐在地板上：从地板上坐到椅子上
+得分
+得分
+得分
+C区爬 和 跪（14项）42分
+0 1 2 3
+0 1 2 3
+0 1 2 3 
+38.俯卧位：向前方腹爬1.8米
+39.四点支撑位：用手与膝支撑身体，保持10秒钟
+40.四点支撑位：从四点位到坐位，不用手支撑
+41.俯卧位：转成四点支撑位，用手、膝负重
+42.四点支撑位：右上肢前伸，手高于肩
+43.四点支撑位：左上肢前伸，手高于肩
+44.四点支撑位：向前爬行或拖行1.8米
+45.四点支撑位：向前交替性四点爬1.8米
+46.四点支撑位：用手和膝/脚四点爬上4级台阶
+47.四点支撑位：用手和膝/脚后退爬下4级台阶
+48.坐垫子上：使用上肢支撑转成高跪位，不用上肢支撑，保持10秒钟
+49.高跪位：使用上肢支撑转成右膝半跪，不用上肢支撑，保持10秒钟
+50.高跪位：使用上肢支撑转成左膝半跪，不用上肢支撑，保持10秒钟
+51.高跪位：双膝行走10步，不用上肢支撑
+得分
+得分
+得分
+D区站 立（13项）39分
+0 1 2 3
+0 1 2 3
+0 1 2 3 
+52.坐在地板上：扶椅子站立
+53.站立：不用上肢支撑，保持3秒钟
+54.站立：单手抓住椅子，右脚抬起，保持3秒钟
+55.站立：单手抓住椅子，左脚抬起，保持3秒钟
+56.站立：不用上肢辅助，保持20秒钟
+57.站立：不用上肢辅助，左脚抬起10秒钟
+58.站立：不用上肢辅助，右脚抬起10秒钟
+59.凳子坐位：转成站立位，不用手协助
+60.高跪位：通过右膝半跪到站立，不用上肢协助
+61.高跪位：通过左膝半跪到站立，不用上肢协助
+62.站立位：有控制的下降到地板坐位，不用上肢协助
+63.站立位：转成蹲位，不用上肢协助
+64.站立位：从地板上拾物后，恢复站立位，不用上肢协助
+得分
+得分
+得分
+E区走、跑、跳（24项）72分
+0 1 2 3
+0 1 2 3
+0 1 2 3 
+65.站立：双手扶栏杆，向右侧横走5步
+66.站立：双手扶栏杆，向左侧横走5步
+67.站立：牵双手向前走10步
+68.站立：牵单手向前走10步
+69.站立：不用扶持，向前走10步
+70.站立：向前走10步，停止，转身180度，返回
+71.站立：后退10步
+72.站立：双手提大物品，向前走10步
+73.站立：在20cm宽的平行线之间，连续向前走10步
+74.站立：在2cm宽的直线上，连续向前走10步
+75.站立：右脚跨过膝盖高度的木棒
+76.站立：左脚跨过膝盖高度的木棒
+77.站立：向前跑4.6米，停止，返回
+78.站立：右脚踢球
+79.站立：左脚踢球
+80.站立：两脚同时跳高30cm
+81.站立：两脚同时跳远30cm
+82.右足单立：在直径60cm圆内，右脚单跳10次
+83.左足单立：在直径60cm圆圈内，左脚单跳10次
+84.站立：抓一侧栏杆，上4级台阶，交替出足
+85.站立：抓一侧栏杆，下4级台阶，交替出足
+86.站立：不用扶栏杆，上4级台阶，交替出足
+87.站立：不用扶栏杆，下4级台阶，交替出足
+88.站在15cm高的台阶：两足同时跳下
+评分标准
+0分：指完全不能完成（做）
+1分：指仅能开始会做（即完成动作&lt;10%）
+2分：指部分（10%&lt; 完成&lt;100%）
+3分：指能顺利圆满完成（即100% 完成）
+评分结果：包括以下几项:
+原始分:5个能区的原始分；②总百分比:5个能区原始分占各自总分百分比之和再除以5；
+得分
+得分
+得分
+日期
+日期
+日期
+评估者
+评估者
+评估者
+原始分
+总百分比
+原始分
+总百分比
+原始分
+总百分比
+PAGE 
+PAGE - 3 -</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>脑瘫的康复评估</t>
+          <t>粗大运动功能评估量表(翻译)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>粗大运动功能评估量表（GMFM-88和GMFM-66）
+Version 1.0翻译
+儿童姓名： 编号： 
+评估日期： （年/月/日）
+出生日期： （年/月/日）
+实足年龄： （年/月）
+评估者： 
+关于研究组：
+Dianne Russel, CanChild Centre for Childhood Disability Research, McMaster University, Institute for Applied Health Sciences, McMaster University, 1400 Main St. W., Rm. 408, Hamilton, L8S 1C7
+Tel: North America – 1 905 525-9140 Ext: 27850
+Tel: All other countries – 001 905 525-9140 Ext: 27850
+E-mail: HYPERLINK "mailto:canchild@mcmaster.ca" canchild@mcmaster.ca Fax:1 905 522-6095
+Website: HYPERLINK "http://www.fhs.mcmaster.ca/canchil" www.fhs.mcmaster.ca/canchild
+项目
+A：卧位&amp;翻身
+计分
+NT
+1、仰卧，头位于中线：旋转头部时肢体对称
+0□ 1□ 2□ 3□
+1
+*
+2、仰卧：双手位于中线，手指交叉
+0□ 1□ 2□ 3□
+2
+3、仰卧：头抬起45°
+0□ 1□ 2□ 3□
+3
+4、仰卧：屈曲右髋和右膝到达全范围
+0□ 1□ 2□ 3□
+4
+5、仰卧：屈曲左髋和左膝到达全范围
+0□ 1□ 2□ 3□
+5
+*
+6、仰卧：右上肢和手拿玩具穿过中线
+0□ 1□ 2□ 3□
+6
+*
+7、仰卧：左上肢和手拿玩具穿过中线
+0□ 1□ 2□ 3□
+7
+8、仰卧：自右侧翻身至俯卧
+0□ 1□ 2□ 3□
+8
+9、仰卧：自左侧翻身至俯卧
+0□ 1□ 2□ 3□
+9
+*
+10、俯卧：抬头至竖直
+0□ 1□ 2□ 3□
+10
+11、前臂俯卧：头部竖直，肘部伸直，胸部抬起
+0□ 1□ 2□ 3□
+11
+12、前臂俯卧：右前臂支撑，对侧上肢向前方完全伸直
+0□ 1□ 2□ 3□
+12
+13、前臂俯卧：左前臂支撑，对侧上肢向前方完全伸直
+0□ 1□ 2□ 3□
+13
+14、俯卧：自右侧翻身至仰卧
+0□ 1□ 2□ 3□
+14
+15、俯卧：自左侧翻身至仰卧
+0□ 1□ 2□ 3□
+15
+16、俯卧：使用肢体自由向右翻身90°
+0□ 1□ 2□ 3□
+16
+17、俯卧：使用肢体自由向左翻身90°
+0□ 1□ 2□ 3□
+17
+ A部分总分
+项目
+B：坐位
+计分
+NT
+*
+18、仰卧，检查者握住儿童双手：可以自主坐起且头部控制良好
+0□ 1□ 2□ 3□
+19、仰卧：翻身至右侧坐起
+0□ 1□ 2□ 3□
+20、仰卧：翻身至左侧坐起
+0□ 1□ 2□ 3□
+*
+21、坐在垫子上，治疗师支撑儿童胸部：头部直立保持3秒
+0□ 1□ 2□ 3□
+*
+22、坐在垫子上，治疗师支撑儿童胸部：头部直立保持10秒
+0□ 1□ 2□ 3□
+*
+23、坐在垫子上，上肢支撑：保持5秒
+0□ 1□ 2□ 3□
+*
+24、坐在垫子上：上肢无支撑，保持3秒
+0□ 1□ 2□ 3□
+*
+25、坐在垫子上玩前方的小玩具：
+身体屈向前方，触碰玩具后，返回上肢支撑状态
+0□ 1□ 2□ 3□
+*
+26、坐在垫子上：儿童向右侧弯45°，触碰玩具，并回到起始位置
+0□ 1□ 2□ 3□
+*
+27、坐在垫子上：儿童向左侧弯45°，触碰玩具，并回到起始位置
+0□ 1□ 2□ 3□
+28、右侧坐：保持上肢无支撑状态5秒钟
+0□ 1□ 2□ 3□
+29、左侧坐：保持上肢无支撑状态5秒钟
+0□ 1□ 2□ 3□
+*
+30、坐在垫子上：有控制的转换到俯卧位
+0□ 1□ 2□ 3□
+*
+31、双脚在前坐在垫子上：从右侧至四点跪位
+0□ 1□ 2□ 3□
+*
+32、双脚在前坐在垫子上：从左侧至四点跪位
+0□ 1□ 2□ 3□
+33、坐在垫子上：无上肢辅助，旋转90°
+0□ 1□ 2□ 3□
+*
+34、坐在板凳上：保持上肢和下肢可以自由活动，10秒钟
+0□ 1□ 2□ 3□
+*
+35、站立：从坐在小板凳至站立
+0□ 1□ 2□ 3□
+*
+36、在地上：从地上至坐在小板凳上
+0□ 1□ 2□ 3□
+*
+37、在地上：从地上至坐在大板凳上
+0□ 1□ 2□ 3□
+ B部分总分
+项目
+C：爬行&amp;跪位
+计分
+NT
+38、俯卧：腹爬1.8米
+0□ 1□ 2□ 3□
+*
+39、四点跪位：保持双手和双膝负重，10秒
+0□ 1□ 2□ 3□
+*
+40、四点跪位：至坐位，双手可自由活动
+0□ 1□ 2□ 3□
+*
+41、俯卧：达到四点跪位，双手和双膝负重
+0□ 1□ 2□ 3□
+*
+42、四点跪位：右上肢前平举，手超过肩水平
+0□ 1□ 2□ 3□
+*
+43、四点跪位：左上肢前平举，手超过肩水平
+0□ 1□ 2□ 3□
+*
+44、四点跪位：爬行或上肢爬行1.8米
+0□ 1□ 2□ 3□
+*
+45、四点跪位：相对向前爬行1.8米
+0□ 1□ 2□ 3□
+*
+46、四点跪位：用双手和双膝/足爬行4步
+0□ 1□ 2□ 3□
+47、四点跪位：用双手和双膝/足向后爬行4步
+0□ 1□ 2□ 3□
+*
+48、坐在垫子上：使用上肢跪起，双上肢无支撑，保持10秒
+0□ 1□ 2□ 3□
+49、直立跪位：使用上肢协助右膝向前半跪位，上肢无支撑，保持10秒
+0□ 1□ 2□ 3□
+50、直立跪位：使用上肢协助左膝向前半跪位，上肢无支撑，保持10秒
+0□ 1□ 2□ 3□
+*
+51、直立跪位：向前跪走10步，双上肢无支撑
+0□ 1□ 2□ 3□
+ C部分总分
+项目
+D：站立
+计分
+NT
+*
+52、在地上：通过大板凳站立
+0□ 1□ 2□ 3□
+*
+53、站立：保持上肢无辅助，3秒
+0□ 1□ 2□ 3□
+*
+54、站立：一只手扶住大板凳，抬起右足，保持3秒
+0□ 1□ 2□ 3□
+*
+55、站立：一只手扶住大板凳，抬起左足，保持3秒
+0□ 1□ 2□ 3□
+*
+56、站立：保持上肢无辅助，20秒
+0□ 1□ 2□ 3□
+*
+57、站立：上肢无辅助，抬起右足，10秒
+0□ 1□ 2□ 3□
+*
+58、站立：上肢无辅助，抬起左足，10秒
+0□ 1□ 2□ 3□
+*
+59、坐在小板凳上：不用上肢辅助站起
+0□ 1□ 2□ 3□
+*
+60、直立跪位：无上肢辅助，通过右膝半跪位站立
+0□ 1□ 2□ 3□
+*
+61、直立跪位：无上肢辅助，通过左膝半跪位站立
+0□ 1□ 2□ 3□
+*
+62、站立：无上肢辅助，有控制的坐在地上
+0□ 1□ 2□ 3□
+*
+63、站立：无上肢辅助，转换为蹲位
+0□ 1□ 2□ 3□
+*
+64、站立：无上肢辅助，从地上捡起物品，并回到站立位
+0□ 1□ 2□ 3□
+ D部分总分
+项目
+E：行走、跑步&amp;跳跃
+计分
+NT
+*
+65、站立，双手扶住大板凳：向右侧走5步
+0□ 1□ 2□ 3□
+*
+66、站立，双手扶住大板凳：向左侧走5步
+0□ 1□ 2□ 3□
+*
+67、站立，双手上举：向前行10步
+0□ 1□ 2□ 3□
+*
+68、站立，单手上举：向前行10步
+0□ 1□ 2□ 3□
+*
+69、站立：前行10步
+0□ 1□ 2□ 3□
+*
+70、站立：前行10步，停住，转身180°，返回
+0□ 1□ 2□ 3□
+*
+71、站立：向后行10步
+0□ 1□ 2□ 3□
+*
+72、站立：双手搬动较大物体，向前行10步
+0□ 1□ 2□ 3□
+*
+73、站立：在20cm宽的平行线内连续前行10步
+0□ 1□ 2□ 3□
+*
+74、站立：沿2cm宽的直线连续前行10步
+0□ 1□ 2□ 3□
+*
+75、站立：右足先行，每步高于膝关节水平
+0□ 1□ 2□ 3□
+*
+76、站立：左足先行，每步高于膝关节水平
+0□ 1□ 2□ 3□
+*
+77、站立：跑4.5米，停住并返回
+0□ 1□ 2□ 3□
+*
+78、站立：用右足踢球
+0□ 1□ 2□ 3□
+*
+79、站立：用左足踢球
+0□ 1□ 2□ 3□
+*
+80、站立：双脚同时跳跃30cm高
+0□ 1□ 2□ 3□
+*
+81、站立：双脚同时向前跳跃30cm
+0□ 1□ 2□ 3□
+*
+82、右足单腿站立：在一个60cm的圆圈内，向前连续跳跃10次
+0□ 1□ 2□ 3□
+*
+83、左足单腿站立：在一个60cm的圆圈内，向前连续跳跃10次
+0□ 1□ 2□ 3□
+*
+84、站立，抓住一侧把手：交替腿向上走4步，再抓向另一侧把手
+0□ 1□ 2□ 3□
+*
+85、站立，抓住一侧把手：交替腿向下走4步，再抓向另一侧把手
+0□ 1□ 2□ 3□
+*
+86、站立：交替腿向上走4步
+0□ 1□ 2□ 3□
+*
+87、站立：交替腿向下走4步
+0□ 1□ 2□ 3□
+*
+88、站立15cm的台阶上：双足同时跳下
+0□ 1□ 2□ 3□
+ E部分总分
+这个评估是否能反映儿童“日常（规律）”的表现？ 是 □ 否 □
+注释：
+GMFM计分总结
+检查部分
+每部分计分%的计算
+目标区域
+A. 卧位&amp;翻身
+ A部分总分 = ×100 = %
+ 51 51
+A. □
+B. 坐位
+ B部分总分 = ×100 = %
+ 60 60
+B. □
+C. 爬行&amp;跪位
+ C部分总分 = ×100 = %
+ 42 42
+C. □
+D. 站位
+ D部分总分 = ×100 = %
+ 39 39
+D. □
+E. 行走、跑步&amp;跳跃
+ E部分总分 = ×100 = %
+ 72 72
+E. □
+总分 = %A+%B+%C+%D+%E 
+ 部分的总和
+ = + + + + = = %
+ 5 5
+ 目标总分 = 每一个目标区域的%分数的综合 
+ 目标区域的数量
+ = = %
+GMFM 评估分5个能区，包括88项，分为卧位与翻身、坐位、爬与跪、站立位、行走与跑跳5个能区。卧位与翻身能区总分为51分，坐位为60，爬与跪42，站立位39，行走与跑72。
+评分标准
+0分：指完全不能完成（做）
+1分：指仅能开始会做（即完成动作《10%）
+2分：指部分（10%《完成《100%）
+3分：指能顺利圆满完成（即100%完成）
+ PAGE \* MERGEFORMAT 6
+Mac Keith Press, 2002 GMFM SCORE SHEET
+GMFCS Level1
+□ □ □ □ □
+I II III IV V
+测试环境（如房间、衣着、时间、其他需要描述的内容）
+GMFM是一种标准化视诊仪器，设计并有效的测量脑瘫儿童的粗大运动功能发育。计分意味着一般指导原则。多数项目的每一个分值都具有特定的描述。重要的是这些指导原则包含在手册中，被用于每一个计分项。
+ 计分项：0 = 无法进行此项运动（无法开始）
+ 1 = 仅能开始此项运动（运动完成&lt;30%）
+ 2 = 部分完成
+ 3 = 全部完成
+ NT = 无法测试（用于GMAE计分）
+如果使用GMFM-66 量表（GMAE）软件，重点是分辨无法完成（NT）的选项中真正的“0”分（儿童无法开始进行此项运动）。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MOCA</t>
+          <t>MMT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>蒙特利尔MoCA</t>
+          <t>肌力评定（MMT）</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MRC分级评定标准
+分级
+表 现
+5
+能对抗的阻力与正常相应肌肉的相同，且能作全范围的活动
+5-   
+能对抗的阻力与5级相同，但活动范围&lt;100%而大于50%
+4+
+在活动的初、中期能对抗的阻力与4级相同，但在末期能对抗5级的阻力
+4
+能对抗阻力，但其大小达不到5级的水平
+4-
+能对抗的阻力与4级相同，但活动范围&lt;100%而大于50%
+3+ 
+能抗重力作全关节活动范围的活动，并能在运动末期对抗一定的阻力
+3
+能抗重力运动，且能完成100%的范围，但不能对抗任何阻力
+3-
+能作抗重力运动，但活动范围&lt;100%而大于50%
+2+
+能抗重力运动，但活动范围&lt;50%
+2
+不能抗重力，但在消除重力影响后能作全关节活动范围的活动
+2-
+即使在消除重力影响下能活动，但活动范围&lt;100%而大于50%
+1
+触诊能发现有肌肉收缩，但不能引起任何关节活动
+0
+无任何肌肉收缩迹象
+评级结果
+ 级
+分级
+表 现
+5
+能对抗的阻力与正常相应肌肉的相同（充分阻力），且能作全范围的活动
+5-   
+能对抗较充分阻力稍小的阻力，活动范围100%
+4+
+能对抗比中等程度稍大的阻力，活动范围100%
+4
+能对抗中等度阻力，活动范围100%
+4-
+能对抗比轻度稍大的阻力，活动范围100%
+3+ 
+能抗重力作全关节活动范围的活动，并能在运动末期对抗轻度的阻力
+3
+能抗重力运动，且能完成100%的范围，但不能对抗任何阻力
+3-
+能作抗重力运动，但活动范围&lt;100%而大于50%
+2+
+能抗重力运动，但活动范围&lt;50%
+2
+不能抗重力，但在消除重力影响后能作全关节活动范围的活动
+2-
+即使在消除重力影响下能活动，但活动范围&lt;100%而大于50%
+1+
+触诊能发现有强力肌肉收缩，但不能引起任何关节活动
+1
+触诊能发现有肌肉收缩，但不能引起任何关节活动
+0
+无任何肌肉收缩迹象
+评级结果
+ 级
+Lovett分级评定标准
+0级 无可测知的肌肉收缩
+1级 有轻微收缩，但不能引起关节活动
+2级 在减重状态下能做关节全范围运动
+3级 能抗重力做关节全范围运动，但不能抗阻力
+4级 能抗重力，抗一定阻力运动
+5级 能抗重力，抗充分阻力运动</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>言语失用的评测方法</t>
+          <t>脊髓损伤步行指数</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>脊髓损伤评定系列
+脊髓损伤步行指数
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+级别
+表现
+缩写
+1
+平行杠内行走，穿戴支具，有两人给予身体上的帮助，走不到10米。
+//B2 10
+2
+平行杠内行走，穿戴支具，有两人给予身体上的帮助，达到10米。
+//B2
+3
+平行杠内行走，穿戴支具，有一人给予身体上的帮助，达到10米。
+//B1
+4
+用助行器行走，穿戴支具，有一人给予身体上的帮助，达到10米。
+WB1
+5
+平行杠内行走，不戴支具，有一人给予身体上的帮助，达到10米。
+//NB1
+6
+平行杠内行走，穿戴支具，没有人给予身体上的帮助，达到10米。
+//B0
+7
+用两个拐杖行走，穿戴支具，有一人给予身体上的帮助，达到10米。
+2CB1
+8
+用助行器行走，不戴支具，有一人给予身体上的帮助，达到10米。
+WNB1
+9
+用助行器行走，穿戴支具，没有人给予身体上的帮助，达到10米。
+WB0
+10
+平行杠内行走，不戴支具，没有身体上的帮助，达到10米。
+//NB0
+11
+用一个拐杖行走，穿戴支具，有一人给予身体上的帮助，达到10米。
+1CB1
+12
+用两个拐杖行走，不戴支具，有一人给予身体上的帮助，达到10米。
+2CNB1
+13
+用两个拐杖行走，穿戴支具，没有人给予身体上的帮助，达到10米。
+2CB0
+14
+用助行器行走，不戴支具，没有人给予身体上的帮助，达到10米。
+WNB0
+15
+用一个拐杖行走，不戴支具，有一人给予身体上的帮助，达到10米。
+1CNB1
+16
+用一个拐杖行走，穿戴支具，没有人给予身体上的帮助，达到10米。
+1CB0
+17
+用两个拐杖行走，不戴支具，没有人给予身体上的帮助，达到10米。
+2CNB0
+18
+不用任何器械行走，不戴支具，有一人给予身体上的帮助，达到10米。
+NDNB1
+19
+用一个拐杖行走，不戴支具，没有人给予身体上的帮助，达到10米。
+1CNB0
+20
+不用任何器械行走，不戴支具，没有人给予身体上的帮助，达到10米。
+NDNB0</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
+          <t>脑瘫的康复评估</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>小儿脑性瘫痪的康复评估
+近年来国内对脑性瘫痪（脑瘫）的早期诊断，早期治疗的研究取得了巨大的进展，但对治疗效果评价尚有争议，由于难以量化而造成评价困难。小儿运动功能评价方法早在20世纪80年代后期就开始引起人们的关注，但目前公认的评价标准尚缺乏，脑瘫治疗目的是最大限度要促进随意运动的发展，如何判断患儿能独立完成其运动显得十分重要，从目前遍及欧亚美各国康复专业机构使用的评价标准或量表来看，对小儿脑瘫的康复评估主要从以下方面进行评估：
+1、肌张力的评价：
+生理学上肌肉的张力是指被动拉长或牵拉肌肉时所遇到的阻力；临床上肌张力是指被动活动肢体或按压肌肉时所感觉到的阻力，这种阻力的产生可以来自于组织的物理特性，肌肉或结缔组织内部的弹性，反射性肌肉收缩，在患有脑瘫的儿童大部分有肌张力障碍或肌张力增高或降低，在向躯体四肢随意运动中就会发现主动肌与拮抗肌的不协调收缩，临床上表现为姿势异常。或异常运动模式或异常姿势反射，因此肌张力的评价对小儿脑瘫的康复效果的评估比较重要。（1）临床肌张力分级是一种定量评价方法，检查时根据被动活动肢体时所感觉到的肢体反应或阻力将其分为0-4级。（2）痉挛分级传统方法主要是根据痉挛程度（Spasticity）分为轻度（S）中度（SS）重度（SSS）3个等级，目前较少应用。现大多数采用改良Ashworth痉挛量表，进行临床肌张力评价，共分为0-4级。
+2、关节活动度的评价：
+由于脑瘫患儿肌肉痉挛或肌腱挛缩或被动非正常姿势及异常运动模式的长期存在，会导致四肢关节活动度障碍，关节活动度障碍又会影响脑瘫儿的自主运动，因此脑瘫康复评价中关节活动度的评价也十分重要。关节活动度（ROM）评价可发现障碍关节活动的因素，判定障碍的程度，提示治疗方法，作为治疗训练的评价手段。其方法有用角度计在关节活动的前后测量其活动度，通过测量了解患者自己能够移动的关节活动度（主动），用外力能够移动的关节活动度（被动），日本学者曾介绍0-15岁不同年龄的关节活动范围正常值。包括肩关节、肘关节、腕关节、髋关节、膝关节、踝关节的屈曲、伸展、外展、内收、外旋、内旋的正常角度参考值。国内有作者报道对168例小儿脑瘫康复评估指标是治疗前后足背屈角，股角及运动商数（MQ）。治疗前后均有显著差异（P〈0.01〉，该文以提示关节的活动度测量可作为脑瘫康复评价的重要指标。也有利用电了角度计测量关节活动度，电子角度计本来是一个轴转动测量旋转角度的仪器，在它的活动臂上设定一个可以滑动机构就可以测定关节活动的角度，这种方法可以与角度计的输出关节的活动角度相对应。如果把两个关节的相对应位置关系用6个独立的量表表示，就可以计算出关节活动的三维运动。
+3、肌力的评价：
+肌力是肌肉在收缩或紧张时所表现出来的能力，以肌肉最大兴奋时所能负荷的重量来表示，由于脑瘫患儿长期的四肢，躯干自主运动障碍，大多患儿有不同程度，不同部位的肌力降低，脑瘫儿能否恢复其自主运动与其四肢，躯干肌力恢复正常是分不开的，所以脑瘫康复评估中肌力评价是非常重要的。
+3.1 徒手肌力检查分级法目前儿科较普遍使用的1936 年英国巴尔的摩儿科医院治疗师Heniy 和Flemce 创立了肌力百分数分级的方法，以抗重力运动幅度和抗阻力幅度为依据，将肌力从0-100%分为6个等级。
+3 .2定量肌力检查有电了肌力图仪等，通过负荷传感器记录系统描绘出髋、膝、踝伸屈肌的肌力曲线图。其优点是测量准确性不受检查者的影响，但这些仪器的构造复杂，不易搬运，造价昂贵。
+4、小儿重要反射的评价：
+小儿脑瘫的概要中就说明了两点，一是运动发育迟缓，二是异常姿势或异常姿势反射，因此小儿重要反射的评价在脑瘫康复的评价中是不可缺少的内容，与脑瘫密切相关的反射除众所周知的Vojta7项姿势反射的特定标准外，还有Moro反射，格兰身体侧弯反射；非对称性紧张性颈反射（ATNR）对称性紧张性颈反射（STNR），紧张性迷路反射（TLR）颈直立反射，迷路立直反射，视性立直，躯干立直，降落伞反射等30 项反射发育判定标准。
+5、精细动作完成的的评价：
+小儿脑瘫的主要障碍是运动发育落后，随意运动障碍，所以粗大动作渎精细动作的评价在脑瘫康复评估中可视为评价的核忁内。运动年龄识价（Motor怭age hest-AT）是以0-з:个月的正常儿童动作能力为标准，与障碍儿的动作能力进行比较的评乷方法，可以甩运动指数（Motor Qvotient-Q）来表示。据中国正常儿童运能力发育年龄标准来测嗺脑瘫儿治疗剭后的MR也可以用经典的G婴幼儿发育评估方法，测出发育商数（Dťvglopmental Qv/-tũent DQ）表示。以DQ粗大运动犄商数与DQ 精细动作的商数反映康复水平。为溆具体嚄反映患儿的康复状况，日本津时素岸胜报道了MAT 的上肢运动发育指数（VMQ）和下肢运动发育反指数（LMQ）的评价法，这样可较客观的量化评价脑瘫儿四肢运动功能恢复的状况。功能独立性测量评价法，Long 与Saclo 报道了功能独立性测量(WeeFIM),该量表包括18 个项目并组成6 个维度,包括自理、括约肌控制、移动、行动、交流和社会认知，各项目从日常生活功能全部支持到完全独立共分7级水平，计1-7分。该量表用于6个月-7岁儿童，其中自理、括约肌控制、移动、行动组成了运动因子，社会认知与交流组成认知因子。米拉尼运动发育评价（Milani-Compareti）判定出较详细的米拉尼运动发育评价表，该评价表其优点除对抬头，保持坐位，坐起，站立，走路等动作进行评价外，还对躯体四肢的调整反应，降落伞反应和倾斜反应及影响上述3种反应的原始反射进行综合评价。该检查表其共分3个部分，自发动作9项，诱发反应4项，自发运动与诱发反应的相互关系17项。适合年龄0-6岁。应用于小儿脑瘫康复评价中也是一种较好的评价方法。
+6、生活自理能力（activities of daily living-ADL）
+是指人们为独立生活而每天必须反复进行的，最基本的，具有共性的身体动作群，即进行衣、食、住、行，个人卫生等基本动作和技巧。广义的ADL 是指人们在家庭生活中，在工作中和社区中的活动。包括日常生活活动能力、判断能力、与他人的交流能力，执行社会任务的能力，以及在经济上、社会上和职业上安排自己生活方式的能力。对于小儿脑瘫的康复目标，家庭及社会对其康复最基本的要求是患儿可以生活自理。因此ADL 的评价在小儿康复医学中越来越受到重视，在脑瘫的康复评价中同样也占有主导地位。目前儿童多用的ADL 评价量表是胡莹媛修定的，该量表包括9 个部分：个人卫生动作，进食动作，更衣动作，排便动作，电器使用，认识交流动作，床上运动，移动动作，步行动作，共50 项，评分按完成的程度每项有2 分，1.5 分，1 分，0.5 分，0分共5个评定级别，满分100分。该量表可以较全面的反应脑瘫儿童治疗前后粗大运动，精细动作，手眼协调动作，肌力及肌张力的情报况，但缺乏对脑瘫异常姿势反射的认识量表。
+7、综合全面评价：
+前面已介绍有关的6种评价方法，都从不同角度对小儿脑瘫进行康复评价。从目前国内外小儿康复医学进展看，对小儿脑瘫实施全面综合康复是一种大的趋势。包括运动、生活自理能力、心理、认知、神经反射等综合评价。Russell1989年报到了婴幼儿运动功能评估量表，经修订后应用于小儿脑瘫的疗效评估，其方法简便易实用，该量表共分5个功能区。（1）卧位运动与部分原始反射残存，姿势反射（降落伞反射）的建立；（2）爬与跪的运动；（3）坐位运动结合平衡反射建立；（4）站位运动；（5）走、跪、跑、及攀登运动。共计80项，评分标准按完成的程度评分0-3分。其适应年龄在0-6岁，以功能区分，实际得分，总分来表示脑瘫康复治疗前后的疗效，该量表5个功能区可以将脑瘫的主要功能障碍、姿势异常、异常姿势反射的康复情况反应出来。该量表即可以评估小儿运动发育，又可对重要反射进行评估，从某些功能区也反映肌力，肌张力的变化情况。因此该量表基本上可以较全面评价小儿脑瘫康复状况，其不足之处是无生活自理能力的评价内容。中国康复中心博爱医院报道，应用脑瘫综合康复评定表对小儿脑瘫进行全面康复评价。该表有5个功能区，50项测评内容：（1）认知能力；（2）言语功能；（3）运动功能；（4）生活自理能力；（5）社会适应能力。其评价标准为02分共五级，50项测评内容：每一项测评内容包括四个小问题，完成一个给0.5 分，全部完成2 分。因此该量表的最在特点是评价客观具体在评价过程中无人为因素的影响，可重复性强，易于操作。该评定量表的另一特点是比较全面的评价脑瘫儿童康复效果。从认知、社会适应能力评价到运动能力，生活自理能力及综合功能的评价。其不足是小儿重要反射的评价，运动功能的评估项目与精神动作评价内容较少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MOCA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>蒙特利尔MoCA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+蒙特利尔认知评估（MoCA）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>言语失用的评测方法</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>言语失用的评测方法 + 首先观察患者的自发语是否具有言语失用的症状特征：(1)音的错误缺乏一贯性，重复同样的词时会出现不同的错误音。(2)在错音种类中，辅音的置换最多，其次是辅音省略、添加、反复等。(3)随着构音器官运动调节的复杂性增加，发音错误也相应增加，其中摩擦音和塞擦音最容易出现错误。(4)辅音在词头的位置比在其它位置的发音时错误多。(5)在置换错误中，与目标音的构音点和构音模式相近的音被置换的最多 。(6)自发性言语和反应性言语(1～10、星期、问候语等)的错误少，有目的性、主动的言语错误多。(7)发音错误随词句的长度和难度增加而增多。(8)有构音器官的探索行为。(9)有韵律的障碍、反复自我修正、速度降低、单音调、口吃样的停顿等特点也会呈现出来。(10) 在多数情况下，患者对自己的错误很在意。如果发现患者的言语符合以上的特征，则可以初步判断其有言语失用的障碍。
+摘自：中国康复理论与实践 2000年第2期第6卷 理论与实践</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>额叶功能评定表</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>语言-认知障碍评定系列表
+额叶功能评定表（FAB）
+姓名： 性别： 年龄： 科室： 床号： 住院号： 
+主诉： 
+诊断： 检查日期：
+检查项目
+操作方法
+评分标准
+类似性
+（概念化）
+“下面两个或三个物体有什么类似的”
+香蕉和桔子
+桌子和椅子
+郁金香、玫瑰和月季
+3题正确3分
+2题正确2分
+1题正确1分
+没有正确0分
+词汇流畅性
+（心理灵活性）
+尽可能多的说出以“一”【yi1】字或“大”字开头的词（60s）
+多于9个3分
+6-9个2分
+3-5个1分
+3个以下0分
+3、运动序列测试（程序性控制）
+检查者坐在患者前面，说“仔细看我如何做”，用左手做3次“拳-刀-掌”动作；“现在用你的右手先跟我做同样序列动作，然后再自己做”，3次同时做后，让患者自己做
+单独连续完成6次3分
+单独连续完成3-5次2分
+患者自己失败，同时做时3次正确1分
+同时做也无法达到3次0分
+4、不一致性指令
+（对干扰的敏感性）
+我拍1下你就拍2下，试行3次，即1-1-1，我拍2下你就拍1下，试行2-2-2，我们正式开始：1-1-2-1-2-2-2-1-1-2
+全正确3分
+1-2个错误2分
+3个以上错误1分
+连续像检查者一样拍起码4次0分
+5、Go-No Go试验
+（抑制性控制）
+当我拍1下时你拍1下，试行1-1-1，当我拍2下时你不用拍，试行2-2-2.我们正式开始：1-1-2-1-2-2-2-1-1-2.
+全正确3分
+1-2个错误2分
+3个以上错误1分
+连续像检查者一样拍起码4次0分
+6、抓握行为
+（环境自主性）
+坐在患者前，使其双手掌向上放在膝盖上，检查者不说任何话或看着患者，把双手触摸患者手掌，观察患者是否自动抓握，如果有则重新试一次，说“现在请别抓我的手”。
+患者没有抓手3分
+患者迟疑并问该怎么做2分
+患者毫不犹豫抓握1分
+在第二次不让抓握时再次抓握0分
+总分</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
